--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -527,13 +527,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.884</v>
+        <v>0.89</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.112</v>
+        <v>0.109</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -561,44 +561,44 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0.113</v>
+        <v>0.105</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.444</v>
+        <v>0.453</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.235</v>
+        <v>0.222</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.116</v>
+        <v>0.132</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.022</v>
+        <v>0.017</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.011</v>
+        <v>0.017</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -613,37 +613,37 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.401</v>
+        <v>0.391</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.417</v>
+        <v>0.414</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.083</v>
+        <v>0.076</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>0.027</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.019</v>
+        <v>0.025</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>0.003</v>
@@ -660,152 +660,150 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" s="1" t="n">
+        <v>0.043</v>
+      </c>
       <c r="E6" s="1" t="n">
-        <v>0.019</v>
+        <v>0.318</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.057</v>
+        <v>0.553</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.216</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.16</v>
+        <v>0.013</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.141</v>
+        <v>0.001</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="R6" s="1" t="n">
         <v>0.002</v>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="E7" s="1" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.028</v>
+        <v>0.067</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.142</v>
+        <v>0.203</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.165</v>
+        <v>0.162</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.189</v>
+        <v>0.119</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.186</v>
+        <v>0.115</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.122</v>
+        <v>0.093</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.048</v>
+        <v>0.066</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="O7" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q7" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="P7" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" s="1" t="n">
-        <v>0.041</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>0.291</v>
+        <v>0.002</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.589</v>
+        <v>0.02</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.065</v>
+        <v>0.151</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.011</v>
+        <v>0.185</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>0.202</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.155</v>
+      </c>
       <c r="K8" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+        <v>0.123</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -814,178 +812,180 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>0.026</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" s="1" t="n">
-        <v>0.083</v>
+        <v>0.013</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.207</v>
+        <v>0.073</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.163</v>
+        <v>0.121</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.094</v>
+        <v>0.135</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.076</v>
+        <v>0.149</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.08</v>
+        <v>0.154</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.123</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.065</v>
+        <v>0.096</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.037</v>
+        <v>0.048</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.036</v>
+        <v>0.041</v>
       </c>
       <c r="P9" s="1" t="n">
         <v>0.021</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.999</v>
+        <v>0.9960000000000001</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="F10" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="G10" s="1" t="n">
-        <v>0.07199999999999999</v>
-      </c>
       <c r="H10" s="1" t="n">
-        <v>0.117</v>
+        <v>0.043</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.157</v>
+        <v>0.066</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.149</v>
+        <v>0.09</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.124</v>
+        <v>0.128</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.113</v>
+        <v>0.165</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.106</v>
+        <v>0.166</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.118</v>
       </c>
       <c r="O10" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="Q10" s="1" t="n">
         <v>0.034</v>
       </c>
-      <c r="P10" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>0.013</v>
-      </c>
       <c r="R10" s="1" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.9970000000000001</v>
+        <v>0.995</v>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
       <c r="G11" s="1" t="n">
-        <v>0.023</v>
+        <v>0.216</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.026</v>
+        <v>0.12</v>
       </c>
       <c r="I11" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="L11" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="J11" s="1" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>0.166</v>
-      </c>
       <c r="M11" s="1" t="n">
-        <v>0.127</v>
+        <v>0.055</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.131</v>
+        <v>0.058</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.102</v>
+        <v>0.042</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.059</v>
+        <v>0.031</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.035</v>
+        <v>0.012</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>0.007</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9940000000000001</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -1002,49 +1002,49 @@
         <v>0.003</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>0.075</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.112</v>
+        <v>0.119</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.101</v>
+        <v>0.117</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.103</v>
+        <v>0.131</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.123</v>
+        <v>0.109</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.109</v>
+        <v>0.095</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.093</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.067</v>
+        <v>0.058</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="13">
@@ -1054,57 +1054,59 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9860000000000001</v>
+        <v>0.9870000000000001</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="E13" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.023</v>
+        <v>0.026</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.113</v>
+        <v>0.119</v>
       </c>
       <c r="H13" s="1" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>0.151</v>
       </c>
-      <c r="I13" s="1" t="n">
-        <v>0.158</v>
-      </c>
       <c r="J13" s="1" t="n">
-        <v>0.139</v>
+        <v>0.112</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.1</v>
+        <v>0.112</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.034</v>
+        <v>0.042</v>
       </c>
       <c r="O13" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="Q13" s="1" t="n">
         <v>0.038</v>
       </c>
-      <c r="P13" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.028</v>
-      </c>
       <c r="R13" s="1" t="n">
-        <v>0.015</v>
+        <v>0.026</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="14">
@@ -1119,48 +1121,50 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="G14" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.016</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.037</v>
+        <v>0.048</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.053</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.153</v>
+        <v>0.183</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.156</v>
+        <v>0.131</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.102</v>
+        <v>0.124</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.089</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="R14" s="1" t="n">
         <v>0.051</v>
       </c>
       <c r="S14" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="T14" s="1" t="n">
         <v>0.025</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.015</v>
       </c>
     </row>
     <row r="15">
@@ -1178,39 +1182,41 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J15" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.013</v>
+        <v>0.019</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.049</v>
+        <v>0.045</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.117</v>
+        <v>0.097</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.169</v>
+        <v>0.184</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.215</v>
+        <v>0.184</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.133</v>
+        <v>0.157</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.111</v>
+        <v>0.114</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.08</v>
+        <v>0.073</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.039</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="16">
@@ -1235,28 +1241,28 @@
         <v>0.002</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.052</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.123</v>
+        <v>0.132</v>
       </c>
       <c r="Q16" s="1" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="R16" s="1" t="n">
         <v>0.174</v>
       </c>
-      <c r="R16" s="1" t="n">
-        <v>0.198</v>
-      </c>
       <c r="S16" s="1" t="n">
-        <v>0.143</v>
+        <v>0.144</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.113</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="17">
@@ -1266,53 +1272,55 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.765</v>
+        <v>0.779</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="G17" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>0.021</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.028</v>
+        <v>0.035</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.06</v>
+        <v>0.049</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="N17" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="R17" s="1" t="n">
         <v>0.068</v>
       </c>
-      <c r="O17" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>0.061</v>
-      </c>
       <c r="S17" s="1" t="n">
-        <v>0.074</v>
+        <v>0.062</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.054</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="18">
@@ -1322,7 +1330,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.7260000000000001</v>
+        <v>0.7060000000000001</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -1335,28 +1343,28 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.041</v>
+        <v>0.029</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.083</v>
+        <v>0.057</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.12</v>
+        <v>0.139</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.166</v>
+        <v>0.154</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.157</v>
+        <v>0.179</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.145</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="19">
@@ -1366,53 +1374,53 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.672</v>
+        <v>0.656</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I19" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="Q19" s="1" t="n">
         <v>0.018</v>
       </c>
-      <c r="J19" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K19" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="L19" s="1" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="M19" s="1" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="N19" s="1" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="O19" s="1" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>0.017</v>
-      </c>
       <c r="R19" s="1" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.018</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="20">
@@ -1422,7 +1430,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.483</v>
+        <v>0.464</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -1434,27 +1442,29 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="N20" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>0.014</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>0.033</v>
+        <v>0.039</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.076</v>
+        <v>0.064</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.096</v>
+        <v>0.091</v>
       </c>
       <c r="S20" s="1" t="n">
         <v>0.126</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.135</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="21">
@@ -1464,14 +1474,16 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.282</v>
+        <v>0.299</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="I21" s="1" t="n">
         <v>0.001</v>
       </c>
@@ -1479,44 +1491,44 @@
         <v>0.002</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.018</v>
+        <v>0.031</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.025</v>
+        <v>0.043</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>0.045</v>
+        <v>0.054</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.046</v>
+        <v>0.044</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.038</v>
+        <v>0.022</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.207</v>
+        <v>0.223</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -1527,40 +1539,36 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="1" t="n">
-        <v>0.008</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" s="1" t="n">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.037</v>
+        <v>0.03</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.043</v>
+        <v>0.064</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.059</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Amaney</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.203</v>
+        <v>0.202</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -1570,35 +1578,45 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="K23" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>0.012</v>
+      </c>
       <c r="P23" s="1" t="n">
-        <v>0.011</v>
+        <v>0.021</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.027</v>
+        <v>0.037</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.062</v>
+        <v>0.045</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.184</v>
+        <v>0.191</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -1611,28 +1629,28 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="25">
@@ -1642,7 +1660,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.126</v>
+        <v>0.162</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1653,32 +1671,26 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M25" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="N25" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.007</v>
+        <v>0.018</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.022</v>
+        <v>0.032</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.044</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="26">
@@ -1688,7 +1700,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.122</v>
+        <v>0.112</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -1702,25 +1714,25 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>0.006</v>
       </c>
       <c r="Q26" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="S26" s="1" t="n">
         <v>0.023</v>
       </c>
-      <c r="R26" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="S26" s="1" t="n">
-        <v>0.033</v>
-      </c>
       <c r="T26" s="1" t="n">
-        <v>0.038</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="27">
@@ -1730,7 +1742,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.08399999999999999</v>
+        <v>0.095</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1744,21 +1756,21 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="O27" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.038</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="28">
@@ -1768,7 +1780,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.05300000000000001</v>
+        <v>0.047</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -1781,36 +1793,34 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="P28" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R28" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bogdansskii</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.022</v>
+        <v>0.013</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -1824,31 +1834,29 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -1866,23 +1874,23 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="S30" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -1896,27 +1904,25 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -1933,24 +1939,20 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="S32" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
       <c r="T32" s="1" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -1968,21 +1970,19 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
-      <c r="S33" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" s="1" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -1999,24 +1999,20 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S34" s="1" t="n">
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" s="1" t="n">
         <v>0.002</v>
-      </c>
-      <c r="T34" s="1" t="n">
-        <v>0.004</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -2037,18 +2033,16 @@
         <v>0.001</v>
       </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -2066,9 +2060,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="S36" t="inlineStr"/>
       <c r="T36" s="1" t="n">
         <v>0.001</v>
       </c>
@@ -2076,7 +2068,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
@@ -2106,7 +2098,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iamgroot</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2132,7 +2124,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2184,7 +2176,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2210,7 +2202,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2236,7 +2228,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>Gluckspilz8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2288,7 +2280,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ЭтоМойНик</t>
+          <t>WHATSWRONGib</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2340,7 +2332,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Gluckspilz8</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2366,7 +2358,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dama_pica</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2392,7 +2384,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Кесадилия</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2418,7 +2410,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>LateNightCraver</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2444,7 +2436,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>KidPoker</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2470,7 +2462,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Кесадилия</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -527,10 +527,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.89</v>
+        <v>0.897</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.109</v>
+        <v>0.102</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>0.001</v>
@@ -561,42 +561,42 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.453</v>
+        <v>0.431</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.222</v>
+        <v>0.237</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.132</v>
+        <v>0.137</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>0.006</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="L4" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N4" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="M4" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -613,43 +613,43 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.391</v>
+        <v>0.417</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.414</v>
+        <v>0.405</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.076</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.027</v>
+        <v>0.018</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.025</v>
+        <v>0.017</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -668,19 +668,19 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="1" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.318</v>
+        <v>0.317</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.553</v>
+        <v>0.556</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>0.001</v>
@@ -713,49 +713,49 @@
         <v>0.001</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.203</v>
+        <v>0.21</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.162</v>
+        <v>0.164</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.119</v>
+        <v>0.129</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.115</v>
+        <v>0.108</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.093</v>
+        <v>0.1</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.079</v>
+        <v>0.059</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.066</v>
+        <v>0.056</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.033</v>
+        <v>0.047</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.031</v>
+        <v>0.027</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -772,40 +772,44 @@
         <v>0.002</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.02</v>
+        <v>0.034</v>
       </c>
       <c r="G8" s="1" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="I8" s="1" t="n">
         <v>0.151</v>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>0.202</v>
-      </c>
       <c r="J8" s="1" t="n">
-        <v>0.155</v>
+        <v>0.176</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.123</v>
+        <v>0.127</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.094</v>
+        <v>0.104</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.016</v>
+        <v>0.024</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>0.006</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+        <v>0.003</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
     </row>
@@ -816,176 +820,178 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>1</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="F9" s="1" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.073</v>
+        <v>0.08</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.121</v>
+        <v>0.115</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.135</v>
+        <v>0.139</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.149</v>
+        <v>0.153</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.154</v>
+        <v>0.14</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.123</v>
+        <v>0.101</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.096</v>
+        <v>0.082</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.048</v>
+        <v>0.077</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.041</v>
+        <v>0.051</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="S9" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T9" s="1" t="n">
         <v>0.002</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>0.001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.9960000000000001</v>
+        <v>0.9979999999999999</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="E10" s="1" t="n">
-        <v>0.001</v>
+        <v>0.016</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.001</v>
+        <v>0.073</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0.008</v>
+        <v>0.22</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.043</v>
+        <v>0.147</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.066</v>
+        <v>0.105</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>0.09</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.128</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.165</v>
+        <v>0.066</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.166</v>
+        <v>0.055</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.118</v>
+        <v>0.055</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.054</v>
+        <v>0.017</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.034</v>
+        <v>0.017</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.995</v>
+        <v>0.9930000000000001</v>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>0.021</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.216</v>
+        <v>0.017</v>
       </c>
       <c r="H11" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="K11" s="1" t="n">
         <v>0.12</v>
       </c>
-      <c r="I11" s="1" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>0.076</v>
-      </c>
       <c r="L11" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.151</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.055</v>
+        <v>0.16</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.058</v>
+        <v>0.134</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.042</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.031</v>
+        <v>0.067</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.012</v>
+        <v>0.039</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="T11" t="inlineStr"/>
+        <v>0.008</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0.008</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -994,7 +1000,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9940000000000001</v>
+        <v>0.9920000000000001</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -1002,46 +1008,46 @@
         <v>0.003</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.022</v>
+        <v>0.015</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>0.075</v>
+        <v>0.077</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.119</v>
+        <v>0.101</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.117</v>
+        <v>0.127</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.131</v>
+        <v>0.113</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.095</v>
+        <v>0.098</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.077</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.058</v>
+        <v>0.05</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.024</v>
+        <v>0.03</v>
       </c>
       <c r="R12" s="1" t="n">
         <v>0.024</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.008</v>
+        <v>0.021</v>
       </c>
       <c r="T12" s="1" t="n">
         <v>0.005</v>
@@ -1054,59 +1060,55 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9870000000000001</v>
+        <v>0.9879999999999999</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" s="1" t="n">
-        <v>0.026</v>
+        <v>0.021</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.119</v>
+        <v>0.116</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.149</v>
+        <v>0.16</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.151</v>
+        <v>0.147</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.112</v>
+        <v>0.136</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.112</v>
+        <v>0.105</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.045</v>
+        <v>0.067</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.042</v>
+        <v>0.034</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.031</v>
+        <v>0.036</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.038</v>
+        <v>0.02</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1116,7 +1118,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9570000000000001</v>
+        <v>0.9550000000000001</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -1125,46 +1127,46 @@
         <v>0.001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.022</v>
+        <v>0.032</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.048</v>
+        <v>0.038</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.053</v>
+        <v>0.061</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.083</v>
+        <v>0.118</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.123</v>
+        <v>0.147</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.183</v>
+        <v>0.14</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.131</v>
+        <v>0.14</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.124</v>
+        <v>0.108</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.051</v>
+        <v>0.041</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.025</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="15">
@@ -1174,7 +1176,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9480000000000001</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -1183,40 +1185,40 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.019</v>
+        <v>0.038</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.045</v>
+        <v>0.053</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.097</v>
+        <v>0.108</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.184</v>
+        <v>0.176</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.184</v>
+        <v>0.196</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.157</v>
+        <v>0.15</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.114</v>
+        <v>0.109</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.073</v>
+        <v>0.056</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.051</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="16">
@@ -1226,7 +1228,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.841</v>
+        <v>0.8460000000000001</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -1238,31 +1240,31 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.132</v>
+        <v>0.137</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.163</v>
+        <v>0.164</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.174</v>
+        <v>0.165</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.144</v>
+        <v>0.17</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.106</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="17">
@@ -1272,55 +1274,53 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.779</v>
+        <v>0.7710000000000001</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H17" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>0.012</v>
-      </c>
       <c r="I17" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.035</v>
+        <v>0.038</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.078</v>
+        <v>0.059</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.102</v>
+        <v>0.089</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.097</v>
+        <v>0.114</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.103</v>
+        <v>0.104</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="R17" s="1" t="n">
         <v>0.068</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.045</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="18">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.7060000000000001</v>
+        <v>0.7250000000000001</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -1340,31 +1340,33 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.057</v>
+        <v>0.08</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="R18" s="1" t="n">
         <v>0.154</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.179</v>
+        <v>0.166</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.137</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="19">
@@ -1374,53 +1376,55 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.656</v>
+        <v>0.6660000000000001</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="G19" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>0.016</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0.029</v>
+        <v>0.033</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.063</v>
+        <v>0.057</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0.091</v>
+        <v>0.101</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.125</v>
+        <v>0.132</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.129</v>
+        <v>0.115</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.067</v>
+        <v>0.093</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.033</v>
+        <v>0.026</v>
       </c>
       <c r="Q19" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="S19" s="1" t="n">
         <v>0.018</v>
       </c>
-      <c r="R19" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S19" s="1" t="n">
-        <v>0.024</v>
-      </c>
       <c r="T19" s="1" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="20">
@@ -1430,7 +1434,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -1449,22 +1453,22 @@
         <v>0.005</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>0.039</v>
+        <v>0.031</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.064</v>
+        <v>0.044</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.091</v>
+        <v>0.105</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.124</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="21">
@@ -1474,61 +1478,59 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.299</v>
+        <v>0.291</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" s="1" t="n">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="I21" s="1" t="n">
-        <v>0.001</v>
-      </c>
       <c r="J21" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.031</v>
+        <v>0.016</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.043</v>
+        <v>0.026</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.045</v>
+        <v>0.053</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.044</v>
+        <v>0.056</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.022</v>
+        <v>0.033</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Amaney</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.223</v>
+        <v>0.221</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -1540,35 +1542,39 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>0.007</v>
+      </c>
       <c r="O22" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0.005</v>
+        <v>0.022</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.03</v>
+        <v>0.044</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.064</v>
+        <v>0.047</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.102</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.202</v>
+        <v>0.218</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -1578,45 +1584,41 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L23" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.021</v>
+        <v>0.036</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.06</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.191</v>
+        <v>0.196</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -1628,39 +1630,35 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="N24" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" s="1" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>0.019</v>
+        <v>0.007</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.045</v>
+        <v>0.051</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.057</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>Добряк</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.162</v>
+        <v>0.148</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1670,37 +1668,45 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="K25" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="O25" s="1" t="n">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="R25" s="1" t="n">
         <v>0.032</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.058</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.112</v>
+        <v>0.148</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -1712,37 +1718,39 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="N26" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.023</v>
+        <v>0.036</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.043</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.095</v>
+        <v>0.117</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1757,30 +1765,32 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
+        <v>0.002</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>0.005</v>
+      </c>
       <c r="Q27" s="1" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.016</v>
+        <v>0.027</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.045</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.047</v>
+        <v>0.067</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -1794,33 +1804,29 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P28" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.016</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.013</v>
+        <v>0.05</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -1834,29 +1840,33 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="P29" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+        <v>0.003</v>
+      </c>
+      <c r="Q29" s="1" t="n">
+        <v>0.008</v>
+      </c>
       <c r="R29" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.007</v>
+        <v>0.022</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -1870,17 +1880,21 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="R30" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0.002</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="31">
@@ -1890,7 +1904,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -1907,22 +1921,24 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+      <c r="R31" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S31" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -1938,9 +1954,13 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="T32" s="1" t="n">
         <v>0.005</v>
       </c>
@@ -1948,11 +1968,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>АРАМАИСКА</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -1969,20 +1989,24 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+      <c r="R33" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S33" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="T33" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -1999,20 +2023,22 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -2030,10 +2056,12 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+      <c r="T35" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2059,16 +2087,16 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
@@ -2090,18 +2118,20 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="S37" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>Сан Саныч</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -2118,13 +2148,15 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+      <c r="S38" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2150,7 +2182,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2202,7 +2234,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2228,7 +2260,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gluckspilz8</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2254,7 +2286,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2280,7 +2312,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WHATSWRONGib</t>
+          <t>iamgroot</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2306,7 +2338,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2332,7 +2364,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ромчик</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2358,7 +2390,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>Кадык</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2384,7 +2416,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Кесадилия</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2410,7 +2442,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LateNightCraver</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2436,7 +2468,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KidPoker</t>
+          <t>Staryii</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2462,7 +2494,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -520,31 +520,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Roman_Furtatov</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.897</v>
+        <v>0.004</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.102</v>
+        <v>0.397</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+        <v>0.394</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -554,48 +574,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="1" t="n">
-        <v>0.431</v>
+        <v>0.052</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.237</v>
+        <v>0.325</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.137</v>
+        <v>0.551</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.038</v>
+        <v>0.058</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -606,51 +618,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Roman_Furtatov</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.003</v>
+        <v>0.878</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.122</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -660,42 +650,56 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" s="1" t="n">
+        <v>0.118</v>
+      </c>
       <c r="D6" s="1" t="n">
-        <v>0.045</v>
+        <v>0.423</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.317</v>
+        <v>0.238</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.556</v>
+        <v>0.116</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.063</v>
+        <v>0.046</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.016</v>
+        <v>0.025</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.001</v>
+        <v>0.011</v>
       </c>
       <c r="J6" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
     </row>
@@ -713,46 +717,50 @@
         <v>0.001</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.21</v>
+        <v>0.172</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.164</v>
+        <v>0.168</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.129</v>
+        <v>0.121</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>0.108</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.1</v>
+        <v>0.111</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.059</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.056</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.027</v>
+        <v>0.013</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+        <v>0.004</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T7" s="1" t="n">
         <v>0.001</v>
       </c>
@@ -769,34 +777,34 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.145</v>
+        <v>0.141</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.179</v>
+        <v>0.192</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.151</v>
+        <v>0.181</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.176</v>
+        <v>0.156</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.127</v>
+        <v>0.137</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.104</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.047</v>
+        <v>0.052</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>0.006</v>
@@ -807,67 +815,69 @@
       <c r="Q8" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="R8" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.999</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="E9" s="1" t="n">
-        <v>0.002</v>
+        <v>0.016</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.007</v>
+        <v>0.097</v>
       </c>
       <c r="G9" s="1" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <v>0.08</v>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0.153</v>
-      </c>
       <c r="K9" s="1" t="n">
-        <v>0.14</v>
+        <v>0.075</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.101</v>
+        <v>0.082</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.082</v>
+        <v>0.066</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.077</v>
+        <v>0.053</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.051</v>
+        <v>0.03</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.025</v>
+        <v>0.018</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="R9" s="1" t="n">
         <v>0.006</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="T9" s="1" t="n">
         <v>0.002</v>
@@ -876,63 +886,59 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.9979999999999999</v>
+        <v>0.998</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" s="1" t="n">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R10" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>0.012</v>
-      </c>
       <c r="S10" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="11">
@@ -942,7 +948,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.9930000000000001</v>
+        <v>0.9940000000000001</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -951,46 +957,46 @@
         <v>0.001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.077</v>
+        <v>0.061</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.081</v>
+        <v>0.094</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.151</v>
+        <v>0.17</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.16</v>
+        <v>0.145</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.134</v>
+        <v>0.11</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.067</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.014</v>
+        <v>0.023</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="12">
@@ -1000,57 +1006,59 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9920000000000001</v>
+        <v>0.9930000000000001</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="E12" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.101</v>
+        <v>0.107</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.127</v>
+        <v>0.1</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.113</v>
+        <v>0.121</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.108</v>
+        <v>0.095</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.098</v>
+        <v>0.106</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.091</v>
+        <v>0.103</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.05</v>
+        <v>0.057</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.043</v>
+        <v>0.053</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="13">
@@ -1060,55 +1068,57 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9879999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="F13" s="1" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.116</v>
+        <v>0.138</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.16</v>
+        <v>0.135</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.147</v>
+        <v>0.157</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.136</v>
+        <v>0.143</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>0.105</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.074</v>
+        <v>0.079</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.067</v>
+        <v>0.051</v>
       </c>
       <c r="N13" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="O13" s="1" t="n">
         <v>0.034</v>
       </c>
-      <c r="O13" s="1" t="n">
-        <v>0.036</v>
-      </c>
       <c r="P13" s="1" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="Q13" s="1" t="n">
         <v>0.02</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="S13" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="T13" s="1" t="n">
         <v>0.012</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1118,7 +1128,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9550000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -1127,46 +1137,46 @@
         <v>0.001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="J14" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="S14" s="1" t="n">
         <v>0.038</v>
       </c>
-      <c r="K14" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="L14" s="1" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="N14" s="1" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>0.032</v>
-      </c>
       <c r="T14" s="1" t="n">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="15">
@@ -1176,7 +1186,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9480000000000001</v>
+        <v>0.9269999999999999</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -1184,41 +1194,39 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.038</v>
+        <v>0.016</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.053</v>
+        <v>0.059</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>0.108</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.176</v>
+        <v>0.174</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.196</v>
+        <v>0.177</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.15</v>
+        <v>0.163</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.109</v>
+        <v>0.096</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.056</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.047</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="16">
@@ -1228,7 +1236,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.8460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -1243,28 +1251,28 @@
         <v>0.003</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.022</v>
+        <v>0.033</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.079</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.137</v>
+        <v>0.129</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.164</v>
+        <v>0.179</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.165</v>
+        <v>0.176</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.17</v>
+        <v>0.133</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.102</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="17">
@@ -1274,53 +1282,53 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.7710000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H17" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>0.004</v>
-      </c>
       <c r="I17" s="1" t="n">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.038</v>
+        <v>0.029</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.05</v>
+        <v>0.057</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.059</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.089</v>
+        <v>0.094</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.114</v>
+        <v>0.103</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.104</v>
+        <v>0.097</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.091</v>
+        <v>0.081</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.068</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.058</v>
+        <v>0.066</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.06</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="18">
@@ -1340,33 +1348,31 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.026</v>
+        <v>0.036</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.08</v>
+        <v>0.091</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.137</v>
+        <v>0.115</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.154</v>
+        <v>0.163</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.166</v>
+        <v>0.17</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.151</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="19">
@@ -1376,52 +1382,50 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.6660000000000001</v>
+        <v>0.678</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>0.016</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0.033</v>
+        <v>0.042</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.057</v>
+        <v>0.061</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0.101</v>
+        <v>0.096</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.132</v>
+        <v>0.138</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.115</v>
+        <v>0.118</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.093</v>
+        <v>0.078</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.026</v>
+        <v>0.048</v>
       </c>
       <c r="Q19" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="S19" s="1" t="n">
         <v>0.017</v>
-      </c>
-      <c r="R19" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="S19" s="1" t="n">
-        <v>0.018</v>
       </c>
       <c r="T19" s="1" t="n">
         <v>0.032</v>
@@ -1434,7 +1438,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.465</v>
+        <v>0.481</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -1450,35 +1454,35 @@
         <v>0.001</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>0.031</v>
+        <v>0.034</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.044</v>
+        <v>0.077</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.105</v>
+        <v>0.112</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.128</v>
+        <v>0.12</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.134</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Комарик</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.291</v>
+        <v>0.21</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -1486,51 +1490,37 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J21" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="K21" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="L21" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="M21" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="N21" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>0.053</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" s="1" t="n">
-        <v>0.05</v>
+        <v>0.007</v>
       </c>
       <c r="Q21" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="S21" s="1" t="n">
         <v>0.056</v>
       </c>
-      <c r="R21" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="S21" s="1" t="n">
-        <v>0.02</v>
-      </c>
       <c r="T21" s="1" t="n">
-        <v>0.015</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.221</v>
+        <v>0.204</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -1543,38 +1533,38 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N22" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="N22" s="1" t="n">
+      <c r="O22" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="P22" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="O22" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="P22" s="1" t="n">
-        <v>0.022</v>
-      </c>
       <c r="Q22" s="1" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="R22" s="1" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="S22" s="1" t="n">
         <v>0.044</v>
       </c>
-      <c r="S22" s="1" t="n">
-        <v>0.047</v>
-      </c>
       <c r="T22" s="1" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Amaney</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.218</v>
+        <v>0.191</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -1590,35 +1580,35 @@
         <v>0.001</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.036</v>
+        <v>0.021</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.046</v>
+        <v>0.047</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.063</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.196</v>
+        <v>0.149</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -1633,32 +1623,32 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.015</v>
+        <v>0.022</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.037</v>
+        <v>0.027</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.051</v>
+        <v>0.036</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Добряк</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.148</v>
+        <v>0.099</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1668,45 +1658,37 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L25" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M25" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N25" s="1" t="n">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P25" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="O25" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="P25" s="1" t="n">
-        <v>0.015</v>
-      </c>
       <c r="Q25" s="1" t="n">
-        <v>0.025</v>
+        <v>0.008</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.032</v>
+        <v>0.016</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.026</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.148</v>
+        <v>0.09</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -1718,39 +1700,35 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N26" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.019</v>
+        <v>0.002</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.024</v>
+        <v>0.013</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.036</v>
+        <v>0.029</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.056</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.117</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1763,34 +1741,34 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" s="1" t="n">
+      <c r="N27" s="1" t="n">
         <v>0.002</v>
       </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.027</v>
+        <v>0.008</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.029</v>
+        <v>0.017</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.042</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.067</v>
+        <v>0.018</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -1807,26 +1785,26 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="R28" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="T28" s="1" t="n">
         <v>0.008999999999999999</v>
-      </c>
-      <c r="S28" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="T28" s="1" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.05</v>
+        <v>0.017</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -1840,33 +1818,27 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="P29" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="Q29" s="1" t="n">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S29" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="R29" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="S29" s="1" t="n">
-        <v>0.015</v>
-      </c>
       <c r="T29" s="1" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bogdansskii</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.022</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -1880,19 +1852,15 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="S30" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" s="1" t="n">
         <v>0.006</v>
       </c>
@@ -1900,11 +1868,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -1921,24 +1889,22 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>АРАМАИСКА</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -1954,25 +1920,25 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S32" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -1992,21 +1958,19 @@
       <c r="R33" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="S33" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -2023,22 +1987,22 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" s="1" t="n">
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="S34" t="inlineStr"/>
       <c r="T34" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -2055,18 +2019,18 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="S35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T35" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -2087,16 +2051,16 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
@@ -2118,20 +2082,18 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>0.001</v>
-      </c>
+          <t>Плейбой в карты</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -2148,15 +2110,13 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2182,7 +2142,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2208,7 +2168,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2234,7 +2194,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Gluckspilz8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2260,7 +2220,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2286,7 +2246,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2312,7 +2272,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iamgroot</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2338,7 +2298,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>dama_pica</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2364,7 +2324,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2390,7 +2350,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Кадык</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2416,7 +2376,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>iamgroot</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2442,7 +2402,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Staryii</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2468,7 +2428,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Staryii</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2494,7 +2454,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ромчик</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -520,51 +520,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Roman_Furtatov</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.004</v>
+        <v>0.881</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.397</v>
+        <v>0.117</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -574,42 +554,54 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" s="1" t="n">
+        <v>0.113</v>
+      </c>
       <c r="D4" s="1" t="n">
-        <v>0.052</v>
+        <v>0.432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.325</v>
+        <v>0.231</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.551</v>
+        <v>0.121</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.058</v>
+        <v>0.037</v>
       </c>
       <c r="H4" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M4" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="I4" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J4" s="1" t="n">
+      <c r="N4" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O4" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="K4" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
@@ -618,29 +610,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Roman_Furtatov</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.878</v>
+        <v>0.006</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>0.397</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -650,56 +664,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>0.118</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="1" t="n">
-        <v>0.423</v>
+        <v>0.052</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.238</v>
+        <v>0.309</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.116</v>
+        <v>0.546</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.046</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
     </row>
@@ -717,49 +719,49 @@
         <v>0.001</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.172</v>
+        <v>0.203</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.168</v>
+        <v>0.154</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="J7" s="1" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="K7" s="1" t="n">
         <v>0.108</v>
       </c>
-      <c r="K7" s="1" t="n">
-        <v>0.111</v>
-      </c>
       <c r="L7" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.045</v>
+        <v>0.033</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="R7" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="T7" s="1" t="n">
         <v>0.001</v>
@@ -772,121 +774,115 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="E8" s="1" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.033</v>
+        <v>0.035</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.141</v>
+        <v>0.152</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.192</v>
+        <v>0.205</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.181</v>
+        <v>0.174</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.156</v>
+        <v>0.153</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.137</v>
+        <v>0.119</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.052</v>
+        <v>0.055</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>0.999</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>0.016</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" s="1" t="n">
-        <v>0.097</v>
+        <v>0.015</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.224</v>
+        <v>0.061</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.125</v>
+        <v>0.124</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.103</v>
+        <v>0.156</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.08</v>
+        <v>0.143</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.075</v>
+        <v>0.157</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.082</v>
+        <v>0.112</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.066</v>
+        <v>0.083</v>
       </c>
       <c r="N9" s="1" t="n">
         <v>0.053</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.03</v>
+        <v>0.049</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="R9" s="1" t="n">
         <v>0.006</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.004</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -894,51 +890,53 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" s="1" t="n">
+        <v>0.03</v>
+      </c>
       <c r="F10" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q10" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="G10" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>0.01</v>
-      </c>
       <c r="R10" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="S10" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="S10" s="1" t="n">
+      <c r="T10" s="1" t="n">
         <v>0.003</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>0.002</v>
       </c>
     </row>
     <row r="11">
@@ -954,46 +952,46 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.04</v>
+        <v>0.031</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.061</v>
+        <v>0.068</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.094</v>
+        <v>0.104</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.121</v>
+        <v>0.11</v>
       </c>
       <c r="L11" s="1" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="M11" s="1" t="n">
         <v>0.17</v>
       </c>
-      <c r="M11" s="1" t="n">
-        <v>0.145</v>
-      </c>
       <c r="N11" s="1" t="n">
-        <v>0.11</v>
+        <v>0.128</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.093</v>
+        <v>0.097</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.046</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.023</v>
+        <v>0.01</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="T11" s="1" t="n">
         <v>0.003</v>
@@ -1002,73 +1000,71 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9930000000000001</v>
+        <v>0.991</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>0.08</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.107</v>
+        <v>0.163</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.1</v>
+        <v>0.169</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.121</v>
+        <v>0.118</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.095</v>
+        <v>0.11</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.106</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.103</v>
+        <v>0.051</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.073</v>
+        <v>0.046</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.057</v>
+        <v>0.028</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.053</v>
+        <v>0.033</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.039</v>
+        <v>0.021</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.018</v>
+        <v>0.026</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.99</v>
+        <v>0.9880000000000001</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -1076,49 +1072,49 @@
         <v>0.003</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.138</v>
+        <v>0.067</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.135</v>
+        <v>0.098</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.157</v>
+        <v>0.129</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.143</v>
+        <v>0.116</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.105</v>
+        <v>0.102</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.079</v>
+        <v>0.096</v>
       </c>
       <c r="M13" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="P13" s="1" t="n">
         <v>0.051</v>
       </c>
-      <c r="N13" s="1" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0.03</v>
-      </c>
       <c r="Q13" s="1" t="n">
-        <v>0.02</v>
+        <v>0.032</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="14">
@@ -1128,7 +1124,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.9620000000000001</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -1137,46 +1133,46 @@
         <v>0.001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>0.067</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.128</v>
+        <v>0.123</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.17</v>
+        <v>0.149</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.144</v>
+        <v>0.154</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.109</v>
+        <v>0.114</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.051</v>
+        <v>0.048</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.038</v>
+        <v>0.029</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="15">
@@ -1186,7 +1182,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9269999999999999</v>
+        <v>0.9470000000000001</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -1196,37 +1192,37 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.016</v>
+        <v>0.035</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.108</v>
+        <v>0.104</v>
       </c>
       <c r="O15" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="Q15" s="1" t="n">
         <v>0.174</v>
       </c>
-      <c r="P15" s="1" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>0.163</v>
-      </c>
       <c r="R15" s="1" t="n">
-        <v>0.096</v>
+        <v>0.105</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.037</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="16">
@@ -1236,7 +1232,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.85</v>
+        <v>0.8330000000000001</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -1248,31 +1244,31 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.079</v>
+        <v>0.066</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.129</v>
+        <v>0.14</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.179</v>
+        <v>0.166</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.176</v>
+        <v>0.155</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.133</v>
+        <v>0.154</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="17">
@@ -1282,20 +1278,20 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.77</v>
+        <v>0.7820000000000001</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.003</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.021</v>
+        <v>0.008</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>0.017</v>
@@ -1304,31 +1300,31 @@
         <v>0.029</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.057</v>
+        <v>0.05</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.094</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="O17" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="P17" s="1" t="n">
         <v>0.103</v>
       </c>
-      <c r="P17" s="1" t="n">
-        <v>0.097</v>
-      </c>
       <c r="Q17" s="1" t="n">
-        <v>0.081</v>
+        <v>0.108</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.079</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.066</v>
+        <v>0.055</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="18">
@@ -1338,7 +1334,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.7250000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -1349,30 +1345,30 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="N18" s="1" t="n">
         <v>0.012</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.036</v>
+        <v>0.032</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.091</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.115</v>
+        <v>0.11</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.163</v>
+        <v>0.157</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.17</v>
+        <v>0.178</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.136</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="19">
@@ -1382,53 +1378,53 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.678</v>
+        <v>0.672</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>0.042</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.061</v>
+        <v>0.064</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0.096</v>
+        <v>0.092</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.138</v>
+        <v>0.124</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>0.118</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.078</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.048</v>
+        <v>0.037</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.013</v>
+        <v>0.019</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.032</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="20">
@@ -1438,7 +1434,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.481</v>
+        <v>0.472</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -1449,40 +1445,42 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="M20" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.077</v>
+        <v>0.066</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.112</v>
+        <v>0.107</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.119</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Amaney</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.21</v>
+        <v>0.212</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -1493,24 +1491,32 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="L21" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>0.011</v>
+      </c>
       <c r="P21" s="1" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.012</v>
+        <v>0.023</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.041</v>
+        <v>0.049</v>
       </c>
       <c r="S21" s="1" t="n">
         <v>0.056</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.094</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="22">
@@ -1520,7 +1526,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -1533,38 +1539,38 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0.007</v>
+        <v>0.017</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.049</v>
+        <v>0.043</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.044</v>
+        <v>0.038</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.058</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.191</v>
+        <v>0.18</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -1576,29 +1582,23 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N23" s="1" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="P23" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>0.021</v>
-      </c>
       <c r="R23" s="1" t="n">
-        <v>0.035</v>
+        <v>0.029</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.047</v>
+        <v>0.058</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.054</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="24">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.149</v>
+        <v>0.145</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -1623,32 +1623,32 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q24" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="R24" s="1" t="n">
         <v>0.022</v>
       </c>
-      <c r="R24" s="1" t="n">
-        <v>0.027</v>
-      </c>
       <c r="S24" s="1" t="n">
-        <v>0.036</v>
+        <v>0.044</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.053</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.099</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1666,29 +1666,29 @@
         <v>0.001</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.029</v>
+        <v>0.02</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.041</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.09</v>
+        <v>0.061</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -1700,13 +1700,17 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="O26" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="Q26" s="1" t="n">
         <v>0.002</v>
@@ -1715,20 +1719,20 @@
         <v>0.013</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.029</v>
+        <v>0.015</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.044</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.05500000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1741,34 +1745,32 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q27" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S27" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="Q27" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="R27" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="S27" s="1" t="n">
-        <v>0.017</v>
-      </c>
       <c r="T27" s="1" t="n">
-        <v>0.021</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bogdansskii</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -1784,27 +1786,23 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="S28" s="1" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>АРАМАИСКА</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.017</v>
+        <v>0.008</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -1820,25 +1818,25 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" s="1" t="n">
+      <c r="Q29" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="S29" s="1" t="n">
-        <v>0.008</v>
-      </c>
       <c r="T29" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -1855,24 +1853,26 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S30" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="R30" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S30" t="inlineStr"/>
       <c r="T30" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -1887,24 +1887,24 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -1924,21 +1924,19 @@
       <c r="R32" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="S32" s="1" t="n">
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" s="1" t="n">
         <v>0.002</v>
-      </c>
-      <c r="T32" s="1" t="n">
-        <v>0.004</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -1955,12 +1953,12 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="T33" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="34">
@@ -1970,7 +1968,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -1988,9 +1986,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" s="1" t="n">
         <v>0.002</v>
       </c>
@@ -1998,11 +1994,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -2020,17 +2016,15 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="S35" t="inlineStr"/>
       <c r="T35" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -2052,15 +2046,15 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
@@ -2090,7 +2084,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2116,7 +2110,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>дюдю221</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2142,7 +2136,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2168,7 +2162,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2194,7 +2188,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gluckspilz8</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2220,7 +2214,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2272,7 +2266,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2298,7 +2292,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>dama_pica</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2324,7 +2318,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>dama_pica</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2350,7 +2344,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ромчик</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2376,7 +2370,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iamgroot</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2428,7 +2422,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>Кесадилия</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2454,7 +2448,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -527,15 +527,17 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.881</v>
+        <v>0.858</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.117</v>
+        <v>0.132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -561,40 +563,40 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0.113</v>
+        <v>0.114</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.432</v>
+        <v>0.278</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.231</v>
+        <v>0.199</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.121</v>
+        <v>0.322</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>0.002</v>
@@ -610,51 +612,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.397</v>
+        <v>0.242</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.408</v>
+        <v>0.46</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.031</v>
+        <v>0.002</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -664,41 +652,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" s="1" t="n">
-        <v>0.052</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>0.309</v>
+        <v>0.007</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.546</v>
+        <v>0.102</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.466</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.01</v>
+        <v>0.189</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.007</v>
+        <v>0.108</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.003</v>
+        <v>0.057</v>
       </c>
       <c r="K6" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -708,232 +702,230 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>0.9999999999999999</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.023</v>
+      </c>
       <c r="D7" s="1" t="n">
-        <v>0.001</v>
+        <v>0.348</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.01</v>
+        <v>0.322</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.203</v>
+        <v>0.033</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.154</v>
+        <v>0.014</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.124</v>
+        <v>0.016</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.116</v>
+        <v>0.011</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.108</v>
+        <v>0.013</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.057</v>
+        <v>0.003</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.033</v>
+        <v>0.003</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.014</v>
+        <v>0.003</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" s="1" t="n">
-        <v>0.035</v>
+        <v>0.013</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.152</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.205</v>
+        <v>0.213</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.174</v>
+        <v>0.182</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.153</v>
+        <v>0.13</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.119</v>
+        <v>0.091</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.066</v>
+        <v>0.075</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.055</v>
+        <v>0.047</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.022</v>
+        <v>0.042</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.011</v>
+        <v>0.028</v>
       </c>
       <c r="P8" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T8" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="Q8" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.999</v>
+        <v>0.9970000000000001</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" s="1" t="n">
+        <v>0.007</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.998</v>
+        <v>0.997</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="1" t="n">
-        <v>0.03</v>
+        <v>0.001</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.093</v>
+        <v>0.002</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0.247</v>
+        <v>0.042</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.134</v>
+        <v>0.077</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.082</v>
+        <v>0.097</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.074</v>
+        <v>0.112</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.08</v>
+        <v>0.118</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.066</v>
+        <v>0.125</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.067</v>
+        <v>0.121</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.042</v>
+        <v>0.09</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.034</v>
+        <v>0.079</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.018</v>
+        <v>0.064</v>
       </c>
       <c r="Q10" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="S10" s="1" t="n">
         <v>0.013</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>0.004</v>
       </c>
       <c r="T10" s="1" t="n">
         <v>0.003</v>
@@ -942,119 +934,119 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.9940000000000001</v>
+        <v>0.9870000000000001</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="F11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.036</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.022</v>
+        <v>0.143</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.031</v>
+        <v>0.147</v>
       </c>
       <c r="I11" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="M11" s="1" t="n">
         <v>0.068</v>
       </c>
-      <c r="J11" s="1" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>0.17</v>
-      </c>
       <c r="N11" s="1" t="n">
-        <v>0.128</v>
+        <v>0.059</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.097</v>
+        <v>0.062</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.046</v>
+        <v>0.032</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="R11" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T11" s="1" t="n">
         <v>0.01</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>0.003</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.991</v>
+        <v>0.9820000000000001</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" s="1" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="G12" s="1" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0.163</v>
-      </c>
       <c r="I12" s="1" t="n">
-        <v>0.169</v>
+        <v>0.047</v>
       </c>
       <c r="J12" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="M12" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="K12" s="1" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0.051</v>
-      </c>
       <c r="N12" s="1" t="n">
-        <v>0.046</v>
+        <v>0.127</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.028</v>
+        <v>0.093</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.033</v>
+        <v>0.083</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.021</v>
+        <v>0.065</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.026</v>
+        <v>0.059</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.014</v>
+        <v>0.04</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.011</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="13">
@@ -1064,125 +1056,123 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9880000000000001</v>
+        <v>0.9730000000000001</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" s="1" t="n">
-        <v>0.017</v>
+        <v>0.011</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.067</v>
+        <v>0.03</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.098</v>
+        <v>0.06</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.129</v>
+        <v>0.104</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.116</v>
+        <v>0.109</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.102</v>
+        <v>0.111</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>0.096</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.103</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.057</v>
+        <v>0.059</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.051</v>
+        <v>0.063</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.032</v>
+        <v>0.052</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.017</v>
+        <v>0.045</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.007</v>
+        <v>0.037</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9620000000000001</v>
+        <v>0.9690000000000001</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" s="1" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.004</v>
+        <v>0.106</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.012</v>
+        <v>0.144</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.017</v>
+        <v>0.158</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.05</v>
+        <v>0.142</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.067</v>
+        <v>0.102</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.11</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.123</v>
+        <v>0.037</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.149</v>
+        <v>0.026</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.154</v>
+        <v>0.033</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.114</v>
+        <v>0.027</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.065</v>
+        <v>0.019</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.048</v>
+        <v>0.03</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9470000000000001</v>
+        <v>0.954</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -1192,183 +1182,205 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.035</v>
+        <v>0.01</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.056</v>
+        <v>0.03</v>
       </c>
       <c r="N15" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O15" s="1" t="n">
         <v>0.104</v>
       </c>
-      <c r="O15" s="1" t="n">
-        <v>0.165</v>
-      </c>
       <c r="P15" s="1" t="n">
-        <v>0.173</v>
+        <v>0.19</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.174</v>
+        <v>0.182</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.105</v>
+        <v>0.19</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.077</v>
+        <v>0.12</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.048</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Котяра 😼</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.8330000000000001</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="G16" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>0.032</v>
+      </c>
       <c r="L16" s="1" t="n">
-        <v>0.002</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.006</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.031</v>
+        <v>0.122</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.066</v>
+        <v>0.13</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.14</v>
+        <v>0.118</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.166</v>
+        <v>0.123</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.155</v>
+        <v>0.11</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.154</v>
+        <v>0.075</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.113</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mihmbox</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.7820000000000001</v>
+        <v>0.875</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" s="1" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.075</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.116</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.101</v>
+        <v>0.119</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.103</v>
+        <v>0.12</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.108</v>
+        <v>0.123</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.079</v>
+        <v>0.077</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.055</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>Mihmbox</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.7100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="G18" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>0.036</v>
+      </c>
       <c r="M18" s="1" t="n">
-        <v>0.001</v>
+        <v>0.047</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.012</v>
+        <v>0.05</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.032</v>
+        <v>0.081</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.11</v>
+        <v>0.103</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.157</v>
+        <v>0.083</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.178</v>
+        <v>0.106</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.148</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="19">
@@ -1378,63 +1390,65 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.672</v>
+        <v>0.7130000000000001</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="G19" s="1" t="n">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.008</v>
+        <v>0.029</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.014</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0.042</v>
+        <v>0.108</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.064</v>
+        <v>0.102</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0.092</v>
+        <v>0.107</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.124</v>
+        <v>0.091</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.118</v>
+        <v>0.048</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.037</v>
+        <v>0.016</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.019</v>
+        <v>0.013</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.019</v>
+        <v>0.025</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.025</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.472</v>
+        <v>0.53</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -1445,32 +1459,30 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="N20" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="O20" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="O20" s="1" t="n">
-        <v>0.012</v>
-      </c>
       <c r="P20" s="1" t="n">
-        <v>0.033</v>
+        <v>0.016</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.066</v>
+        <v>0.045</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.107</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.125</v>
+        <v>0.168</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.122</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="21">
@@ -1480,7 +1492,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.212</v>
+        <v>0.381</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -1490,43 +1502,45 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L21" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.002</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.011</v>
+        <v>0.031</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>0.013</v>
+        <v>0.039</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.023</v>
+        <v>0.061</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.049</v>
+        <v>0.078</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.056</v>
+        <v>0.074</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.052</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Комарик</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.206</v>
+        <v>0.251</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -1536,41 +1550,45 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="K22" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="M22" s="1" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.008</v>
+        <v>0.032</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0.017</v>
+        <v>0.025</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.026</v>
+        <v>0.042</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.038</v>
+        <v>0.045</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.066</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.18</v>
+        <v>0.145</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -1585,30 +1603,32 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
+        <v>0.002</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="Q23" s="1" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.029</v>
+        <v>0.024</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.058</v>
+        <v>0.046</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.073</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.145</v>
+        <v>0.141</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -1622,33 +1642,31 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" s="1" t="n">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q24" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="P24" s="1" t="n">
+      <c r="R24" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="Q24" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="R24" s="1" t="n">
-        <v>0.022</v>
-      </c>
       <c r="S24" s="1" t="n">
-        <v>0.044</v>
+        <v>0.038</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.049</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.094</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1661,34 +1679,36 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="O25" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.034</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Добряк</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.061</v>
+        <v>0.066</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -1703,36 +1723,34 @@
       <c r="M26" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="N26" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.013</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bogdansskii</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.017</v>
+        <v>0.064</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1746,31 +1764,33 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="P27" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.01</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.011</v>
+        <v>0.042</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -1786,19 +1806,23 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="R28" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S28" t="inlineStr"/>
+        <v>0.003</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>0.011</v>
+      </c>
       <c r="T28" s="1" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
+          <t>Абеляр</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1818,15 +1842,15 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" s="1" t="n">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="30">
@@ -1852,23 +1876,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="R30" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S30" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" s="1" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1887,10 +1905,10 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" s="1" t="n">
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" s="1" t="n">
@@ -1900,7 +1918,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1921,10 +1939,10 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" s="1" t="n">
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="S32" t="inlineStr"/>
       <c r="T32" s="1" t="n">
         <v>0.002</v>
       </c>
@@ -1932,11 +1950,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -1953,10 +1971,10 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="R33" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" s="1" t="n">
         <v>0.001</v>
       </c>
@@ -1964,7 +1982,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1994,7 +2012,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>dama_pica</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -2015,21 +2033,19 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>0.001</v>
-      </c>
+          <t>АРАМАИСКА</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -2047,19 +2063,15 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Chinaski</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>0.001</v>
-      </c>
+          <t>Тихоня</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
@@ -2077,14 +2089,12 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2110,7 +2120,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>дюдю221</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2136,7 +2146,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2162,7 +2172,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2188,7 +2198,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2214,7 +2224,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2240,7 +2250,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2266,7 +2276,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2292,7 +2302,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2318,7 +2328,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>dama_pica</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2344,7 +2354,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>KidPoker</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2370,7 +2380,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ромчик</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2396,7 +2406,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Staryii</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2422,7 +2432,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Кесадилия</t>
+          <t>WHATSWRONGib</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2448,7 +2458,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>Чейз</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -527,13 +527,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.858</v>
+        <v>0.857</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.132</v>
+        <v>0.135</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>0.001</v>
@@ -556,55 +556,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0.114</v>
+        <v>0.02</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.278</v>
+        <v>0.324</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.199</v>
+        <v>0.347</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.322</v>
+        <v>0.206</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.039</v>
+        <v>0.021</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.015</v>
+        <v>0.025</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.011</v>
+        <v>0.024</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="L4" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="M4" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -619,19 +617,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.242</v>
+        <v>0.248</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.46</v>
+        <v>0.443</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.29</v>
+        <v>0.305</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>0.001</v>
@@ -661,34 +659,34 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.102</v>
+        <v>0.117</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.466</v>
+        <v>0.469</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.189</v>
+        <v>0.177</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.108</v>
+        <v>0.104</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.057</v>
+        <v>0.046</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="M6" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="N6" s="1" t="n">
         <v>0.006</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.008999999999999999</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>0.001</v>
@@ -702,55 +700,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>0.9999999999999999</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.023</v>
+        <v>0.121</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.348</v>
+        <v>0.292</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.322</v>
+        <v>0.188</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>0.033</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.014</v>
+        <v>0.023</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="P7" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -762,407 +760,409 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" s="1" t="n">
-        <v>0.013</v>
+        <v>0.019</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.213</v>
+        <v>0.201</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.182</v>
+        <v>0.172</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.13</v>
+        <v>0.141</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.091</v>
+        <v>0.078</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.075</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.047</v>
+        <v>0.058</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.042</v>
+        <v>0.046</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.028</v>
+        <v>0.036</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.026</v>
+        <v>0.016</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.9970000000000001</v>
+        <v>0.997</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="F9" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.015</v>
-      </c>
       <c r="T9" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.997</v>
+        <v>0.996</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0.042</v>
+        <v>0.017</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.077</v>
+        <v>0.04</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.097</v>
+        <v>0.074</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.112</v>
+        <v>0.08</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.118</v>
+        <v>0.125</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.125</v>
+        <v>0.138</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.121</v>
+        <v>0.131</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.09</v>
+        <v>0.129</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.079</v>
+        <v>0.105</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.064</v>
+        <v>0.076</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.027</v>
+        <v>0.043</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
       <c r="S10" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="T10" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.9870000000000001</v>
+        <v>0.9880000000000001</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" s="1" t="n">
-        <v>0.036</v>
+        <v>0.002</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.143</v>
+        <v>0.005</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.147</v>
+        <v>0.017</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.104</v>
+        <v>0.038</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.091</v>
+        <v>0.066</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.061</v>
+        <v>0.12</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.068</v>
+        <v>0.145</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.059</v>
+        <v>0.121</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.062</v>
+        <v>0.109</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.032</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.036</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.036</v>
+        <v>0.046</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.014</v>
+        <v>0.031</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.01</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9820000000000001</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="F12" s="1" t="n">
-        <v>0.001</v>
+        <v>0.026</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>0.007</v>
+        <v>0.149</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.025</v>
+        <v>0.143</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.047</v>
+        <v>0.109</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.074</v>
+        <v>0.095</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.104</v>
+        <v>0.077</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.114</v>
+        <v>0.068</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.118</v>
+        <v>0.066</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.127</v>
+        <v>0.054</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.093</v>
+        <v>0.042</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.083</v>
+        <v>0.057</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.065</v>
+        <v>0.037</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.059</v>
+        <v>0.032</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.04</v>
+        <v>0.017</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9730000000000001</v>
+        <v>0.971</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R13" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0.045</v>
-      </c>
       <c r="S13" s="1" t="n">
-        <v>0.037</v>
+        <v>0.025</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9690000000000001</v>
+        <v>0.9680000000000001</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="F14" s="1" t="n">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.106</v>
+        <v>0.035</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.144</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.158</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.142</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>0.102</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.037</v>
+        <v>0.094</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.026</v>
+        <v>0.067</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.033</v>
+        <v>0.065</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.027</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.019</v>
+        <v>0.06</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.027</v>
+        <v>0.038</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="15">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.954</v>
+        <v>0.961</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -1180,39 +1180,39 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" s="1" t="n">
+      <c r="I15" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" s="1" t="n">
         <v>0.003</v>
-      </c>
-      <c r="K15" s="1" t="n">
-        <v>0.004</v>
       </c>
       <c r="L15" s="1" t="n">
         <v>0.01</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.06</v>
+        <v>0.067</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.104</v>
+        <v>0.1</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.19</v>
+        <v>0.178</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.182</v>
+        <v>0.184</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.19</v>
+        <v>0.178</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.12</v>
+        <v>0.132</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.061</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1222,53 +1222,55 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.904</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="G16" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>0.032</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.122</v>
+        <v>0.105</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.13</v>
+        <v>0.118</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.118</v>
+        <v>0.135</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.123</v>
+        <v>0.107</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.075</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.052</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="17">
@@ -1278,51 +1280,53 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.875</v>
+        <v>0.874</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="H17" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>0.015</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.03</v>
+        <v>0.019</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.116</v>
+        <v>0.105</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.119</v>
+        <v>0.139</v>
       </c>
       <c r="P17" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Q17" s="1" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q17" s="1" t="n">
-        <v>0.123</v>
-      </c>
       <c r="R17" s="1" t="n">
-        <v>0.077</v>
+        <v>0.095</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="18">
@@ -1332,55 +1336,53 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.73</v>
+        <v>0.703</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.019</v>
+        <v>0.029</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>0.024</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.05</v>
+        <v>0.055</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>0.081</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.061</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.103</v>
+        <v>0.104</v>
       </c>
       <c r="R18" s="1" t="n">
         <v>0.083</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.106</v>
+        <v>0.091</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.079</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="19">
@@ -1390,55 +1392,55 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.7130000000000001</v>
+        <v>0.6950000000000001</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>0.015</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.029</v>
+        <v>0.039</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.052</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0.108</v>
+        <v>0.099</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.102</v>
+        <v>0.123</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0.107</v>
+        <v>0.092</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.091</v>
+        <v>0.065</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.048</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.013</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="S19" s="1" t="n">
         <v>0.025</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.033</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="20">
@@ -1448,7 +1450,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.53</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -1459,30 +1461,32 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="M20" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="N20" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.168</v>
+        <v>0.186</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="21">
@@ -1492,7 +1496,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.381</v>
+        <v>0.401</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -1500,37 +1504,39 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" s="1" t="n">
+      <c r="I21" s="1" t="n">
         <v>0.001</v>
       </c>
+      <c r="J21" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" s="1" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.031</v>
+        <v>0.026</v>
       </c>
       <c r="P21" s="1" t="n">
         <v>0.039</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.061</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.078</v>
+        <v>0.065</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.074</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.075</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1540,7 +1546,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.251</v>
+        <v>0.254</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -1548,43 +1554,47 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="K22" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="L22" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>0.008</v>
+        <v>0.016</v>
       </c>
       <c r="O22" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="P22" s="1" t="n">
         <v>0.032</v>
       </c>
-      <c r="P22" s="1" t="n">
-        <v>0.025</v>
-      </c>
       <c r="Q22" s="1" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.04</v>
+        <v>0.038</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.045</v>
+        <v>0.034</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.04</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -1606,29 +1616,29 @@
         <v>0.002</v>
       </c>
       <c r="P23" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q23" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="Q23" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="R23" s="1" t="n">
-        <v>0.024</v>
+        <v>0.017</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.046</v>
+        <v>0.036</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.061</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.141</v>
+        <v>0.144</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -1644,19 +1654,19 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.089</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="25">
@@ -1666,7 +1676,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.094</v>
+        <v>0.095</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1679,32 +1689,30 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.024</v>
+        <v>0.027</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Добряк</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -1720,37 +1728,33 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="1" t="n">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P26" s="1" t="n">
+      <c r="Q26" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="Q26" s="1" t="n">
+      <c r="R26" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="R26" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="S26" s="1" t="n">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.024</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.064</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1764,33 +1768,31 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="Q27" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R27" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="R27" s="1" t="n">
-        <v>0.012</v>
-      </c>
       <c r="S27" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.042</v>
+        <v>0.01</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -1806,27 +1808,23 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" s="1" t="n">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="R28" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="S28" s="1" t="n">
-        <v>0.011</v>
-      </c>
       <c r="T28" s="1" t="n">
-        <v>0.025</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -1847,20 +1845,18 @@
         <v>0.001</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T29" s="1" t="n">
-        <v>0.006</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -1877,20 +1873,22 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -1906,24 +1904,20 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Кальян</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>0.003</v>
-      </c>
+          <t>Плейбой в карты</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -1940,22 +1934,16 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T32" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>0.002</v>
-      </c>
+          <t>EliasPavlov</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -1971,23 +1959,17 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>0.002</v>
-      </c>
+          <t>Викусик</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2005,19 +1987,15 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dama_pica</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>0.001</v>
-      </c>
+          <t>АРАМАИСКА</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -2033,16 +2011,14 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2068,7 +2044,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2094,7 +2070,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>dama_pica</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2120,7 +2096,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2146,7 +2122,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2172,7 +2148,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2198,7 +2174,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2224,7 +2200,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2250,7 +2226,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2276,7 +2252,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2302,7 +2278,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2354,7 +2330,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KidPoker</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2380,7 +2356,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Staryii</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2406,7 +2382,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Кесадилия</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2432,7 +2408,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WHATSWRONGib</t>
+          <t>Gluckspilz8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2458,7 +2434,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Чейз</t>
+          <t>finch79</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -36,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,17 +44,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thick">
+        <color rgb="00FF0000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0000FF00"/>
+          <bgColor rgb="0000FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -416,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,90 +444,95 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Final Rank</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Rank 1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Rank 2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Rank 3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Rank 4</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Rank 5</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Rank 6</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Rank 7</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Rank 8</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Rank 9</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Rank 10</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Rank 11</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Rank 12</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Rank 13</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Rank 14</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Rank 15</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Rank 16</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Rank 17</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Rank 18</t>
         </is>
@@ -526,20 +548,24 @@
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>0.857</v>
+      <c r="C3" t="n">
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.135</v>
+        <v>0.677</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.007</v>
+        <v>0.267</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+        <v>0.044</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -552,6 +578,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -562,43 +589,45 @@
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>0.02</v>
+      <c r="C4" t="n">
+        <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.324</v>
+        <v>0.292</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.347</v>
+        <v>0.514</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.206</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.021</v>
+        <v>0.039</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.025</v>
+        <v>0.034</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>0.01</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>0.001</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" s="1" t="n">
         <v>0.001</v>
@@ -606,1001 +635,1042 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q5" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0.005</v>
+      </c>
       <c r="E6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.082</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.117</v>
+        <v>0.514</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.469</v>
+        <v>0.347</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.177</v>
+        <v>0.045</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.104</v>
+        <v>0.005</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.046</v>
+        <v>0.001</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.9999999999999999</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="E7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <v>0.188</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="H7" s="1" t="n">
+      <c r="K7" s="1" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <v>0.023</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="J7" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="M7" s="1" t="n">
+      <c r="P7" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="R7" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="N7" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>0.9990000000000001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="F8" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="M8" s="1" t="n">
         <v>0.019</v>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>0.058</v>
-      </c>
       <c r="N8" s="1" t="n">
-        <v>0.046</v>
+        <v>0.034</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.036</v>
+        <v>0.017</v>
       </c>
       <c r="P8" s="1" t="n">
         <v>0.026</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="T8" s="1" t="n">
         <v>0.004</v>
       </c>
+      <c r="U8" s="1" t="n">
+        <v>0.006</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>0.999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="T9" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>0.002</v>
+      <c r="U9" s="1" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>0.9920000000000001</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" s="1" t="n">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.074</v>
+        <v>0.068</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.08</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.125</v>
+        <v>0.117</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.138</v>
+        <v>0.1</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.131</v>
+        <v>0.105</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.129</v>
+        <v>0.101</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.105</v>
+        <v>0.094</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.043</v>
+        <v>0.067</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.022</v>
+        <v>0.066</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
+        <v>0.034</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>0.007</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>0.9880000000000001</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>9</v>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.017</v>
+        <v>0.006</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.038</v>
+        <v>0.022</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.066</v>
+        <v>0.054</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.12</v>
+        <v>0.113</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.145</v>
+        <v>0.115</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.121</v>
+        <v>0.112</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.109</v>
+        <v>0.117</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.108</v>
       </c>
       <c r="Q11" s="1" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="R11" s="1" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="R11" s="1" t="n">
-        <v>0.046</v>
-      </c>
       <c r="S11" s="1" t="n">
-        <v>0.031</v>
+        <v>0.044</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9850000000000001</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>0.149</v>
-      </c>
+        <v>0.9880000000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" s="1" t="n">
-        <v>0.143</v>
+        <v>0.001</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.109</v>
+        <v>0.008</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.095</v>
+        <v>0.022</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.077</v>
+        <v>0.035</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.068</v>
+        <v>0.067</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.066</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.054</v>
+        <v>0.131</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.042</v>
+        <v>0.133</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.057</v>
+        <v>0.144</v>
       </c>
       <c r="Q12" s="1" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="T12" s="1" t="n">
         <v>0.037</v>
       </c>
-      <c r="R12" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.01</v>
+      <c r="U12" s="1" t="n">
+        <v>0.023</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.971</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>0.9750000000000001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>11</v>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>0.095</v>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" s="1" t="n">
-        <v>0.146</v>
+        <v>0.005</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.154</v>
+        <v>0.024</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.162</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.118</v>
+        <v>0.129</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.061</v>
+        <v>0.13</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.056</v>
+        <v>0.129</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.033</v>
+        <v>0.102</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.024</v>
+        <v>0.082</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.023</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.02</v>
+        <v>0.064</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.03</v>
+        <v>0.057</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.025</v>
+        <v>0.046</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.015</v>
+        <v>0.042</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>0.022</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9680000000000001</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>0.9710000000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="T14" s="1" t="n">
         <v>0.035</v>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="L14" s="1" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="N14" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.022</v>
+      <c r="U14" s="1" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.961</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>0.9650000000000002</v>
+      </c>
+      <c r="C15" t="n">
+        <v>13</v>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="I15" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>0.004</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>0.024</v>
+      </c>
       <c r="K15" s="1" t="n">
-        <v>0.003</v>
+        <v>0.06</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.036</v>
+        <v>0.105</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.067</v>
+        <v>0.108</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.178</v>
+        <v>0.116</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.184</v>
+        <v>0.112</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.178</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.132</v>
+        <v>0.073</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.05</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>0.039</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.904</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>0.9650000000000001</v>
+      </c>
+      <c r="C16" t="n">
+        <v>14</v>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H16" s="1" t="n">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="I16" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="L16" s="1" t="n">
-        <v>0.049</v>
-      </c>
       <c r="M16" s="1" t="n">
-        <v>0.076</v>
+        <v>0.016</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.105</v>
+        <v>0.028</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.118</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.135</v>
+        <v>0.11</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.107</v>
+        <v>0.162</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.109</v>
+        <v>0.201</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.194</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.048</v>
+        <v>0.114</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.874</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>0.9450000000000001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>15</v>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="G17" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.007</v>
+        <v>0.034</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.015</v>
+        <v>0.081</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.019</v>
+        <v>0.109</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.053</v>
+        <v>0.12</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.075</v>
+        <v>0.096</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.105</v>
+        <v>0.076</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.139</v>
+        <v>0.08</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.125</v>
+        <v>0.064</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.12</v>
+        <v>0.058</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.095</v>
+        <v>0.064</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.063</v>
+        <v>0.049</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.055</v>
+        <v>0.061</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mihmbox</t>
+          <t>sl1dbygad</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>0.6930000000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>16</v>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" s="1" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.029</v>
+        <v>0.019</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.024</v>
+        <v>0.039</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.034</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.044</v>
+        <v>0.097</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.055</v>
+        <v>0.122</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.081</v>
+        <v>0.101</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.061</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.104</v>
+        <v>0.066</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.083</v>
+        <v>0.03</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.091</v>
+        <v>0.019</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.075</v>
+        <v>0.007</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>0.021</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
+          <t>Mihmbox</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.6950000000000001</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>0.607</v>
+      </c>
+      <c r="C19" t="n">
+        <v>17</v>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>0.015</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" s="1" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>0.052</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" s="1" t="n">
-        <v>0.099</v>
+        <v>0.004</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.123</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0.092</v>
+        <v>0.016</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.065</v>
+        <v>0.023</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.025</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.019</v>
+        <v>0.057</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.023</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.025</v>
+        <v>0.103</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.029</v>
+        <v>0.103</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Niko</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M20" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N20" s="1" t="n">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ksuhony</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="3" t="n">
         <v>0.003</v>
       </c>
-      <c r="O20" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="R20" s="1" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>0.206</v>
+      <c r="O20" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>0.179</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>0.326</v>
+      </c>
+      <c r="C21" t="n">
+        <v>19</v>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J21" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="M21" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="N21" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>0.026</v>
-      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" s="1" t="n">
-        <v>0.039</v>
+        <v>0.001</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.065</v>
+        <v>0.018</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.037</v>
       </c>
       <c r="T21" s="1" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="U21" s="1" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Комарик</t>
+          <t>Amaney</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>0.305</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J22" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K22" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="M22" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O22" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="N22" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="O22" s="1" t="n">
+      <c r="P22" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="R22" s="1" t="n">
         <v>0.039</v>
       </c>
-      <c r="P22" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="R22" s="1" t="n">
-        <v>0.038</v>
-      </c>
       <c r="S22" s="1" t="n">
-        <v>0.034</v>
+        <v>0.047</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.038</v>
+        <v>0.079</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>0.098</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>0.138</v>
+      </c>
+      <c r="C23" t="n">
+        <v>21</v>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -1612,23 +1682,22 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.017</v>
+        <v>0.008</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.042</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>0.059</v>
       </c>
     </row>
     <row r="24">
@@ -1638,9 +1707,11 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
+        <v>0.055</v>
+      </c>
+      <c r="C24" t="n">
+        <v>22</v>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
@@ -1653,32 +1724,33 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" s="1" t="n">
-        <v>0.034</v>
+        <v>0.001</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.036</v>
+        <v>0.008</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.061</v>
+        <v>0.015</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>0.031</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>0.049</v>
+      </c>
+      <c r="C25" t="n">
+        <v>23</v>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
@@ -1691,34 +1763,39 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="R25" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="S25" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="S25" s="1" t="n">
-        <v>0.027</v>
-      </c>
       <c r="T25" s="1" t="n">
-        <v>0.045</v>
+        <v>0.008</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>0.023</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
+        <v>0.031</v>
+      </c>
+      <c r="C26" t="n">
+        <v>24</v>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
@@ -1731,32 +1808,35 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R26" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="R26" s="1" t="n">
-        <v>0.007</v>
-      </c>
       <c r="S26" s="1" t="n">
-        <v>0.019</v>
+        <v>0.003</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.036</v>
+        <v>0.004</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Добряк</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.05400000000000001</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>0.022</v>
+      </c>
+      <c r="C27" t="n">
+        <v>25</v>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
@@ -1769,20 +1849,21 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" s="1" t="n">
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R27" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="Q27" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R27" s="1" t="n">
-        <v>0.004</v>
-      </c>
       <c r="S27" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="U27" s="1" t="n">
         <v>0.01</v>
-      </c>
-      <c r="T27" s="1" t="n">
-        <v>0.033</v>
       </c>
     </row>
     <row r="28">
@@ -1792,9 +1873,11 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
+        <v>0.016</v>
+      </c>
+      <c r="C28" t="n">
+        <v>26</v>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
@@ -1811,22 +1894,27 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="T28" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="T28" s="1" t="n">
-        <v>0.007</v>
+      <c r="U28" s="1" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>Абеляр</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
+        <v>0.008</v>
+      </c>
+      <c r="C29" t="n">
+        <v>27</v>
+      </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
@@ -1841,24 +1929,29 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
+        <v>0.001</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
+        <v>0.007</v>
+      </c>
+      <c r="C30" t="n">
+        <v>28</v>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
@@ -1873,24 +1966,27 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>0.004</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>0.005</v>
+      </c>
+      <c r="C31" t="n">
+        <v>29</v>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -1910,15 +2006,22 @@
       <c r="T31" s="1" t="n">
         <v>0.001</v>
       </c>
+      <c r="U31" s="1" t="n">
+        <v>0.004</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+          <t>maria_merlot</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="C32" t="n">
+        <v>30</v>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -1933,18 +2036,27 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
+      <c r="U32" s="1" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+          <t>Пиковая Дама</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>31</v>
+      </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
@@ -1962,15 +2074,20 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
+      <c r="U33" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>32</v>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
@@ -1988,6 +2105,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1996,7 +2114,9 @@
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>33</v>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
@@ -2014,15 +2134,18 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>34</v>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -2040,15 +2163,18 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="n">
+        <v>35</v>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -2066,15 +2192,18 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dama_pica</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>36</v>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -2092,15 +2221,18 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>dama_pica</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="n">
+        <v>37</v>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -2118,15 +2250,18 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="n">
+        <v>38</v>
+      </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -2144,15 +2279,18 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Gluckspilz8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="n">
+        <v>39</v>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -2170,15 +2308,18 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="n">
+        <v>40</v>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -2196,15 +2337,18 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>41</v>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -2222,15 +2366,18 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="n">
+        <v>42</v>
+      </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
@@ -2248,15 +2395,18 @@
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="n">
+        <v>43</v>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -2274,15 +2424,18 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>44</v>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
@@ -2300,15 +2453,18 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="n">
+        <v>45</v>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -2326,15 +2482,18 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>46</v>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
@@ -2352,15 +2511,18 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Staryii</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="n">
+        <v>47</v>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -2378,15 +2540,18 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Кесадилия</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>48</v>
+      </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
@@ -2404,15 +2569,18 @@
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gluckspilz8</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>49</v>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
@@ -2430,15 +2598,18 @@
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>finch79</t>
+          <t>Кесадилия</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>50</v>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
@@ -2456,9 +2627,10 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:T52">
+  <conditionalFormatting sqref="B2:B52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2470,6 +2642,23 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D2:U52">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00FF0000"/>
+        <color rgb="00FFFF00"/>
+        <color rgb="0000FF00"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C52">
+    <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="0">
+      <formula>18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -552,19 +552,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.677</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.267</v>
+        <v>0.263</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -593,45 +593,41 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.292</v>
+        <v>0.287</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.514</v>
+        <v>0.515</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.039</v>
+        <v>0.041</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>0.026</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="M4" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="N4" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -650,51 +646,51 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>0.026</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.033</v>
-      </c>
       <c r="K5" s="1" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" s="1" t="n">
+      <c r="R5" s="1" t="n">
         <v>0.001</v>
       </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
     </row>
@@ -711,29 +707,25 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0.082</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.514</v>
+        <v>0.502</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.347</v>
+        <v>0.356</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.045</v>
+        <v>0.052</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.006</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -748,7 +740,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -758,114 +750,114 @@
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" s="1" t="n">
+        <v>0.012</v>
+      </c>
       <c r="F7" s="1" t="n">
-        <v>0.006</v>
+        <v>0.062</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.062</v>
+        <v>0.259</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.181</v>
+        <v>0.373</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.322</v>
+        <v>0.09</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.188</v>
+        <v>0.031</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.107</v>
+        <v>0.013</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.043</v>
+        <v>0.015</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.035</v>
+        <v>0.021</v>
       </c>
       <c r="N7" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>0.023</v>
       </c>
-      <c r="O7" s="1" t="n">
-        <v>0.017</v>
-      </c>
       <c r="P7" s="1" t="n">
-        <v>0.008</v>
+        <v>0.031</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.003</v>
+        <v>0.02</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+        <v>0.012</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.9990000000000001</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" s="1" t="n">
-        <v>0.05</v>
+        <v>0.004</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.256</v>
+        <v>0.049</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.401</v>
+        <v>0.215</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.104</v>
+        <v>0.32</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.018</v>
+        <v>0.175</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.011</v>
+        <v>0.099</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.008</v>
+        <v>0.068</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.019</v>
+        <v>0.036</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.034</v>
+        <v>0.021</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.026</v>
+        <v>0.002</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>0.017</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="U8" s="1" t="n">
-        <v>0.006</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -874,57 +866,55 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" s="1" t="n">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.121</v>
+        <v>0.098</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.229</v>
+        <v>0.263</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.254</v>
+        <v>0.228</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.119</v>
+        <v>0.115</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.08</v>
+        <v>0.065</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.027</v>
+        <v>0.038</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.022</v>
+        <v>0.026</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="U9" s="1" t="n">
         <v>0.001</v>
@@ -933,7 +923,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -945,60 +935,56 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" s="1" t="n">
-        <v>0.068</v>
+        <v>0.002</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.117</v>
+        <v>0.036</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.1</v>
+        <v>0.062</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>0.105</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.101</v>
+        <v>0.12</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.094</v>
+        <v>0.154</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.077</v>
+        <v>0.143</v>
       </c>
       <c r="Q10" s="1" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="S10" s="1" t="n">
         <v>0.067</v>
       </c>
-      <c r="R10" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>0.034</v>
-      </c>
       <c r="T10" s="1" t="n">
-        <v>0.034</v>
+        <v>0.041</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.007</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.9880000000000001</v>
+        <v>0.9890000000000001</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
@@ -1007,59 +993,59 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" s="1" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.006</v>
+        <v>0.026</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.022</v>
+        <v>0.06</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.054</v>
+        <v>0.109</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.1</v>
+        <v>0.117</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.113</v>
+        <v>0.119</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.115</v>
+        <v>0.099</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.112</v>
+        <v>0.092</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.117</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.108</v>
+        <v>0.061</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.058</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.044</v>
+        <v>0.035</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9880000000000001</v>
+        <v>0.988</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1067,58 +1053,60 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="H12" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.008</v>
+        <v>0.022</v>
       </c>
       <c r="J12" s="1" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="U12" s="1" t="n">
         <v>0.022</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0.023</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9750000000000001</v>
+        <v>0.9820000000000001</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1126,58 +1114,60 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" s="1" t="n">
+        <v>0.005</v>
+      </c>
       <c r="H13" s="1" t="n">
-        <v>0.005</v>
+        <v>0.021</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.024</v>
+        <v>0.063</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.129</v>
+        <v>0.14</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.13</v>
+        <v>0.098</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.129</v>
+        <v>0.096</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.082</v>
+        <v>0.089</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.064</v>
+        <v>0.057</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.057</v>
+        <v>0.042</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.046</v>
+        <v>0.04</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.042</v>
+        <v>0.022</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9710000000000001</v>
+        <v>0.9820000000000001</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1186,59 +1176,59 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.019</v>
+        <v>0.006</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.076</v>
+        <v>0.026</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.092</v>
+        <v>0.064</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.115</v>
+        <v>0.11</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.106</v>
+        <v>0.119</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.11</v>
+        <v>0.143</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.092</v>
+        <v>0.104</v>
       </c>
       <c r="O14" s="1" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="P14" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="P14" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="Q14" s="1" t="n">
-        <v>0.061</v>
+        <v>0.067</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.052</v>
+        <v>0.078</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.043</v>
+        <v>0.051</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.035</v>
+        <v>0.038</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9650000000000002</v>
+        <v>0.9590000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1247,57 +1237,49 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="1" t="n">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="I15" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J15" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="K15" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L15" s="1" t="n">
-        <v>0.09</v>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" s="1" t="n">
-        <v>0.105</v>
+        <v>0.014</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.108</v>
+        <v>0.029</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.11</v>
+        <v>0.054</v>
       </c>
       <c r="P15" s="1" t="n">
         <v>0.116</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.112</v>
+        <v>0.161</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.196</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.073</v>
+        <v>0.2</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.05</v>
+        <v>0.131</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.039</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9650000000000001</v>
+        <v>0.9540000000000001</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1307,38 +1289,44 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>0.065</v>
+      </c>
       <c r="L16" s="1" t="n">
-        <v>0.008</v>
+        <v>0.081</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.016</v>
+        <v>0.1</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.028</v>
+        <v>0.101</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.11</v>
+        <v>0.106</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.162</v>
+        <v>0.099</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.201</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.194</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.114</v>
+        <v>0.056</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.061</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="17">
@@ -1355,50 +1343,46 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" s="1" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.034</v>
+        <v>0.04</v>
       </c>
       <c r="J17" s="1" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="N17" s="1" t="n">
         <v>0.081</v>
       </c>
-      <c r="K17" s="1" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="L17" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>0.076</v>
-      </c>
       <c r="O17" s="1" t="n">
-        <v>0.08</v>
+        <v>0.062</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="Q17" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="S17" s="1" t="n">
         <v>0.058</v>
       </c>
-      <c r="R17" s="1" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="S17" s="1" t="n">
-        <v>0.049</v>
-      </c>
       <c r="T17" s="1" t="n">
-        <v>0.061</v>
+        <v>0.067</v>
       </c>
       <c r="U17" s="1" t="n">
         <v>0.04</v>
@@ -1411,7 +1395,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.6930000000000001</v>
+        <v>0.678</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1420,47 +1404,45 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>0.097</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.122</v>
+        <v>0.12</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.101</v>
+        <v>0.102</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.066</v>
+        <v>0.054</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.03</v>
+        <v>0.046</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="19">
@@ -1470,7 +1452,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.607</v>
+        <v>0.629</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1479,45 +1461,45 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" s="1" t="n">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.025</v>
+        <v>0.034</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.036</v>
+        <v>0.048</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.073</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.103</v>
+        <v>0.09</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.103</v>
+        <v>0.104</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="20">
@@ -1527,7 +1509,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.591</v>
+        <v>0.6080000000000001</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1542,29 +1524,27 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="3" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="n">
         <v>0.002</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.031</v>
+        <v>0.025</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.126</v>
+        <v>0.131</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.179</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="21">
@@ -1574,7 +1554,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.326</v>
+        <v>0.319</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1595,19 +1575,19 @@
         <v>0.001</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="R21" s="1" t="n">
         <v>0.018</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.099</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.18</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="22">
@@ -1617,7 +1597,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.305</v>
+        <v>0.306</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1630,43 +1610,43 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="N22" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.019</v>
+        <v>0.025</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.039</v>
+        <v>0.044</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.047</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.079</v>
+        <v>0.058</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.098</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>Комарик</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.138</v>
+        <v>0.252</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1677,37 +1657,51 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="J23" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>0.028</v>
+      </c>
       <c r="Q23" s="1" t="n">
-        <v>0.003</v>
+        <v>0.023</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.008</v>
+        <v>0.03</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.026</v>
+        <v>0.043</v>
       </c>
       <c r="T23" s="1" t="n">
         <v>0.042</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.059</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.055</v>
+        <v>0.125</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1725,18 +1719,20 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" s="1" t="n">
+        <v>0.005</v>
+      </c>
       <c r="R24" s="1" t="n">
-        <v>0.001</v>
+        <v>0.011</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.008</v>
+        <v>0.021</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.015</v>
+        <v>0.034</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.031</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="25">
@@ -1746,7 +1742,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.049</v>
+        <v>0.054</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1762,36 +1758,28 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P25" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="R25" s="1" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.008</v>
+        <v>0.022</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.023</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.031</v>
+        <v>0.052</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1809,30 +1797,28 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.004</v>
+        <v>0.012</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.02</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Добряк</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1850,30 +1836,26 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" s="1" t="n">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="R27" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="S27" s="1" t="n">
-        <v>0.002</v>
-      </c>
       <c r="T27" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>Добряк</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -1892,25 +1874,27 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S28" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="C29" t="n">
         <v>27</v>
@@ -1937,13 +1921,13 @@
         <v>0.004</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1967,9 +1951,11 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+      <c r="S30" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T30" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="U30" s="1" t="n">
         <v>0.004</v>
@@ -1978,11 +1964,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="C31" t="n">
         <v>29</v>
@@ -2002,22 +1988,22 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="S31" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="C32" t="n">
         <v>30</v>
@@ -2036,11 +2022,13 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="U32" s="1" t="n">
         <v>0.002</v>
       </c>
@@ -2048,11 +2036,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="C33" t="n">
         <v>31</v>
@@ -2071,7 +2059,9 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="R33" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" s="1" t="n">
@@ -2081,10 +2071,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>Vitos2049</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="C34" t="n">
         <v>32</v>
       </c>
@@ -2105,15 +2097,19 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" s="1" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>Абеляр</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="C35" t="n">
         <v>33</v>
       </c>
@@ -2132,17 +2128,21 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+      <c r="S35" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>dama_pica</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="C36" t="n">
         <v>34</v>
       </c>
@@ -2163,15 +2163,19 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>Кальян</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="C37" t="n">
         <v>35</v>
       </c>
@@ -2192,12 +2196,14 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2226,7 +2232,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dama_pica</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2255,7 +2261,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2284,7 +2290,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gluckspilz8</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2313,7 +2319,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2342,7 +2348,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2371,7 +2377,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2400,7 +2406,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>KidPoker</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2458,7 +2464,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2487,7 +2493,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2516,7 +2522,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2545,7 +2551,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2574,7 +2580,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>Андрюха Пират</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:V52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,11 @@
           <t>Rank 18</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Rank 19</t>
+        </is>
+      </c>
     </row>
     <row r="2"/>
     <row r="3">
@@ -552,20 +557,18 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.263</v>
+        <v>0.265</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -579,6 +582,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -593,37 +597,39 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.287</v>
+        <v>0.28</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.515</v>
+        <v>0.52</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.066</v>
+        <v>0.075</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.041</v>
+        <v>0.033</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.035</v>
+        <v>0.038</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="P4" s="1" t="n">
         <v>0.001</v>
       </c>
@@ -632,6 +638,7 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -646,53 +653,54 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.323</v>
+        <v>0.314</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.248</v>
+        <v>0.269</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.153</v>
+        <v>0.13</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.038</v>
+        <v>0.05</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.026</v>
+        <v>0.033</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="M5" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P5" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="N5" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>0.006</v>
-      </c>
       <c r="Q5" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
+        <v>0.001</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -707,7 +715,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0.082</v>
@@ -716,10 +724,10 @@
         <v>0.502</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.052</v>
+        <v>0.045</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>0.006</v>
@@ -736,11 +744,12 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -750,66 +759,59 @@
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" s="1" t="n">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>0.062</v>
-      </c>
       <c r="G7" s="1" t="n">
-        <v>0.259</v>
+        <v>0.047</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.373</v>
+        <v>0.193</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.09</v>
+        <v>0.325</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.031</v>
+        <v>0.197</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.013</v>
+        <v>0.095</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.015</v>
+        <v>0.048</v>
       </c>
       <c r="M7" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <v>0.021</v>
       </c>
-      <c r="N7" s="1" t="n">
-        <v>0.019</v>
-      </c>
       <c r="O7" s="1" t="n">
-        <v>0.023</v>
+        <v>0.008</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.031</v>
+        <v>0.004</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="U7" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
@@ -817,117 +819,133 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.049</v>
+        <v>0.022</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.215</v>
+        <v>0.097</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.32</v>
+        <v>0.257</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.175</v>
+        <v>0.243</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.099</v>
+        <v>0.116</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.068</v>
+        <v>0.065</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.036</v>
+        <v>0.046</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.021</v>
+        <v>0.034</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.007</v>
+        <v>0.044</v>
       </c>
       <c r="P8" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="Q8" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="V8" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.056</v>
+      </c>
       <c r="G9" s="1" t="n">
-        <v>0.021</v>
+        <v>0.254</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.098</v>
+        <v>0.415</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.263</v>
+        <v>0.077</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.228</v>
+        <v>0.024</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.115</v>
+        <v>0.016</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.065</v>
+        <v>0.011</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.045</v>
+        <v>0.019</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.026</v>
+        <v>0.017</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.021</v>
+        <v>0.015</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="T9" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="U9" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="V9" s="1" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.9920000000000001</v>
+        <v>0.9940000000000001</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
@@ -935,56 +953,63 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.029</v>
+      </c>
       <c r="I10" s="1" t="n">
-        <v>0.002</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.021</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.036</v>
+        <v>0.101</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.062</v>
+        <v>0.112</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.12</v>
+        <v>0.099</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.154</v>
+        <v>0.111</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.143</v>
+        <v>0.078</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.127</v>
+        <v>0.068</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.093</v>
+        <v>0.046</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.067</v>
+        <v>0.043</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.041</v>
+        <v>0.024</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.021</v>
+        <v>0.013</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>0.006</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.9890000000000001</v>
+        <v>0.9920000000000001</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
@@ -993,59 +1018,62 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" s="1" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.026</v>
+        <v>0.008</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.06</v>
+        <v>0.032</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.109</v>
+        <v>0.077</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.117</v>
+        <v>0.133</v>
       </c>
       <c r="L11" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="M11" s="1" t="n">
         <v>0.119</v>
       </c>
-      <c r="M11" s="1" t="n">
-        <v>0.099</v>
-      </c>
       <c r="N11" s="1" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.061</v>
+        <v>0.075</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.075</v>
+        <v>0.066</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.058</v>
+        <v>0.051</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.035</v>
+        <v>0.062</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.027</v>
+        <v>0.039</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.018</v>
+        <v>0.025</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.988</v>
+        <v>0.9920000000000001</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1053,60 +1081,61 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="I12" s="1" t="n">
-        <v>0.022</v>
-      </c>
       <c r="J12" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.016</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.09</v>
+        <v>0.042</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.137</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.104</v>
+        <v>0.074</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.133</v>
+        <v>0.11</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.095</v>
+        <v>0.129</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.094</v>
+        <v>0.126</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.092</v>
+        <v>0.143</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.061</v>
+        <v>0.118</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.034</v>
+        <v>0.073</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.028</v>
+        <v>0.046</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.022</v>
+        <v>0.03</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>0.008</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9820000000000001</v>
+        <v>0.992</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1114,60 +1143,61 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" s="1" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" s="1" t="n">
-        <v>0.021</v>
+        <v>0.004</v>
       </c>
       <c r="I13" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R13" s="1" t="n">
         <v>0.063</v>
       </c>
-      <c r="J13" s="1" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0.042</v>
-      </c>
       <c r="S13" s="1" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.022</v>
+        <v>0.028</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.023</v>
+        <v>0.013</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>0.006</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9820000000000001</v>
+        <v>0.9890000000000001</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1176,49 +1206,52 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.026</v>
+        <v>0.064</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.064</v>
+        <v>0.115</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.119</v>
+        <v>0.14</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.143</v>
+        <v>0.095</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.104</v>
+        <v>0.092</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.081</v>
+        <v>0.073</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.077</v>
+        <v>0.06</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.067</v>
+        <v>0.06</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.078</v>
+        <v>0.042</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.051</v>
+        <v>0.04</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.038</v>
+        <v>0.031</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="15">
@@ -1228,7 +1261,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9590000000000001</v>
+        <v>0.9830000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1240,36 +1273,39 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="M15" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.116</v>
+        <v>0.12</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.161</v>
+        <v>0.14</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.196</v>
+        <v>0.229</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.2</v>
+        <v>0.181</v>
       </c>
       <c r="T15" s="1" t="n">
         <v>0.131</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.056</v>
+        <v>0.048</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="16">
@@ -1279,7 +1315,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9540000000000001</v>
+        <v>0.9800000000000002</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1287,46 +1323,53 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="I16" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.065</v>
+        <v>0.059</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.081</v>
+        <v>0.09</v>
       </c>
       <c r="M16" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="P16" s="1" t="n">
         <v>0.1</v>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>0.106</v>
       </c>
       <c r="Q16" s="1" t="n">
         <v>0.099</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="17">
@@ -1336,7 +1379,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9450000000000001</v>
+        <v>0.9680000000000001</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1344,58 +1387,63 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="H17" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.04</v>
+        <v>0.026</v>
       </c>
       <c r="J17" s="1" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="S17" s="1" t="n">
         <v>0.065</v>
       </c>
-      <c r="K17" s="1" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="L17" s="1" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="O17" s="1" t="n">
+      <c r="T17" s="1" t="n">
         <v>0.062</v>
       </c>
-      <c r="P17" s="1" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="S17" s="1" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="T17" s="1" t="n">
-        <v>0.067</v>
-      </c>
       <c r="U17" s="1" t="n">
-        <v>0.04</v>
+        <v>0.043</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>0.028</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.678</v>
+        <v>0.7550000000000001</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1405,44 +1453,39 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L18" s="1" t="n">
-        <v>0.07099999999999999</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" s="1" t="n">
-        <v>0.097</v>
+        <v>0.001</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.12</v>
+        <v>0.001</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.102</v>
+        <v>0.002</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.054</v>
+        <v>0.026</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.046</v>
+        <v>0.064</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.017</v>
+        <v>0.113</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.012</v>
+        <v>0.171</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.017</v>
+        <v>0.198</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>0.169</v>
       </c>
     </row>
     <row r="19">
@@ -1452,7 +1495,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.629</v>
+        <v>0.716</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1469,125 +1512,144 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.048</v>
+        <v>0.036</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.058</v>
+        <v>0.052</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.078</v>
+        <v>0.068</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.09</v>
+        <v>0.097</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.104</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="U19" s="1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V19" s="1" t="n">
         <v>0.089</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ksuhony</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>0.6080000000000001</v>
-      </c>
-      <c r="C20" s="2" t="n">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sl1dbygad</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>0.6990000000000001</v>
+      </c>
+      <c r="C20" t="n">
         <v>18</v>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>0.198</v>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Niko</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="C21" t="n">
+      <c r="B21" s="3" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="C21" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="R21" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="S21" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="T21" s="1" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="U21" s="1" t="n">
-        <v>0.161</v>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>0.206</v>
       </c>
     </row>
     <row r="22">
@@ -1597,7 +1659,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.306</v>
+        <v>0.3730000000000001</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1609,34 +1671,39 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="K22" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="P22" s="1" t="n">
         <v>0.012</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.025</v>
+        <v>0.033</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.044</v>
+        <v>0.034</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.058</v>
+        <v>0.075</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.082</v>
+        <v>0.075</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="23">
@@ -1646,7 +1713,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.252</v>
+        <v>0.31</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1656,42 +1723,43 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="I23" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="L23" s="1" t="n">
         <v>0.002</v>
       </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>0.021</v>
+        <v>0.013</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>0.028</v>
+        <v>0.023</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.023</v>
+        <v>0.029</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.03</v>
+        <v>0.051</v>
       </c>
       <c r="S23" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="U23" s="1" t="n">
         <v>0.043</v>
       </c>
-      <c r="T23" s="1" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <v>0.048</v>
+      <c r="V23" s="1" t="n">
+        <v>0.026</v>
       </c>
     </row>
     <row r="24">
@@ -1701,7 +1769,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.125</v>
+        <v>0.203</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1718,31 +1786,36 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q24" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.054</v>
+        <v>0.063</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>0.083</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.054</v>
+        <v>0.11</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1760,26 +1833,33 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="Q25" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="S25" s="1" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.022</v>
+        <v>0.014</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.029</v>
+        <v>0.033</v>
+      </c>
+      <c r="V25" s="1" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.052</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1796,29 +1876,34 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.034</v>
+        <v>0.026</v>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>0.043</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.019</v>
+        <v>0.048</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1837,25 +1922,30 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S27" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Добряк</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.018</v>
+        <v>0.046</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -1874,27 +1964,26 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S28" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>0.027</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Добряк</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.017</v>
+        <v>0.035</v>
       </c>
       <c r="C29" t="n">
         <v>27</v>
@@ -1913,25 +2002,30 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S29" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
+      </c>
+      <c r="V29" s="1" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.007</v>
+        <v>0.023</v>
       </c>
       <c r="C30" t="n">
         <v>28</v>
@@ -1952,13 +2046,16 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="T30" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="U30" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="U30" s="1" t="n">
-        <v>0.004</v>
+      <c r="V30" s="1" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="31">
@@ -1968,7 +2065,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
       <c r="C31" t="n">
         <v>29</v>
@@ -1989,21 +2086,26 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="T31" t="inlineStr"/>
+        <v>0.001</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="U31" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
+      </c>
+      <c r="V31" s="1" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="C32" t="n">
         <v>30</v>
@@ -2024,23 +2126,26 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
+      </c>
+      <c r="V32" s="1" t="n">
+        <v>0.003</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bogdansskii</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="C33" t="n">
         <v>31</v>
@@ -2059,23 +2164,24 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" s="1" t="n">
         <v>0.001</v>
       </c>
+      <c r="V33" s="1" t="n">
+        <v>0.004</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="C34" t="n">
         <v>32</v>
@@ -2100,15 +2206,18 @@
       <c r="U34" s="1" t="n">
         <v>0.002</v>
       </c>
+      <c r="V34" s="1" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="C35" t="n">
         <v>33</v>
@@ -2128,20 +2237,23 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+      <c r="U35" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V35" s="1" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dama_pica</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="C36" t="n">
         <v>34</v>
@@ -2163,18 +2275,19 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" s="1" t="n">
-        <v>0.001</v>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" s="1" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="C37" t="n">
         <v>35</v>
@@ -2196,14 +2309,15 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" s="1" t="n">
-        <v>0.001</v>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" s="1" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2228,11 +2342,12 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2257,11 +2372,12 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2286,11 +2402,12 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2315,11 +2432,12 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2344,11 +2462,12 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2373,11 +2492,12 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2402,11 +2522,12 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KidPoker</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2431,11 +2552,12 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2460,11 +2582,12 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2489,11 +2612,12 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2518,11 +2642,12 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>hachatur</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2547,11 +2672,12 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2576,11 +2702,12 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Андрюха Пират</t>
+          <t>stepblv</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2605,6 +2732,7 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2634,6 +2762,7 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B52">
@@ -2648,7 +2777,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:U52">
+  <conditionalFormatting sqref="D2:V52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2662,7 +2791,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C52">
     <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="0">
-      <formula>18</formula>
+      <formula>19</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -433,8 +433,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -557,18 +560,20 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.757</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.265</v>
+        <v>0.225</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.04</v>
+        <v>0.012</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -597,42 +602,40 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.28</v>
+        <v>0.242</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.075</v>
+        <v>0.036</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.033</v>
+        <v>0.025</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.027</v>
+        <v>0.013</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="N4" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
@@ -643,7 +646,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -652,52 +655,36 @@
       <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>0.025</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>0.127</v>
+        <v>0.062</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.314</v>
+        <v>0.459</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.269</v>
+        <v>0.416</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.13</v>
+        <v>0.046</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.05</v>
+        <v>0.012</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.033</v>
+        <v>0.003</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="N5" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="O5" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
@@ -705,7 +692,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -715,31 +702,45 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0.082</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.502</v>
+        <v>0.433</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.36</v>
+        <v>0.231</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.045</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I6" s="1" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -749,7 +750,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -761,57 +762,63 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" s="1" t="n">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.047</v>
+        <v>0.106</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.193</v>
+        <v>0.196</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.325</v>
+        <v>0.157</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.197</v>
+        <v>0.157</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.095</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.048</v>
+        <v>0.077</v>
       </c>
       <c r="M7" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <v>0.045</v>
       </c>
-      <c r="N7" s="1" t="n">
-        <v>0.021</v>
-      </c>
       <c r="O7" s="1" t="n">
-        <v>0.008</v>
+        <v>0.026</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="R7" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="T7" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.9990000000000001</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
@@ -819,133 +826,123 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.022</v>
+        <v>0.025</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.097</v>
+        <v>0.121</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.257</v>
+        <v>0.196</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.243</v>
+        <v>0.189</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.116</v>
+        <v>0.165</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.065</v>
+        <v>0.148</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.046</v>
+        <v>0.068</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.044</v>
+        <v>0.025</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.02</v>
+        <v>0.003</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U8" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="V8" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.9989999999999999</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" s="1" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" s="1" t="n">
-        <v>0.056</v>
+        <v>0.001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.254</v>
+        <v>0.008</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.415</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.077</v>
+        <v>0.175</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.024</v>
+        <v>0.171</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.016</v>
+        <v>0.16</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.011</v>
+        <v>0.106</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.019</v>
+        <v>0.067</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.019</v>
+        <v>0.051</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.022</v>
+        <v>0.035</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.017</v>
+        <v>0.033</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.015</v>
+        <v>0.031</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.9940000000000001</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
@@ -954,62 +951,62 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.029</v>
+        <v>0.014</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.101</v>
+        <v>0.109</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.112</v>
+        <v>0.136</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.107</v>
+        <v>0.145</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.099</v>
+        <v>0.153</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.111</v>
+        <v>0.124</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.068</v>
+        <v>0.062</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.046</v>
+        <v>0.036</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.043</v>
+        <v>0.03</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.024</v>
+        <v>0.007</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.9920000000000001</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
@@ -1021,55 +1018,55 @@
         <v>0.001</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
       <c r="K11" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L11" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="L11" s="1" t="n">
-        <v>0.112</v>
-      </c>
       <c r="M11" s="1" t="n">
-        <v>0.119</v>
+        <v>0.142</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.091</v>
+        <v>0.139</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.09</v>
+        <v>0.116</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.075</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="Q11" s="1" t="n">
         <v>0.066</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.051</v>
+        <v>0.043</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.062</v>
+        <v>0.021</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.025</v>
+        <v>0.012</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1082,186 +1079,190 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="1" t="n">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="I12" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>0.016</v>
-      </c>
       <c r="K12" s="1" t="n">
-        <v>0.042</v>
+        <v>0.001</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.074</v>
+        <v>0.026</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.11</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.129</v>
+        <v>0.106</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.126</v>
+        <v>0.155</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.143</v>
+        <v>0.159</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.118</v>
+        <v>0.146</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.073</v>
+        <v>0.122</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.046</v>
+        <v>0.104</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.03</v>
+        <v>0.058</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.008</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.992</v>
+        <v>0.9910000000000001</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="E13" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0.161</v>
+      </c>
       <c r="H13" s="1" t="n">
-        <v>0.004</v>
+        <v>0.325</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.023</v>
+        <v>0.165</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.049</v>
+        <v>0.061</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.101</v>
+        <v>0.026</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.101</v>
+        <v>0.007</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.124</v>
+        <v>0.005</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.116</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.124</v>
+        <v>0.016</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.109</v>
+        <v>0.018</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.09</v>
+        <v>0.021</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.063</v>
+        <v>0.035</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.041</v>
+        <v>0.029</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.028</v>
+        <v>0.043</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.013</v>
+        <v>0.026</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9890000000000001</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="G14" s="1" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.018</v>
+        <v>0.045</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.064</v>
+        <v>0.104</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.115</v>
+        <v>0.13</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.14</v>
+        <v>0.113</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>0.095</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.092</v>
+        <v>0.068</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.073</v>
+        <v>0.036</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.06</v>
+        <v>0.038</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.042</v>
+        <v>0.031</v>
       </c>
       <c r="S14" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="T14" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="T14" s="1" t="n">
-        <v>0.031</v>
-      </c>
       <c r="U14" s="1" t="n">
-        <v>0.015</v>
+        <v>0.043</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.011</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9830000000000001</v>
+        <v>0.9780000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1269,43 +1270,53 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="G15" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>0.12</v>
+      </c>
       <c r="L15" s="1" t="n">
-        <v>0.003</v>
+        <v>0.118</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.015</v>
+        <v>0.111</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.03</v>
+        <v>0.113</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.056</v>
+        <v>0.092</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.12</v>
+        <v>0.078</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.14</v>
+        <v>0.046</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.229</v>
+        <v>0.05</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.181</v>
+        <v>0.035</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.131</v>
+        <v>0.037</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.048</v>
+        <v>0.038</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="16">
@@ -1315,7 +1326,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9800000000000002</v>
+        <v>0.95</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1323,32 +1334,30 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" s="1" t="n">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="I16" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="J16" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="J16" s="1" t="n">
-        <v>0.029</v>
-      </c>
       <c r="K16" s="1" t="n">
-        <v>0.059</v>
+        <v>0.025</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.09</v>
+        <v>0.037</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.112</v>
+        <v>0.097</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.117</v>
+        <v>0.102</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.104</v>
+        <v>0.11</v>
       </c>
       <c r="P16" s="1" t="n">
         <v>0.1</v>
@@ -1357,29 +1366,29 @@
         <v>0.099</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.081</v>
+        <v>0.062</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.075</v>
+        <v>0.091</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.058</v>
+        <v>0.073</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.03</v>
+        <v>0.078</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.016</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9680000000000001</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1387,63 +1396,51 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H17" s="1" t="n">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="I17" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="K17" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="L17" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>0.093</v>
-      </c>
       <c r="N17" s="1" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.037</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.052</v>
+        <v>0.096</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.048</v>
+        <v>0.143</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.065</v>
+        <v>0.173</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.062</v>
+        <v>0.163</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.043</v>
+        <v>0.137</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.028</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.7550000000000001</v>
+        <v>0.926</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1454,48 +1451,52 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="M18" s="1" t="n">
-        <v>0.001</v>
+        <v>0.014</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.001</v>
+        <v>0.029</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.002</v>
+        <v>0.058</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.01</v>
+        <v>0.083</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.026</v>
+        <v>0.11</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.064</v>
+        <v>0.131</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.113</v>
+        <v>0.135</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.171</v>
+        <v>0.146</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.198</v>
+        <v>0.124</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.169</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mihmbox</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.716</v>
+        <v>0.893</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1505,47 +1506,41 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="K19" s="1" t="n">
-        <v>0.012</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N19" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="M19" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="N19" s="1" t="n">
-        <v>0.032</v>
-      </c>
       <c r="O19" s="1" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.052</v>
+        <v>0.058</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.081</v>
+        <v>0.097</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.068</v>
+        <v>0.14</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.097</v>
+        <v>0.143</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.163</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.089</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="20">
@@ -1555,7 +1550,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.6990000000000001</v>
+        <v>0.6110000000000001</v>
       </c>
       <c r="C20" t="n">
         <v>18</v>
@@ -1564,58 +1559,60 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="I20" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.046</v>
+        <v>0.018</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>0.075</v>
+        <v>0.042</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.092</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>0.119</v>
+        <v>0.091</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>0.089</v>
+        <v>0.115</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>0.106</v>
+        <v>0.094</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.062</v>
+        <v>0.076</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.022</v>
+        <v>0.033</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.011</v>
+        <v>0.017</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.017</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.03</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>Mihmbox</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.518</v>
+        <v>0.38</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>19</v>
@@ -1628,28 +1625,38 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="L21" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.012</v>
+      </c>
       <c r="Q21" s="3" t="n">
-        <v>0.006</v>
+        <v>0.021</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.022</v>
+        <v>0.014</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>0.033</v>
+        <v>0.043</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>0.097</v>
+        <v>0.058</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.154</v>
+        <v>0.09</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>0.206</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="22">
@@ -1659,7 +1666,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.3730000000000001</v>
+        <v>0.356</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1671,39 +1678,39 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="N22" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.033</v>
+        <v>0.015</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.034</v>
+        <v>0.04</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.068</v>
+        <v>0.055</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.075</v>
+        <v>0.067</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>0.06</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="23">
@@ -1713,7 +1720,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.31</v>
+        <v>0.3260000000000001</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1722,44 +1729,50 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="I23" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>0.001</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>0.012</v>
+      </c>
       <c r="K23" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>0.018</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>0.015</v>
+      </c>
       <c r="M23" s="1" t="n">
-        <v>0.006</v>
+        <v>0.033</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>0.011</v>
+        <v>0.043</v>
       </c>
       <c r="O23" s="1" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S23" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="P23" s="1" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>0.046</v>
-      </c>
       <c r="T23" s="1" t="n">
-        <v>0.058</v>
+        <v>0.013</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.043</v>
+        <v>0.007</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>0.026</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="24">
@@ -1769,7 +1782,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.203</v>
+        <v>0.215</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1790,22 +1803,22 @@
         <v>0.001</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.03</v>
+        <v>0.019</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.063</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.083</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="25">
@@ -1815,7 +1828,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.11</v>
+        <v>0.187</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1833,33 +1846,31 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.014</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.033</v>
+        <v>0.059</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.05</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1876,34 +1887,30 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" s="1" t="n">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="T26" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="S26" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="T26" s="1" t="n">
-        <v>0.008</v>
-      </c>
       <c r="U26" s="1" t="n">
-        <v>0.026</v>
+        <v>0.011</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.043</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.048</v>
+        <v>0.033</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1922,31 +1929,25 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S27" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U27" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="U27" s="1" t="n">
-        <v>0.013</v>
-      </c>
       <c r="V27" s="1" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Obscur</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>0.046</v>
-      </c>
+          <t>nesmotri_v_shelll1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>26</v>
       </c>
@@ -1966,25 +1967,17 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U28" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="V28" s="1" t="n">
-        <v>0.027</v>
-      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Добряк</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>0.035</v>
-      </c>
+          <t>Тихоня</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>27</v>
       </c>
@@ -2002,21 +1995,11 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S29" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T29" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U29" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V29" s="1" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2024,9 +2007,7 @@
           <t>Викусик</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
-        <v>0.023</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>28</v>
       </c>
@@ -2045,28 +2026,18 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="T30" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U30" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="V30" s="1" t="n">
-        <v>0.016</v>
-      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kirienish</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>0.02</v>
-      </c>
+          <t>Chinaski</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>29</v>
       </c>
@@ -2085,18 +2056,10 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T31" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U31" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="V31" s="1" t="n">
-        <v>0.013</v>
-      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2104,9 +2067,7 @@
           <t>maria_merlot</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>30</v>
       </c>
@@ -2125,647 +2086,13 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T32" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U32" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="V32" s="1" t="n">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Плейбой в карты</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C33" t="n">
-        <v>31</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="V33" s="1" t="n">
-        <v>0.004</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Кальян</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="C34" t="n">
-        <v>32</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="V34" s="1" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Vitos2049</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="C35" t="n">
-        <v>33</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="V35" s="1" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Тихоня</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="C36" t="n">
-        <v>34</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" s="1" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Пиковая Дама</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="C37" t="n">
-        <v>35</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" s="1" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>nesmotri_v_shelll1</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
-        <v>36</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>yankkk</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
-        <v>37</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Никитос</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
-        <v>38</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>EliasPavlov</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
-        <v>39</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Настя дай стек</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
-        <v>40</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Дядя Витя</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
-        <v>41</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>cheremsha</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
-        <v>42</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Al</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="n">
-        <v>43</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Yanchik_250</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="n">
-        <v>44</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Chinaski</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="n">
-        <v>45</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Ромчик</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="n">
-        <v>46</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>hachatur</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="n">
-        <v>47</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Bushido</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="n">
-        <v>48</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>stepblv</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="n">
-        <v>49</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Кесадилия</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="n">
-        <v>50</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B52">
+  <conditionalFormatting sqref="B2:B32">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2777,7 +2104,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:V52">
+  <conditionalFormatting sqref="D2:V32">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2789,7 +2116,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C52">
+  <conditionalFormatting sqref="C3:C32">
     <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="0">
       <formula>19</formula>
     </cfRule>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -560,20 +560,18 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.757</v>
+        <v>0.765</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.225</v>
+        <v>0.226</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="H3" s="1" t="n">
         <v>0.001</v>
       </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -602,34 +600,34 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.242</v>
+        <v>0.234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.025</v>
+        <v>0.034</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="N4" s="1" t="n">
         <v>0.002</v>
@@ -657,26 +655,22 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>0.062</v>
+        <v>0.066</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.459</v>
+        <v>0.447</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.416</v>
+        <v>0.43</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.046</v>
+        <v>0.041</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.016</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -705,41 +699,43 @@
         <v>0.001</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.433</v>
+        <v>0.447</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.231</v>
+        <v>0.222</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.033</v>
+        <v>0.039</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>0.016</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
+        <v>0.004</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="Q6" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
@@ -760,54 +756,56 @@
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="F7" s="1" t="n">
-        <v>0.021</v>
+        <v>0.033</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.106</v>
+        <v>0.092</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.196</v>
+        <v>0.186</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.157</v>
+        <v>0.138</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.157</v>
+        <v>0.126</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.077</v>
+        <v>0.095</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.045</v>
+        <v>0.061</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.026</v>
+        <v>0.035</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="R7" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="V7" t="inlineStr"/>
     </row>
@@ -829,42 +827,44 @@
         <v>0.005</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.025</v>
+        <v>0.031</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.121</v>
+        <v>0.109</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.196</v>
+        <v>0.193</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.189</v>
+        <v>0.203</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.165</v>
+        <v>0.154</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.148</v>
+        <v>0.129</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.068</v>
+        <v>0.081</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.036</v>
+        <v>0.05</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
+        <v>0.001</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -887,52 +887,52 @@
         <v>0.001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.008</v>
+        <v>0.018</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.175</v>
+        <v>0.183</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.171</v>
+        <v>0.18</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.16</v>
+        <v>0.142</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.106</v>
+        <v>0.117</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.051</v>
+        <v>0.036</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.035</v>
+        <v>0.031</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.031</v>
+        <v>0.026</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="10">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
@@ -951,52 +951,52 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.014</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.028</v>
+        <v>0.034</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.068</v>
+        <v>0.074</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.109</v>
+        <v>0.103</v>
       </c>
       <c r="L10" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="N10" s="1" t="n">
         <v>0.136</v>
       </c>
-      <c r="M10" s="1" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>0.153</v>
-      </c>
       <c r="O10" s="1" t="n">
-        <v>0.124</v>
+        <v>0.117</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.076</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.062</v>
+        <v>0.055</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="11">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
@@ -1014,53 +1014,51 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.031</v>
+        <v>0.021</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.079</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.133</v>
+        <v>0.104</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>0.142</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.139</v>
+        <v>0.134</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.066</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.043</v>
+        <v>0.057</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.021</v>
+        <v>0.036</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="12">
@@ -1070,7 +1068,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9920000000000001</v>
+        <v>0.9940000000000001</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1085,40 +1083,40 @@
         <v>0.001</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="M12" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="V12" s="1" t="n">
         <v>0.026</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>0.028</v>
       </c>
     </row>
     <row r="13">
@@ -1128,29 +1126,29 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9910000000000001</v>
+        <v>0.9900000000000001</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.032</v>
+        <v>0.024</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.161</v>
+        <v>0.15</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.325</v>
+        <v>0.329</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.165</v>
+        <v>0.17</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>0.026</v>
@@ -1159,31 +1157,31 @@
         <v>0.007</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.035</v>
+        <v>0.028</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.029</v>
+        <v>0.041</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.043</v>
+        <v>0.034</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="V13" s="1" t="n">
         <v>0.011</v>
@@ -1192,77 +1190,75 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9800000000000001</v>
+        <v>0.9840000000000002</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" s="1" t="n">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="G14" s="1" t="n">
-        <v>0.008</v>
-      </c>
       <c r="H14" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>0.045</v>
       </c>
-      <c r="I14" s="1" t="n">
-        <v>0.104</v>
-      </c>
       <c r="J14" s="1" t="n">
-        <v>0.13</v>
+        <v>0.066</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.123</v>
+        <v>0.109</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.113</v>
+        <v>0.116</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.095</v>
+        <v>0.107</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.068</v>
+        <v>0.098</v>
       </c>
       <c r="O14" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="U14" s="1" t="n">
         <v>0.036</v>
       </c>
-      <c r="P14" s="1" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>0.043</v>
-      </c>
       <c r="V14" s="1" t="n">
-        <v>0.024</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9780000000000001</v>
+        <v>0.9810000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1271,52 +1267,52 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" s="1" t="n">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.014</v>
+        <v>0.058</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.043</v>
+        <v>0.099</v>
       </c>
       <c r="J15" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="N15" s="1" t="n">
         <v>0.056</v>
       </c>
-      <c r="K15" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L15" s="1" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="N15" s="1" t="n">
-        <v>0.113</v>
-      </c>
       <c r="O15" s="1" t="n">
-        <v>0.092</v>
+        <v>0.036</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.078</v>
+        <v>0.026</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.035</v>
+        <v>0.056</v>
       </c>
       <c r="T15" s="1" t="n">
         <v>0.037</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.038</v>
+        <v>0.028</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.023</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="16">
@@ -1326,7 +1322,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.95</v>
+        <v>0.9410000000000001</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1339,56 +1335,56 @@
         <v>0.001</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.025</v>
+        <v>0.032</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.037</v>
+        <v>0.044</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.097</v>
+        <v>0.082</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.102</v>
+        <v>0.112</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.1</v>
+        <v>0.108</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.099</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.062</v>
+        <v>0.081</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.091</v>
+        <v>0.079</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.073</v>
+        <v>0.081</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.078</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.066</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1400,47 +1396,51 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="M17" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.037</v>
+        <v>0.057</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.077</v>
+        <v>0.091</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.096</v>
+        <v>0.104</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.143</v>
+        <v>0.122</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.173</v>
+        <v>0.15</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.163</v>
+        <v>0.136</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.137</v>
+        <v>0.14</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.926</v>
+        <v>0.9279999999999999</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1450,43 +1450,43 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" s="1" t="n">
+      <c r="I18" s="1" t="n">
         <v>0.001</v>
       </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.058</v>
+        <v>0.051</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.083</v>
+        <v>0.074</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.131</v>
+        <v>0.12</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.135</v>
+        <v>0.154</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.146</v>
+        <v>0.18</v>
       </c>
       <c r="U18" s="1" t="n">
         <v>0.124</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.089</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.893</v>
+        <v>0.888</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1510,37 +1510,37 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="O19" s="1" t="n">
         <v>0.038</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.058</v>
+        <v>0.049</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.097</v>
+        <v>0.094</v>
       </c>
       <c r="R19" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="U19" s="1" t="n">
         <v>0.14</v>
       </c>
-      <c r="S19" s="1" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="T19" s="1" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="U19" s="1" t="n">
-        <v>0.13</v>
-      </c>
       <c r="V19" s="1" t="n">
-        <v>0.106</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="20">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.6110000000000001</v>
+        <v>0.623</v>
       </c>
       <c r="C20" t="n">
         <v>18</v>
@@ -1560,49 +1560,49 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I20" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="I20" s="1" t="n">
-        <v>0.002</v>
-      </c>
       <c r="J20" s="1" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="K20" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="S20" s="1" t="n">
         <v>0.018</v>
       </c>
-      <c r="L20" s="1" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="M20" s="1" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="N20" s="1" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="R20" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>0.017</v>
-      </c>
       <c r="T20" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="U20" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.008</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="21">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.38</v>
+        <v>0.373</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>19</v>
@@ -1626,37 +1626,37 @@
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="3" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>0.021</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.014</v>
+        <v>0.025</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>0.043</v>
+        <v>0.035</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.09</v>
+        <v>0.093</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>0.128</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="22">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.356</v>
+        <v>0.332</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1679,9 +1679,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" s="1" t="n">
         <v>0.001</v>
       </c>
@@ -1689,38 +1687,38 @@
         <v>0.001</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.04</v>
+        <v>0.021</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.055</v>
+        <v>0.028</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.067</v>
+        <v>0.089</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Комарик</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.3260000000000001</v>
+        <v>0.246</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1729,60 +1727,48 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" s="1" t="n">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="I23" s="1" t="n">
+      <c r="O23" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="J23" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K23" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="L23" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="M23" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="N23" s="1" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="O23" s="1" t="n">
-        <v>0.049</v>
-      </c>
       <c r="P23" s="1" t="n">
-        <v>0.04</v>
+        <v>0.001</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.037</v>
+        <v>0.001</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.04</v>
+        <v>0.004</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.013</v>
+        <v>0.028</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.007</v>
+        <v>0.062</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>0.003</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.215</v>
+        <v>0.172</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1799,36 +1785,32 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="S24" s="1" t="n">
         <v>0.007</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.108</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.187</v>
+        <v>0.05</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1847,30 +1829,28 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" s="1" t="n">
-        <v>0.007</v>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="U25" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="T25" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="U25" s="1" t="n">
-        <v>0.059</v>
-      </c>
       <c r="V25" s="1" t="n">
-        <v>0.099</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.063</v>
+        <v>0.039</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1891,16 +1871,16 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="T26" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.047</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="27">
@@ -1910,7 +1890,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1935,19 +1915,21 @@
         <v>0.002</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.023</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>Пассажир</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>0.013</v>
+      </c>
       <c r="C28" t="n">
         <v>26</v>
       </c>
@@ -1967,14 +1949,20 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="T28" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -2004,7 +1992,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -2034,7 +2022,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -2064,7 +2052,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -560,16 +560,16 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.765</v>
+        <v>0.727</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.226</v>
+        <v>0.263</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -600,40 +600,42 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.234</v>
+        <v>0.267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.62</v>
+        <v>0.588</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.034</v>
+        <v>0.041</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.028</v>
+        <v>0.02</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.016</v>
+        <v>0.022</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="N4" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
@@ -653,23 +655,27 @@
       <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="E5" s="1" t="n">
-        <v>0.066</v>
+        <v>0.054</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.447</v>
+        <v>0.459</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.43</v>
+        <v>0.433</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.041</v>
+        <v>0.038</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>0.013</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -696,47 +702,45 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.447</v>
+        <v>0.439</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.222</v>
+        <v>0.221</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.092</v>
+        <v>0.107</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.05</v>
+        <v>0.039</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.02</v>
+        <v>0.026</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.015</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="Q6" s="1" t="n">
         <v>0.002</v>
       </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -760,52 +764,52 @@
         <v>0.002</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.092</v>
+        <v>0.103</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.186</v>
+        <v>0.193</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.138</v>
+        <v>0.162</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.126</v>
+        <v>0.125</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.102</v>
+        <v>0.128</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.095</v>
+        <v>0.08</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.073</v>
+        <v>0.053</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.061</v>
+        <v>0.049</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.035</v>
+        <v>0.029</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="V7" t="inlineStr"/>
     </row>
@@ -824,47 +828,43 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.031</v>
+        <v>0.022</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.109</v>
+        <v>0.12</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.193</v>
+        <v>0.216</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.203</v>
+        <v>0.202</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.154</v>
+        <v>0.173</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>0.129</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.081</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.05</v>
+        <v>0.039</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.004</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -872,7 +872,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -882,57 +882,59 @@
         <v>7</v>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="F9" s="1" t="n">
-        <v>0.001</v>
+        <v>0.019</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.018</v>
+        <v>0.143</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.328</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.183</v>
+        <v>0.172</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.142</v>
+        <v>0.033</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.117</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.068</v>
+        <v>0.006</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.036</v>
+        <v>0.016</v>
       </c>
       <c r="O9" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>0.031</v>
       </c>
-      <c r="P9" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.022</v>
-      </c>
       <c r="T9" s="1" t="n">
-        <v>0.017</v>
+        <v>0.027</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.005</v>
+        <v>0.021</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.006</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="10">
@@ -942,7 +944,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
@@ -951,53 +953,51 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="U10" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="U10" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V10" s="1" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
@@ -1016,59 +1016,59 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.021</v>
+        <v>0.026</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.107</v>
+        <v>0.093</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.104</v>
+        <v>0.119</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.142</v>
+        <v>0.146</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.134</v>
+        <v>0.153</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.114</v>
+        <v>0.125</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.091</v>
+        <v>0.097</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.057</v>
+        <v>0.04</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.036</v>
+        <v>0.027</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9940000000000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1076,112 +1076,106 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="G12" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0.152</v>
+      </c>
       <c r="J12" s="1" t="n">
-        <v>0.001</v>
+        <v>0.19</v>
       </c>
       <c r="K12" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U12" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="L12" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>0.026</v>
-      </c>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9900000000000001</v>
+        <v>0.999</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" s="1" t="n">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K13" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="F13" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>0.026</v>
-      </c>
       <c r="L13" s="1" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.01</v>
+        <v>0.033</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.015</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.019</v>
+        <v>0.124</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.019</v>
+        <v>0.156</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.019</v>
+        <v>0.185</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.028</v>
+        <v>0.158</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.041</v>
+        <v>0.106</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.034</v>
+        <v>0.089</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.027</v>
+        <v>0.038</v>
       </c>
       <c r="V13" s="1" t="n">
         <v>0.011</v>
@@ -1190,139 +1184,143 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9840000000000002</v>
+        <v>0.9850000000000002</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="G14" s="1" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.022</v>
+        <v>0.042</v>
       </c>
       <c r="I14" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="T14" s="1" t="n">
         <v>0.045</v>
       </c>
-      <c r="J14" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="L14" s="1" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="N14" s="1" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.057</v>
-      </c>
       <c r="U14" s="1" t="n">
-        <v>0.036</v>
+        <v>0.045</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.015</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9810000000000001</v>
+        <v>0.9840000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="G15" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H15" s="1" t="n">
         <v>0.014</v>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>0.058</v>
-      </c>
       <c r="I15" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="K15" s="1" t="n">
         <v>0.099</v>
       </c>
-      <c r="J15" s="1" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="K15" s="1" t="n">
-        <v>0.135</v>
-      </c>
       <c r="L15" s="1" t="n">
-        <v>0.106</v>
+        <v>0.134</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.091</v>
+        <v>0.145</v>
       </c>
       <c r="N15" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="Q15" s="1" t="n">
         <v>0.056</v>
       </c>
-      <c r="O15" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>0.048</v>
-      </c>
       <c r="R15" s="1" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.056</v>
+        <v>0.038</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.037</v>
+        <v>0.043</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.028</v>
+        <v>0.032</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9410000000000001</v>
+        <v>0.9630000000000001</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1331,60 +1329,54 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" s="1" t="n">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="I16" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>0.032</v>
-      </c>
       <c r="L16" s="1" t="n">
-        <v>0.044</v>
+        <v>0.005</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.082</v>
+        <v>0.014</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.112</v>
+        <v>0.036</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.1</v>
+        <v>0.066</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.108</v>
+        <v>0.093</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.097</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.081</v>
+        <v>0.129</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.079</v>
+        <v>0.164</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.081</v>
+        <v>0.155</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.051</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9569999999999999</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1396,51 +1388,49 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.091</v>
+        <v>0.082</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.122</v>
+        <v>0.18</v>
       </c>
       <c r="S17" s="1" t="n">
         <v>0.15</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.136</v>
+        <v>0.151</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.14</v>
+        <v>0.129</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.09</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.9279999999999999</v>
+        <v>0.9509999999999998</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1450,43 +1440,45 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>0.023</v>
+      </c>
       <c r="L18" s="1" t="n">
-        <v>0.002</v>
+        <v>0.058</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.005</v>
+        <v>0.083</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.018</v>
+        <v>0.108</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.051</v>
+        <v>0.127</v>
       </c>
       <c r="P18" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="S18" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="Q18" s="1" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="R18" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>0.154</v>
-      </c>
       <c r="T18" s="1" t="n">
-        <v>0.18</v>
+        <v>0.076</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.124</v>
+        <v>0.077</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="19">
@@ -1496,7 +1488,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.888</v>
+        <v>0.921</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1508,39 +1500,39 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" s="1" t="n">
+      <c r="K19" s="1" t="n">
         <v>0.001</v>
       </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="O19" s="1" t="n">
         <v>0.038</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.049</v>
+        <v>0.083</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.094</v>
+        <v>0.123</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.151</v>
+        <v>0.134</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.139</v>
+        <v>0.153</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.144</v>
+        <v>0.158</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.14</v>
+        <v>0.131</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.111</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="20">
@@ -1550,7 +1542,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.623</v>
+        <v>0.63</v>
       </c>
       <c r="C20" t="n">
         <v>18</v>
@@ -1559,50 +1551,48 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" s="1" t="n">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="I20" s="1" t="n">
-        <v>0.001</v>
-      </c>
       <c r="J20" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U20" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="K20" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L20" s="1" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="M20" s="1" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="N20" s="1" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="R20" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="U20" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="V20" s="1" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="21">
@@ -1612,7 +1602,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.373</v>
+        <v>0.411</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>19</v>
@@ -1624,39 +1614,39 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="3" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="3" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>0.006</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>0.035</v>
+        <v>0.047</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>0.057</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.093</v>
+        <v>0.097</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>0.107</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="22">
@@ -1666,7 +1656,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.332</v>
+        <v>0.366</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1684,31 +1674,31 @@
         <v>0.001</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.021</v>
+        <v>0.029</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.028</v>
+        <v>0.044</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.061</v>
+        <v>0.054</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.089</v>
+        <v>0.079</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>0.091</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="23">
@@ -1718,7 +1708,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.246</v>
+        <v>0.271</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1733,32 +1723,28 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="1" t="n">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q23" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="O23" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>0.001</v>
-      </c>
       <c r="R23" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.028</v>
+        <v>0.042</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.062</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>0.131</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="24">
@@ -1768,7 +1754,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.172</v>
+        <v>0.207</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1785,22 +1771,26 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="P24" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q24" s="1" t="n">
+        <v>0.007</v>
+      </c>
       <c r="R24" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.051</v>
+        <v>0.058</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.09</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="25">
@@ -1810,7 +1800,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.05</v>
+        <v>0.074</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1829,18 +1819,20 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S25" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.035</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="26">
@@ -1850,7 +1842,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.039</v>
+        <v>0.047</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1871,16 +1863,16 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="27">
@@ -1890,7 +1882,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.024</v>
+        <v>0.041</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1911,24 +1903,22 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" s="1" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.018</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -1949,20 +1939,16 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" s="1" t="n">
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" s="1" t="n">
         <v>0.001</v>
-      </c>
-      <c r="U28" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="V28" s="1" t="n">
-        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1992,7 +1978,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -2052,7 +2038,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -560,17 +560,15 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.727</v>
+        <v>0.979</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.263</v>
+        <v>0.011</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -590,7 +588,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -600,42 +598,28 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.267</v>
+        <v>0.012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.588</v>
+        <v>0.517</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.041</v>
+        <v>0.362</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.037</v>
+        <v>0.106</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
@@ -646,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -656,27 +640,29 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.054</v>
+        <v>0.322</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.459</v>
+        <v>0.395</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.433</v>
+        <v>0.211</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.013</v>
+        <v>0.021</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>0.003</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -702,44 +688,40 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.09</v>
+        <v>0.149</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.439</v>
+        <v>0.195</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.221</v>
+        <v>0.414</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.107</v>
+        <v>0.12</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.039</v>
+        <v>0.06</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.03</v>
+        <v>0.021</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.026</v>
+        <v>0.017</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
@@ -750,7 +732,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -760,63 +742,51 @@
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" s="1" t="n">
-        <v>0.024</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.103</v>
+        <v>0.102</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.193</v>
+        <v>0.375</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.162</v>
+        <v>0.279</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.125</v>
+        <v>0.108</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.128</v>
+        <v>0.062</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.053</v>
+        <v>0.012</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.049</v>
+        <v>0.015</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.029</v>
+        <v>0.004</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="U7" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.004</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -826,45 +796,51 @@
         <v>6</v>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="F8" s="1" t="n">
-        <v>0.004</v>
+        <v>0.028</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.022</v>
+        <v>0.142</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.12</v>
+        <v>0.301</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.216</v>
+        <v>0.209</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.202</v>
+        <v>0.117</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.173</v>
+        <v>0.066</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.129</v>
+        <v>0.04</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.027</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.039</v>
+        <v>0.018</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+        <v>0.013</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -872,7 +848,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -882,65 +858,59 @@
         <v>7</v>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" s="1" t="n">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="T9" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="F9" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>0.027</v>
-      </c>
       <c r="U9" s="1" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="V9" s="1" t="n">
-        <v>0.016</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -956,48 +926,50 @@
         <v>0.002</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.037</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.03</v>
+        <v>0.102</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.112</v>
+        <v>0.2</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.128</v>
+        <v>0.149</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.176</v>
+        <v>0.093</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.145</v>
+        <v>0.066</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.132</v>
+        <v>0.046</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.062</v>
+        <v>0.048</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.058</v>
+        <v>0.024</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.035</v>
+        <v>0.016</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.025</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
       <c r="U10" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="V10" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1014,61 +986,63 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="H11" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="I11" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>0.019</v>
-      </c>
       <c r="V11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1076,61 +1050,57 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0.089</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="n">
-        <v>0.152</v>
+        <v>0.002</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.19</v>
+        <v>0.008</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.15</v>
+        <v>0.029</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.12</v>
+        <v>0.067</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.062</v>
+        <v>0.104</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.046</v>
+        <v>0.162</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.038</v>
+        <v>0.144</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.042</v>
+        <v>0.162</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.028</v>
+        <v>0.133</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.02</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.029</v>
+        <v>0.055</v>
       </c>
       <c r="T12" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="U12" s="1" t="n">
         <v>0.01</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0.005</v>
       </c>
       <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1138,57 +1108,63 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="G13" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0.054</v>
+      </c>
       <c r="J13" s="1" t="n">
-        <v>0.001</v>
+        <v>0.082</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.002</v>
+        <v>0.105</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.012</v>
+        <v>0.124</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.033</v>
+        <v>0.121</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.124</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.156</v>
+        <v>0.055</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.185</v>
+        <v>0.061</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.158</v>
+        <v>0.062</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.106</v>
+        <v>0.057</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.089</v>
+        <v>0.059</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9850000000000002</v>
+        <v>0.998</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1196,55 +1172,55 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.095</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.123</v>
+        <v>0.144</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.118</v>
+        <v>0.159</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.119</v>
+        <v>0.135</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.096</v>
+        <v>0.101</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.056</v>
+        <v>0.073</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.037</v>
+        <v>0.047</v>
       </c>
       <c r="P14" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="T14" s="1" t="n">
         <v>0.032</v>
       </c>
-      <c r="Q14" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.045</v>
-      </c>
       <c r="U14" s="1" t="n">
-        <v>0.045</v>
+        <v>0.014</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.027</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="15">
@@ -1254,63 +1230,61 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9840000000000001</v>
+        <v>0.9960000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.048</v>
+        <v>0.013</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.078</v>
+        <v>0.039</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.099</v>
+        <v>0.058</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.134</v>
+        <v>0.081</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.145</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.092</v>
+        <v>0.107</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.073</v>
+        <v>0.125</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.056</v>
+        <v>0.104</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.035</v>
+        <v>0.08</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.038</v>
+        <v>0.08</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.043</v>
+        <v>0.068</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.032</v>
+        <v>0.026</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="16">
@@ -1320,7 +1294,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9630000000000001</v>
+        <v>0.993</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1330,53 +1304,57 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K16" s="1" t="n">
-        <v>0.001</v>
+        <v>0.022</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.005</v>
+        <v>0.04</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.014</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.036</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.066</v>
+        <v>0.099</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.093</v>
+        <v>0.106</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.097</v>
+        <v>0.128</v>
       </c>
       <c r="R16" s="1" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="S16" s="1" t="n">
         <v>0.129</v>
       </c>
-      <c r="S16" s="1" t="n">
-        <v>0.164</v>
-      </c>
       <c r="T16" s="1" t="n">
-        <v>0.155</v>
+        <v>0.098</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.13</v>
+        <v>0.057</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.073</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9569999999999999</v>
+        <v>0.989</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1387,50 +1365,54 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>0.005</v>
+      </c>
       <c r="L17" s="1" t="n">
-        <v>0.003</v>
+        <v>0.027</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.011</v>
+        <v>0.053</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.025</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.053</v>
+        <v>0.124</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.082</v>
+        <v>0.131</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.105</v>
+        <v>0.119</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.18</v>
+        <v>0.148</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.15</v>
+        <v>0.114</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.151</v>
+        <v>0.101</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.129</v>
+        <v>0.062</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.068</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.9509999999999998</v>
+        <v>0.985</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1442,53 +1424,53 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="1" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="K18" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M18" s="1" t="n">
         <v>0.023</v>
       </c>
-      <c r="L18" s="1" t="n">
+      <c r="N18" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="O18" s="1" t="n">
         <v>0.058</v>
       </c>
-      <c r="M18" s="1" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="N18" s="1" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="O18" s="1" t="n">
-        <v>0.127</v>
-      </c>
       <c r="P18" s="1" t="n">
-        <v>0.093</v>
+        <v>0.095</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.081</v>
+        <v>0.119</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.169</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.074</v>
+        <v>0.194</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.076</v>
+        <v>0.165</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.077</v>
+        <v>0.082</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.065</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.921</v>
+        <v>0.9740000000000001</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1498,41 +1480,47 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="K19" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>0.014</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>0.027</v>
+      </c>
       <c r="M19" s="1" t="n">
-        <v>0.004</v>
+        <v>0.038</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.015</v>
+        <v>0.061</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.038</v>
+        <v>0.076</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.083</v>
+        <v>0.1</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.123</v>
+        <v>0.113</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.134</v>
+        <v>0.132</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.153</v>
+        <v>0.124</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.158</v>
+        <v>0.146</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.131</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.081</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="20">
@@ -1542,7 +1530,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.63</v>
+        <v>0.551</v>
       </c>
       <c r="C20" t="n">
         <v>18</v>
@@ -1552,47 +1540,39 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="K20" s="1" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="L20" s="1" t="n">
-        <v>0.047</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" s="1" t="n">
-        <v>0.08</v>
+        <v>0.001</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>0.114</v>
+        <v>0.004</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>0.109</v>
+        <v>0.012</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>0.098</v>
+        <v>0.012</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.066</v>
+        <v>0.026</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.017</v>
+        <v>0.042</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.027</v>
+        <v>0.064</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.01</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.006</v>
+        <v>0.161</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.02</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="21">
@@ -1602,7 +1582,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.411</v>
+        <v>0.406</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>19</v>
@@ -1614,49 +1594,45 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="3" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="3" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>0.006</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>0.047</v>
+        <v>0.03</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>0.057</v>
+        <v>0.063</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.097</v>
+        <v>0.118</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>0.131</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.366</v>
+        <v>0.342</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1673,32 +1649,30 @@
       <c r="M22" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="N22" s="1" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="P22" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="R22" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="Q22" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="R22" s="1" t="n">
-        <v>0.029</v>
-      </c>
       <c r="S22" s="1" t="n">
-        <v>0.044</v>
+        <v>0.022</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.054</v>
+        <v>0.036</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.079</v>
+        <v>0.112</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>0.109</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="23">
@@ -1708,7 +1682,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.271</v>
+        <v>0.332</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1726,35 +1700,35 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="Q23" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="S23" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>0.129</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Amaney</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.207</v>
+        <v>0.206</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1771,26 +1745,24 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" s="1" t="n">
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="R24" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="Q24" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="R24" s="1" t="n">
-        <v>0.007</v>
-      </c>
       <c r="S24" s="1" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="25">
@@ -1800,7 +1772,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.074</v>
+        <v>0.112</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1818,31 +1790,33 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="R25" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.043</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.047</v>
+        <v>0.096</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1862,27 +1836,25 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.014</v>
+        <v>0.025</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.027</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>Абеляр</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.041</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1901,24 +1873,28 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="U27" s="1" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.031</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -1942,13 +1918,13 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1978,7 +1954,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>SPQR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -2008,7 +1984,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -2038,7 +2014,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -560,16 +560,18 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.979</v>
+        <v>0.977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.011</v>
+        <v>0.021</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -598,21 +600,23 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="H4" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" s="1" t="n">
+        <v>0.005</v>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -630,7 +634,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -640,29 +644,27 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.322</v>
+        <v>0.103</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.395</v>
+        <v>0.376</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.211</v>
+        <v>0.264</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.039</v>
+        <v>0.167</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.021</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.003</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -687,39 +689,33 @@
       <c r="C6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>0.149</v>
+        <v>0.059</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.195</v>
+        <v>0.214</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.414</v>
+        <v>0.232</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.12</v>
+        <v>0.246</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.06</v>
+        <v>0.206</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.021</v>
+        <v>0.03</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>0.011</v>
-      </c>
+        <v>0.012</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.003</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -732,7 +728,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -741,41 +737,39 @@
       <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.008</v>
+      </c>
       <c r="F7" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.102</v>
+        <v>0.292</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.375</v>
+        <v>0.323</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.279</v>
+        <v>0.206</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.108</v>
+        <v>0.018</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.062</v>
+        <v>0.003</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.03</v>
+        <v>0.002</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="P7" s="1" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
@@ -795,52 +789,44 @@
       <c r="C8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="E8" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="Q8" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -860,57 +846,55 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" s="1" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.006</v>
-      </c>
       <c r="T9" s="1" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -923,58 +907,56 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.037</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.102</v>
+        <v>0.047</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.197</v>
+        <v>0.249</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.2</v>
+        <v>0.178</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.149</v>
+        <v>0.129</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.093</v>
+        <v>0.103</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.066</v>
+        <v>0.08</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.046</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.048</v>
+        <v>0.042</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.024</v>
+        <v>0.036</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.018</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="V10" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.008</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -986,50 +968,46 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" s="1" t="n">
-        <v>0.046</v>
+        <v>0.012</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.09</v>
+        <v>0.057</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.105</v>
+        <v>0.128</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.121</v>
+        <v>0.16</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.145</v>
+        <v>0.137</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.137</v>
+        <v>0.12</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.093</v>
+        <v>0.12</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.078</v>
+        <v>0.083</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.063</v>
+        <v>0.079</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.037</v>
+        <v>0.047</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.034</v>
+        <v>0.029</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="V11" s="1" t="n">
         <v>0.001</v>
@@ -1053,45 +1031,47 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="V12" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="J12" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1100,7 +1080,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9990000000000001</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1108,125 +1088,115 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" s="1" t="n">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.054</v>
+        <v>0.003</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.082</v>
+        <v>0.027</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.105</v>
+        <v>0.063</v>
       </c>
       <c r="L13" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="N13" s="1" t="n">
         <v>0.124</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="O13" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="N13" s="1" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="O13" s="1" t="n">
+      <c r="P13" s="1" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="S13" s="1" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="P13" s="1" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>0.057</v>
-      </c>
       <c r="T13" s="1" t="n">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.998</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" s="1" t="n">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="G14" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>0.04</v>
-      </c>
       <c r="I14" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.037</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.144</v>
+        <v>0.207</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.159</v>
+        <v>0.208</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.135</v>
+        <v>0.19</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.101</v>
+        <v>0.13</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.073</v>
+        <v>0.082</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.046</v>
+        <v>0.042</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.036</v>
+        <v>0.024</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.03</v>
+        <v>0.021</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.043</v>
+        <v>0.007</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="V14" s="1" t="n">
         <v>0.005</v>
       </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1238,63 +1208,59 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" s="1" t="n">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.039</v>
+        <v>0.041</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.058</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.081</v>
+        <v>0.097</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.107</v>
+        <v>0.101</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.125</v>
+        <v>0.099</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.105</v>
+        <v>0.113</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.104</v>
+        <v>0.075</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.08</v>
+        <v>0.076</v>
       </c>
       <c r="S15" s="1" t="n">
         <v>0.08</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.068</v>
+        <v>0.058</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.993</v>
+        <v>0.9949999999999999</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1304,44 +1270,42 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.04</v>
+        <v>0.023</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.042</v>
       </c>
       <c r="N16" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="U16" s="1" t="n">
         <v>0.08400000000000001</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="U16" s="1" t="n">
-        <v>0.057</v>
       </c>
       <c r="V16" s="1" t="n">
         <v>0.023</v>
@@ -1350,11 +1314,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.989</v>
+        <v>0.9930000000000001</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1369,50 +1333,50 @@
         <v>0.003</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.053</v>
+        <v>0.035</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.124</v>
+        <v>0.067</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.131</v>
+        <v>0.09</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.119</v>
+        <v>0.098</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.148</v>
+        <v>0.118</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.114</v>
+        <v>0.166</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.101</v>
+        <v>0.158</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.062</v>
+        <v>0.122</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.033</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.985</v>
+        <v>0.973</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1424,53 +1388,53 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="1" t="n">
-        <v>0.002</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.01</v>
+        <v>0.034</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.023</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.033</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.058</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.095</v>
+        <v>0.108</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.119</v>
+        <v>0.106</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.169</v>
+        <v>0.118</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.194</v>
+        <v>0.1</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.165</v>
+        <v>0.115</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.033</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.9740000000000001</v>
+        <v>0.9540000000000001</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1480,57 +1444,55 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="K19" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="L19" s="1" t="n">
         <v>0.014</v>
       </c>
-      <c r="L19" s="1" t="n">
-        <v>0.027</v>
-      </c>
       <c r="M19" s="1" t="n">
-        <v>0.038</v>
+        <v>0.025</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.061</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.076</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.1</v>
+        <v>0.092</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.113</v>
+        <v>0.131</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.132</v>
+        <v>0.148</v>
       </c>
       <c r="S19" s="1" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="T19" s="1" t="n">
         <v>0.124</v>
       </c>
-      <c r="T19" s="1" t="n">
-        <v>0.146</v>
-      </c>
       <c r="U19" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.551</v>
+        <v>0.655</v>
       </c>
       <c r="C20" t="n">
         <v>18</v>
@@ -1543,146 +1505,154 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="M20" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="N20" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>0.178</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mihmbox</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="C21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L21" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="O20" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="R20" s="1" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="U20" s="1" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>0.144</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Mihmbox</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="3" t="n">
+      <c r="M21" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>0.171</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ПокерНЕок</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q22" s="3" t="n">
         <v>0.003</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>0.138</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Добросердечный</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="C22" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P22" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="R22" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="S22" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="T22" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="U22" s="1" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>0.145</v>
+      <c r="R22" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>0.212</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.332</v>
+        <v>0.173</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1699,36 +1669,30 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" s="1" t="n">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.043</v>
+        <v>0.01</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.107</v>
+        <v>0.041</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>0.151</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.206</v>
+        <v>0.165</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1746,33 +1710,31 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" s="1" t="n">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="R24" s="1" t="n">
-        <v>0.002</v>
-      </c>
       <c r="S24" s="1" t="n">
-        <v>0.017</v>
+        <v>0.003</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.03</v>
+        <v>0.013</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.095</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>sl1dbygad</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.112</v>
+        <v>0.046</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1790,33 +1752,29 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" s="1" t="n">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="R25" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S25" s="1" t="n">
+      <c r="T25" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="T25" s="1" t="n">
-        <v>0.007</v>
-      </c>
       <c r="U25" s="1" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>Amaney</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.096</v>
+        <v>0.01</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1837,24 +1795,22 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" s="1" t="n">
-        <v>0.025</v>
+        <v>0.005</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1873,18 +1829,12 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" s="1" t="n">
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" s="1" t="n">
         <v>0.001</v>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>0.006</v>
       </c>
     </row>
     <row r="28">
@@ -1893,9 +1843,7 @@
           <t>Викусик</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>26</v>
       </c>
@@ -1917,14 +1865,12 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1954,7 +1900,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SPQR</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1984,7 +1930,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -2014,7 +1960,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -2068,7 +2014,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C32">
     <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="0">
-      <formula>19</formula>
+      <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -560,18 +560,18 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.977</v>
+        <v>0.974</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>0.021</v>
       </c>
       <c r="F3" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -600,22 +600,22 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.786</v>
+        <v>0.394</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.145</v>
+        <v>0.399</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.036</v>
+        <v>0.156</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.012</v>
+        <v>0.039</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -644,27 +644,29 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.103</v>
+        <v>0.367</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.376</v>
+        <v>0.292</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.264</v>
+        <v>0.158</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.167</v>
+        <v>0.104</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="J5" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -680,7 +682,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -689,34 +691,42 @@
       <c r="C6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="E6" s="1" t="n">
-        <v>0.059</v>
+        <v>0.181</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.214</v>
+        <v>0.132</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.232</v>
+        <v>0.175</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.246</v>
+        <v>0.198</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.206</v>
+        <v>0.212</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>0.025</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.029</v>
+      </c>
       <c r="M6" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -737,36 +747,30 @@
       <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="K7" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -780,7 +784,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -789,29 +793,27 @@
       <c r="C8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.118</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.175</v>
+        <v>0.195</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.236</v>
+        <v>0.265</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.33</v>
+        <v>0.337</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.064</v>
+        <v>0.059</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.031</v>
+        <v>0.035</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>0.016</v>
@@ -819,9 +821,7 @@
       <c r="M8" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="N8" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -834,7 +834,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -846,49 +846,49 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="H9" s="1" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.062</v>
+        <v>0.096</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.273</v>
+        <v>0.355</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.194</v>
+        <v>0.178</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.144</v>
+        <v>0.114</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.097</v>
+        <v>0.082</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.068</v>
+        <v>0.04</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.052</v>
+        <v>0.043</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.033</v>
+        <v>0.021</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -910,53 +910,51 @@
         <v>0.001</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.047</v>
+        <v>0.061</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.249</v>
+        <v>0.21</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.178</v>
+        <v>0.188</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.129</v>
+        <v>0.157</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.103</v>
+        <v>0.114</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.08</v>
+        <v>0.082</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.042</v>
+        <v>0.044</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>0.036</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.02</v>
+        <v>0.031</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="U10" s="1" t="n">
-        <v>0.008</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -969,54 +967,56 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="I11" s="1" t="n">
-        <v>0.012</v>
+        <v>0.027</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.057</v>
+        <v>0.157</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.128</v>
+        <v>0.147</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.16</v>
+        <v>0.125</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.137</v>
+        <v>0.124</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.12</v>
+        <v>0.113</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.12</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.079</v>
+        <v>0.052</v>
       </c>
       <c r="R11" s="1" t="n">
         <v>0.047</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1034,53 +1034,51 @@
         <v>0.003</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.016</v>
+        <v>0.042</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.036</v>
+        <v>0.091</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.13</v>
+        <v>0.164</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.133</v>
+        <v>0.144</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.157</v>
+        <v>0.127</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.137</v>
+        <v>0.102</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.134</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.073</v>
+        <v>0.062</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.06</v>
+        <v>0.033</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.004</v>
+      </c>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1089,60 +1087,58 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="U13" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="J13" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="U13" s="1" t="n">
-        <v>0.026</v>
-      </c>
       <c r="V13" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.998</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1151,47 +1147,49 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="U14" s="1" t="n">
         <v>0.037</v>
       </c>
-      <c r="J14" s="1" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="L14" s="1" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="N14" s="1" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" s="1" t="n">
+        <v>0.027</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1200,7 +1198,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9960000000000001</v>
+        <v>0.998</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1211,56 +1209,56 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.041</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.097</v>
+        <v>0.053</v>
       </c>
       <c r="M15" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="R15" s="1" t="n">
         <v>0.122</v>
       </c>
-      <c r="N15" s="1" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="R15" s="1" t="n">
-        <v>0.076</v>
-      </c>
       <c r="S15" s="1" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9949999999999999</v>
+        <v>0.9950000000000001</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1269,56 +1267,60 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.018</v>
+      </c>
       <c r="J16" s="1" t="n">
-        <v>0.003</v>
+        <v>0.068</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.021</v>
+        <v>0.13</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.023</v>
+        <v>0.143</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.042</v>
+        <v>0.1</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.074</v>
+        <v>0.096</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.102</v>
+        <v>0.075</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.121</v>
+        <v>0.065</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.15</v>
+        <v>0.066</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.145</v>
+        <v>0.053</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.023</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9930000000000001</v>
+        <v>0.9740000000000001</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1330,53 +1332,53 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.023</v>
+        <v>0.014</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.035</v>
+        <v>0.019</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.058</v>
+        <v>0.043</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.098</v>
+        <v>0.138</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.118</v>
+        <v>0.154</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.166</v>
+        <v>0.158</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.158</v>
+        <v>0.144</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.122</v>
+        <v>0.095</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.048</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.973</v>
+        <v>0.9520000000000001</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1386,45 +1388,47 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="J18" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.02</v>
+        <v>0.057</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.034</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="N18" s="1" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="S18" s="1" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="O18" s="1" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="P18" s="1" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="R18" s="1" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>0.1</v>
-      </c>
       <c r="T18" s="1" t="n">
-        <v>0.115</v>
+        <v>0.057</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.08</v>
+        <v>0.078</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="19">
@@ -1434,7 +1438,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.9540000000000001</v>
+        <v>0.902</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1445,98 +1449,92 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" s="1" t="n">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Добросердечный</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.5449999999999999</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="K19" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="L19" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="M19" s="1" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="N19" s="1" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="O19" s="1" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="R19" s="1" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="S19" s="1" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="T19" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="U19" s="1" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>0.054</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Добросердечный</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="C20" t="n">
-        <v>18</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="M20" s="1" t="n">
+      <c r="M20" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="N20" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R20" s="1" t="n">
+      <c r="N20" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="Q20" s="3" t="n">
         <v>0.041</v>
       </c>
-      <c r="S20" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U20" s="1" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>0.178</v>
+      <c r="R20" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="21">
@@ -1546,7 +1544,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.612</v>
+        <v>0.542</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1559,100 +1557,96 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="L21" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Obscur</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q22" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="M21" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N21" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P21" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R21" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="S21" s="1" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="T21" s="1" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="U21" s="1" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>0.171</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>ПокерНЕок</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q22" s="3" t="n">
+      <c r="R22" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V22" s="3" t="n">
-        <v>0.212</v>
+      <c r="S22" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>0.233</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.173</v>
+        <v>0.351</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1670,29 +1664,33 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="Q23" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>0.007</v>
+      </c>
       <c r="S23" s="1" t="n">
-        <v>0.004</v>
+        <v>0.026</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.01</v>
+        <v>0.063</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.041</v>
+        <v>0.089</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>0.118</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.165</v>
+        <v>0.244</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1707,24 +1705,30 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="P24" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q24" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="R24" s="1" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.003</v>
+        <v>0.022</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.013</v>
+        <v>0.029</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.057</v>
+        <v>0.067</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.089</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="25">
@@ -1734,7 +1738,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.046</v>
+        <v>0.023</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1753,7 +1757,9 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="S25" s="1" t="n">
         <v>0.001</v>
       </c>
@@ -1761,10 +1767,10 @@
         <v>0.004</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.029</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="26">
@@ -1774,7 +1780,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1791,27 +1797,29 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+      <c r="T26" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="U26" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>0.001</v>
-      </c>
+          <t>EliasPavlov</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>25</v>
       </c>
@@ -1833,14 +1841,12 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1900,7 +1906,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>averagemorningstarenjoyer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1930,7 +1936,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1960,7 +1966,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>nnnekk</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -2014,7 +2020,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C32">
     <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="0">
-      <formula>20</formula>
+      <formula>18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -540,11 +540,6 @@
           <t>Rank 18</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Rank 19</t>
-        </is>
-      </c>
     </row>
     <row r="2"/>
     <row r="3">
@@ -560,17 +555,15 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.974</v>
+        <v>0.976</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -585,7 +578,6 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -603,16 +595,16 @@
         <v>0.005</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.394</v>
+        <v>0.396</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.399</v>
+        <v>0.396</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.156</v>
+        <v>0.151</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.039</v>
+        <v>0.045</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>0.007</v>
@@ -629,7 +621,6 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -647,22 +638,22 @@
         <v>0.015</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.367</v>
+        <v>0.377</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.292</v>
+        <v>0.257</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.158</v>
+        <v>0.172</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.104</v>
+        <v>0.109</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.056</v>
+        <v>0.066</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>0.002</v>
@@ -677,12 +668,11 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -691,54 +681,45 @@
       <c r="C6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>0.181</v>
+        <v>0.02</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.132</v>
+        <v>0.114</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.175</v>
+        <v>0.325</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.198</v>
+        <v>0.328</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.212</v>
+        <v>0.196</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.026</v>
+        <v>0.01</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.025</v>
+        <v>0.003</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.004</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -747,39 +728,50 @@
       <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="E7" s="1" t="n">
-        <v>0.017</v>
+        <v>0.169</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.104</v>
+        <v>0.152</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.312</v>
+        <v>0.148</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.373</v>
+        <v>0.206</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.174</v>
+        <v>0.195</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.012</v>
+        <v>0.042</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+        <v>0.029</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -795,31 +787,31 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.195</v>
+        <v>0.203</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.265</v>
+        <v>0.289</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.337</v>
+        <v>0.305</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.059</v>
+        <v>0.062</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.035</v>
+        <v>0.024</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -829,7 +821,6 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -846,50 +837,47 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" s="1" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.096</v>
+        <v>0.113</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.355</v>
+        <v>0.361</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>0.178</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.114</v>
+        <v>0.134</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.082</v>
+        <v>0.066</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.043</v>
+        <v>0.026</v>
       </c>
       <c r="P9" s="1" t="n">
         <v>0.03</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.019</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="T9" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -910,46 +898,47 @@
         <v>0.001</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.061</v>
+        <v>0.043</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.21</v>
+        <v>0.196</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.188</v>
+        <v>0.209</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.157</v>
+        <v>0.136</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.114</v>
+        <v>0.117</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.082</v>
+        <v>0.096</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.059</v>
+        <v>0.081</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.044</v>
+        <v>0.039</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.031</v>
+        <v>0.024</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+        <v>0.004</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -968,59 +957,56 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.027</v>
+        <v>0.036</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.157</v>
+        <v>0.134</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.147</v>
+        <v>0.152</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.125</v>
+        <v>0.141</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.124</v>
+        <v>0.134</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.113</v>
+        <v>0.078</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="V11" s="1" t="n">
-        <v>0.002</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1031,54 +1017,53 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.042</v>
+        <v>0.011</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.091</v>
+        <v>0.028</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.118</v>
+        <v>0.066</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.164</v>
+        <v>0.112</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.144</v>
+        <v>0.135</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.127</v>
+        <v>0.162</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.102</v>
+        <v>0.149</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.147</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.062</v>
+        <v>0.105</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.033</v>
+        <v>0.045</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="V12" t="inlineStr"/>
+        <v>0.007</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.999</v>
+        <v>0.9970000000000001</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1087,58 +1072,57 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="I13" s="1" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.01</v>
+        <v>0.045</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.029</v>
+        <v>0.101</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.135</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.138</v>
+        <v>0.171</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.159</v>
+        <v>0.117</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.179</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.132</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.106</v>
+        <v>0.051</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.058</v>
+        <v>0.032</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="V13" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.998</v>
+        <v>0.9830000000000001</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1149,46 +1133,43 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" s="1" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.019</v>
+        <v>0.067</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.056</v>
+        <v>0.114</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.078</v>
+        <v>0.109</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.08</v>
+        <v>0.118</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.099</v>
+        <v>0.102</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.127</v>
+        <v>0.092</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.104</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.103</v>
+        <v>0.077</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.101</v>
+        <v>0.073</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.093</v>
+        <v>0.059</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="V14" s="1" t="n">
-        <v>0.027</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="15">
@@ -1198,7 +1179,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.998</v>
+        <v>0.9820000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1212,53 +1193,50 @@
         <v>0.002</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.018</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.044</v>
+        <v>0.052</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.053</v>
+        <v>0.062</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.101</v>
+        <v>0.083</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.096</v>
+        <v>0.102</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.127</v>
+        <v>0.115</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.141</v>
+        <v>0.122</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.134</v>
+        <v>0.129</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.122</v>
+        <v>0.126</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.077</v>
+        <v>0.083</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="V15" s="1" t="n">
-        <v>0.01</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9800000000000001</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1267,50 +1245,45 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J16" s="1" t="n">
         <v>0.018</v>
       </c>
-      <c r="J16" s="1" t="n">
-        <v>0.068</v>
-      </c>
       <c r="K16" s="1" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.143</v>
+        <v>0.075</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.1</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.106</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.075</v>
+        <v>0.137</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.065</v>
+        <v>0.112</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.066</v>
+        <v>0.101</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.053</v>
+        <v>0.091</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.05</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>0.01</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="17">
@@ -1320,7 +1293,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9740000000000001</v>
+        <v>0.9359999999999999</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1330,45 +1303,44 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J17" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.014</v>
+        <v>0.025</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>0.019</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.043</v>
+        <v>0.047</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>0.062</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.102</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.138</v>
+        <v>0.112</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.154</v>
+        <v>0.161</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.158</v>
+        <v>0.184</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.144</v>
+        <v>0.125</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="V17" s="1" t="n">
-        <v>0.052</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1378,7 +1350,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.9520000000000001</v>
+        <v>0.896</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1389,46 +1361,43 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.021</v>
+        <v>0.028</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.057</v>
+        <v>0.046</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.103</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.117</v>
+        <v>0.094</v>
       </c>
       <c r="O18" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="S18" s="1" t="n">
         <v>0.081</v>
       </c>
-      <c r="P18" s="1" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="R18" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="S18" s="1" t="n">
+      <c r="T18" s="1" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="T18" s="1" t="n">
-        <v>0.057</v>
-      </c>
       <c r="U18" s="1" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="V18" s="1" t="n">
-        <v>0.051</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="19">
@@ -1438,7 +1407,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.902</v>
+        <v>0.761</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1454,31 +1423,28 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.076</v>
+        <v>0.1</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.182</v>
+        <v>0.149</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.234</v>
+        <v>0.221</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>0.117</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="20">
@@ -1488,7 +1454,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.5449999999999999</v>
+        <v>0.446</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1500,41 +1466,36 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="3" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.041</v>
+        <v>0.033</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.063</v>
+        <v>0.048</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.093</v>
+        <v>0.117</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>0.11</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="21">
@@ -1544,7 +1505,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.542</v>
+        <v>0.43</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1555,42 +1516,41 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K21" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>0.012</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.067</v>
+        <v>0.053</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.079</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.075</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>0.093</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="22">
@@ -1600,7 +1560,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.467</v>
+        <v>0.23</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1617,26 +1577,21 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.054</v>
+        <v>0.061</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>0.233</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="23">
@@ -1646,7 +1601,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.351</v>
+        <v>0.215</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1663,24 +1618,23 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="Q23" s="1" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="S23" s="1" t="n">
         <v>0.026</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.063</v>
+        <v>0.05</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>0.164</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="24">
@@ -1690,7 +1644,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.244</v>
+        <v>0.125</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1705,30 +1659,25 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.022</v>
+        <v>0.013</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.029</v>
+        <v>0.038</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="V24" s="1" t="n">
-        <v>0.114</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="25">
@@ -1738,7 +1687,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.023</v>
+        <v>0.011</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1757,20 +1706,15 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="V25" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="26">
@@ -1780,7 +1724,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1797,20 +1741,15 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="V26" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="27">
@@ -1841,12 +1780,11 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1871,12 +1809,11 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1901,12 +1838,11 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>averagemorningstarenjoyer</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1931,12 +1867,11 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1961,12 +1896,11 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nnnekk</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1991,10 +1925,589 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Yanchik_250</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>31</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Дядя Витя</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>32</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Настя дай стек</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>33</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>@TryFraiz</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>34</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Кальян</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="n">
+        <v>35</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Пиковая Дама</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>36</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Rik_dds</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="n">
+        <v>37</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Абеляр</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="n">
+        <v>38</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>nesmotri_v_shelll1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="n">
+        <v>39</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Сан Саныч</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="n">
+        <v>40</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Пассажир</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>41</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>vovaa_25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="n">
+        <v>42</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Тихоня</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="n">
+        <v>43</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>yankkk</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>44</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>dama_pica</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="n">
+        <v>45</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Добряк</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>46</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>кинчоч</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="n">
+        <v>47</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cheremsha</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>48</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chesters</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>49</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>finch79</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>50</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B32">
+  <conditionalFormatting sqref="B2:B52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2006,7 +2519,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:V32">
+  <conditionalFormatting sqref="D2:U52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2018,7 +2531,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C32">
+  <conditionalFormatting sqref="C3:C52">
     <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="0">
       <formula>18</formula>
     </cfRule>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -555,13 +555,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.976</v>
+        <v>0.978</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -592,22 +592,22 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.396</v>
+        <v>0.359</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.396</v>
+        <v>0.416</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.151</v>
+        <v>0.178</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.045</v>
+        <v>0.037</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -635,29 +635,27 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.377</v>
+        <v>0.416</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.257</v>
+        <v>0.25</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.172</v>
+        <v>0.162</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.109</v>
+        <v>0.103</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.066</v>
+        <v>0.047</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -672,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -681,34 +679,42 @@
       <c r="C6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" s="1" t="n">
+        <v>0.008</v>
+      </c>
       <c r="E6" s="1" t="n">
-        <v>0.02</v>
+        <v>0.163</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.114</v>
+        <v>0.14</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.325</v>
+        <v>0.167</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.328</v>
+        <v>0.203</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.196</v>
+        <v>0.2</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.01</v>
+        <v>0.043</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.003</v>
+        <v>0.03</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+        <v>0.028</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -719,7 +725,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -728,45 +734,35 @@
       <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>0.169</v>
+        <v>0.02</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.152</v>
+        <v>0.118</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.148</v>
+        <v>0.327</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.206</v>
+        <v>0.326</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.195</v>
+        <v>0.177</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.042</v>
+        <v>0.024</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.029</v>
+        <v>0.007</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P7" s="1" t="n">
         <v>0.001</v>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
@@ -787,33 +783,35 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.076</v>
+        <v>0.074</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.203</v>
+        <v>0.164</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.289</v>
+        <v>0.301</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.305</v>
+        <v>0.334</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.021</v>
+        <v>0.011</v>
       </c>
       <c r="M8" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -839,43 +837,43 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.113</v>
+        <v>0.102</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.361</v>
+        <v>0.37</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.178</v>
+        <v>0.193</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.134</v>
+        <v>0.107</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.044</v>
+        <v>0.047</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.026</v>
+        <v>0.032</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="S9" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="U9" t="inlineStr"/>
     </row>
@@ -894,51 +892,47 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.043</v>
+        <v>0.054</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.196</v>
+        <v>0.175</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.209</v>
+        <v>0.213</v>
       </c>
       <c r="L10" s="1" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="M10" s="1" t="n">
         <v>0.136</v>
       </c>
-      <c r="M10" s="1" t="n">
-        <v>0.117</v>
-      </c>
       <c r="N10" s="1" t="n">
-        <v>0.096</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.081</v>
+        <v>0.059</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.039</v>
+        <v>0.054</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>0.038</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.024</v>
+        <v>0.027</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="U10" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.007</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -955,58 +949,60 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="H11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>0.036</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.134</v>
+        <v>0.14</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.152</v>
+        <v>0.144</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.141</v>
+        <v>0.123</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.134</v>
+        <v>0.128</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.078</v>
+        <v>0.116</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.101</v>
+        <v>0.092</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.077</v>
+        <v>0.064</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.05</v>
+        <v>0.053</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.046</v>
+        <v>0.043</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.024</v>
+        <v>0.034</v>
       </c>
       <c r="T11" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.998</v>
+        <v>0.9980000000000001</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1017,53 +1013,53 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J12" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="U12" s="1" t="n">
         <v>0.011</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0.007</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9970000000000001</v>
+        <v>0.9960000000000001</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1072,57 +1068,53 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I13" s="1" t="n">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" s="1" t="n">
         <v>0.011</v>
       </c>
-      <c r="J13" s="1" t="n">
-        <v>0.045</v>
-      </c>
       <c r="K13" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="R13" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="L13" s="1" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0.051</v>
-      </c>
       <c r="S13" s="1" t="n">
-        <v>0.032</v>
+        <v>0.057</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9830000000000001</v>
+        <v>0.9880000000000001</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1131,55 +1123,57 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="I14" s="1" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.067</v>
+        <v>0.018</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.114</v>
+        <v>0.032</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.109</v>
+        <v>0.076</v>
       </c>
       <c r="M14" s="1" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="O14" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="N14" s="1" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>0.092</v>
-      </c>
       <c r="P14" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.138</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.077</v>
+        <v>0.141</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.073</v>
+        <v>0.11</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.059</v>
+        <v>0.096</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.04</v>
+        <v>0.043</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9820000000000001</v>
+        <v>0.9810000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1187,46 +1181,48 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" s="1" t="n">
-        <v>0.002</v>
+        <v>0.024</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.018</v>
+        <v>0.056</v>
       </c>
       <c r="K15" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="T15" s="1" t="n">
         <v>0.052</v>
       </c>
-      <c r="L15" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="N15" s="1" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="R15" s="1" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="S15" s="1" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="T15" s="1" t="n">
-        <v>0.055</v>
-      </c>
       <c r="U15" s="1" t="n">
-        <v>0.033</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="16">
@@ -1247,43 +1243,43 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.05</v>
+        <v>0.053</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.075</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N16" s="1" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R16" s="1" t="n">
         <v>0.095</v>
       </c>
-      <c r="O16" s="1" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>0.101</v>
-      </c>
       <c r="S16" s="1" t="n">
-        <v>0.091</v>
+        <v>0.102</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.035</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="17">
@@ -1293,7 +1289,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9359999999999999</v>
+        <v>0.928</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1307,40 +1303,40 @@
         <v>0.001</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.019</v>
+        <v>0.03</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.047</v>
+        <v>0.041</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>0.062</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.102</v>
+        <v>0.08</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.161</v>
+        <v>0.157</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.184</v>
+        <v>0.174</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.125</v>
+        <v>0.162</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1350,7 +1346,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.896</v>
+        <v>0.9040000000000001</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1361,43 +1357,43 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.046</v>
+        <v>0.063</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.06</v>
+        <v>0.073</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.094</v>
+        <v>0.108</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.096</v>
+        <v>0.106</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.108</v>
+        <v>0.099</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.077</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.081</v>
+        <v>0.075</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.052</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.056</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="19">
@@ -1407,7 +1403,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.761</v>
+        <v>0.777</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1422,39 +1418,37 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.05</v>
+        <v>0.039</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.1</v>
+        <v>0.099</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.149</v>
+        <v>0.16</v>
       </c>
       <c r="T19" s="1" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="U19" s="1" t="n">
         <v>0.221</v>
-      </c>
-      <c r="U19" s="1" t="n">
-        <v>0.208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Mihmbox</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.446</v>
+        <v>0.467</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1464,48 +1458,54 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="I20" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.003</v>
+      </c>
       <c r="L20" s="3" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.004</v>
+        <v>0.012</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.024</v>
+        <v>0.03</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.033</v>
+        <v>0.039</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.048</v>
+        <v>0.054</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.09</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.117</v>
+        <v>0.097</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.107</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mihmbox</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.43</v>
+        <v>0.458</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1516,38 +1516,34 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="K21" s="1" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" s="1" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.012</v>
+        <v>0.003</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.026</v>
+        <v>0.019</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>0.023</v>
+        <v>0.03</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.04</v>
+        <v>0.049</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.053</v>
+        <v>0.081</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="U21" s="1" t="n">
         <v>0.096</v>
@@ -1560,7 +1556,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.23</v>
+        <v>0.219</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1578,20 +1574,18 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" s="1" t="n">
         <v>0.006</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.027</v>
+        <v>0.015</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.061</v>
+        <v>0.067</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.134</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="23">
@@ -1601,7 +1595,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.215</v>
+        <v>0.158</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1619,22 +1613,22 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q23" s="1" t="n">
         <v>0.003</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>0.01</v>
       </c>
       <c r="R23" s="1" t="n">
         <v>0.011</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.026</v>
+        <v>0.019</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.05</v>
+        <v>0.041</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.115</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="24">
@@ -1644,7 +1638,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.125</v>
+        <v>0.129</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1662,22 +1656,22 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="Q24" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R24" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="R24" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="S24" s="1" t="n">
-        <v>0.013</v>
+        <v>0.019</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.038</v>
+        <v>0.033</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.058</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1687,7 +1681,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1706,15 +1700,17 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S25" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="26">
@@ -1724,7 +1720,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1745,20 +1741,20 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>finch79</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="C27" t="n">
         <v>25</v>
       </c>
@@ -1779,12 +1775,14 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1813,7 +1811,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1871,7 +1869,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1900,7 +1898,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1929,7 +1927,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1958,7 +1956,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1987,7 +1985,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -2016,7 +2014,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2045,7 +2043,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2074,7 +2072,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2103,7 +2101,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2132,7 +2130,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>Добряк</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2161,7 +2159,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2190,7 +2188,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2219,7 +2217,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2248,7 +2246,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>vovaa_25</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2277,7 +2275,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2306,7 +2304,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2335,7 +2333,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>dama_pica</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2364,7 +2362,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Добряк</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2393,7 +2391,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Абеляр</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2422,7 +2420,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2451,7 +2449,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>dama_pica</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2480,7 +2478,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>finch79</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -555,13 +555,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.978</v>
+        <v>0.965</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -592,23 +592,21 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.359</v>
+        <v>0.345</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.416</v>
+        <v>0.48</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.178</v>
+        <v>0.149</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0.008</v>
-      </c>
+        <v>0.018</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -635,26 +633,24 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.416</v>
+        <v>0.419</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.162</v>
+        <v>0.197</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.103</v>
+        <v>0.091</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.006</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -680,41 +676,39 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.163</v>
+        <v>0.181</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.14</v>
+        <v>0.159</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.167</v>
+        <v>0.287</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.203</v>
+        <v>0.277</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.2</v>
+        <v>0.028</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.043</v>
+        <v>0.014</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.028</v>
+        <v>0.019</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -725,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -736,29 +730,27 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.118</v>
+        <v>0.089</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.327</v>
+        <v>0.358</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.326</v>
+        <v>0.446</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.177</v>
+        <v>0.054</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -772,7 +764,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -782,52 +774,60 @@
         <v>6</v>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>0.074</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" s="1" t="n">
-        <v>0.164</v>
+        <v>0.004</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.301</v>
+        <v>0.061</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.334</v>
+        <v>0.273</v>
       </c>
       <c r="J8" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <v>0.064</v>
       </c>
-      <c r="K8" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="O8" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
@@ -840,51 +840,39 @@
         <v>0.016</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.102</v>
+        <v>0.196</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.37</v>
+        <v>0.381</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.193</v>
+        <v>0.285</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.06</v>
+        <v>0.021</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
@@ -892,56 +880,60 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="H10" s="1" t="n">
-        <v>0.005</v>
+        <v>0.055</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.054</v>
+        <v>0.208</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.175</v>
+        <v>0.115</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.213</v>
+        <v>0.101</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.154</v>
+        <v>0.131</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.136</v>
+        <v>0.1</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.059</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.038</v>
+        <v>0.034</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="T10" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
@@ -949,60 +941,58 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <v>0.008</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>0.005</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9980000000000001</v>
+        <v>0.997</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1011,55 +1001,57 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="I12" s="1" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.034</v>
+        <v>0.025</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.094</v>
+        <v>0.057</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.14</v>
+        <v>0.092</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.159</v>
+        <v>0.144</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.152</v>
+        <v>0.176</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.132</v>
+        <v>0.182</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.097</v>
+        <v>0.141</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.065</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.056</v>
+        <v>0.038</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="T12" s="1" t="n">
         <v>0.024</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9960000000000001</v>
+        <v>0.994</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1070,51 +1062,41 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>0.139</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" s="1" t="n">
-        <v>0.153</v>
+        <v>0.004</v>
       </c>
       <c r="P13" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="T13" s="1" t="n">
         <v>0.165</v>
       </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>0.022</v>
-      </c>
       <c r="U13" s="1" t="n">
-        <v>0.011</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9880000000000001</v>
+        <v>0.9910000000000001</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1122,58 +1104,60 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="H14" s="1" t="n">
-        <v>0.001</v>
+        <v>0.022</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.002</v>
+        <v>0.095</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.018</v>
+        <v>0.111</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.032</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.076</v>
+        <v>0.108</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.098</v>
+        <v>0.091</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.118</v>
+        <v>0.094</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.138</v>
+        <v>0.062</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.141</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.11</v>
+        <v>0.037</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.096</v>
+        <v>0.042</v>
       </c>
       <c r="T14" s="1" t="n">
         <v>0.043</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.031</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9810000000000001</v>
+        <v>0.9890000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1181,48 +1165,48 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" s="1" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" s="1" t="n">
-        <v>0.024</v>
+        <v>0.017</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.056</v>
+        <v>0.029</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.112</v>
+        <v>0.055</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.123</v>
+        <v>0.121</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.092</v>
+        <v>0.135</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.126</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.06</v>
+        <v>0.142</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.074</v>
+        <v>0.117</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.073</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.063</v>
+        <v>0.034</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.052</v>
+        <v>0.038</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.042</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="16">
@@ -1232,7 +1216,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9800000000000001</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1241,45 +1225,47 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="I16" s="1" t="n">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.022</v>
+        <v>0.04</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.053</v>
+        <v>0.059</v>
       </c>
       <c r="L16" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="R16" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="M16" s="1" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>0.095</v>
-      </c>
       <c r="S16" s="1" t="n">
-        <v>0.102</v>
+        <v>0.05</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.064</v>
+        <v>0.047</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.041</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="17">
@@ -1289,7 +1275,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.928</v>
+        <v>0.9359999999999999</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1299,44 +1285,42 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.03</v>
+        <v>0.043</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.041</v>
+        <v>0.054</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.062</v>
+        <v>0.082</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.116</v>
+        <v>0.144</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.157</v>
+        <v>0.148</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.174</v>
+        <v>0.131</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.162</v>
+        <v>0.105</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1330,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.9040000000000001</v>
+        <v>0.897</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1355,45 +1339,47 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="I18" s="1" t="n">
-        <v>0.004</v>
+        <v>0.042</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.025</v>
+        <v>0.044</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.073</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.108</v>
+        <v>0.097</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.106</v>
+        <v>0.09</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.099</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.075</v>
+        <v>0.058</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.052</v>
+        <v>0.056</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.047</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="19">
@@ -1403,7 +1389,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.777</v>
+        <v>0.7570000000000001</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1416,39 +1402,45 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="O19" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.022</v>
+        <v>0.038</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.039</v>
+        <v>0.065</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.099</v>
+        <v>0.11</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.16</v>
+        <v>0.136</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.228</v>
+        <v>0.201</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.221</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Mihmbox</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.467</v>
+        <v>0.4359999999999999</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1458,54 +1450,50 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="3" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.017</v>
+        <v>0.011</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.039</v>
+        <v>0.051</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.097</v>
+        <v>0.089</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.111</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Mihmbox</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.458</v>
+        <v>0.427</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1514,39 +1502,45 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" s="1" t="n">
+        <v>0.005</v>
+      </c>
       <c r="L21" s="1" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.011</v>
+        <v>0.021</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.049</v>
+        <v>0.047</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.081</v>
+        <v>0.05</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.078</v>
+        <v>0.05</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.09</v>
+        <v>0.063</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.096</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="22">
@@ -1556,7 +1550,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.219</v>
+        <v>0.243</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1574,18 +1568,20 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="R22" s="1" t="n">
         <v>0.006</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.067</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.131</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="23">
@@ -1595,7 +1591,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.158</v>
+        <v>0.205</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1610,25 +1606,29 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="N23" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="P23" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.041</v>
+        <v>0.044</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.083</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="24">
@@ -1653,25 +1653,29 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="N24" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="P24" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.019</v>
+        <v>0.011</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.033</v>
+        <v>0.029</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1681,7 +1685,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1698,19 +1702,19 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="T25" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1720,7 +1724,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1743,18 +1747,16 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>finch79</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>0.001</v>
-      </c>
+          <t>Плейбой в карты</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>25</v>
       </c>
@@ -1775,14 +1777,12 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1811,7 +1811,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1840,7 +1840,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1869,7 +1869,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1898,7 +1898,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1956,7 +1956,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -2014,7 +2014,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2072,7 +2072,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2101,7 +2101,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2130,7 +2130,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Добряк</t>
+          <t>finch79</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2217,7 +2217,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>АРАМАИСКА</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2246,7 +2246,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2275,7 +2275,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2362,7 +2362,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2391,7 +2391,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2420,7 +2420,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2449,7 +2449,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dama_pica</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>Кесадилия</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -555,13 +555,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.978</v>
+        <v>0.839</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.02</v>
+        <v>0.148</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.002</v>
+        <v>0.013</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -582,7 +582,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -592,22 +592,22 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.002</v>
+        <v>0.144</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.359</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.416</v>
+        <v>0.178</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.178</v>
+        <v>0.083</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -625,7 +625,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -635,26 +635,22 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.416</v>
+        <v>0.129</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.162</v>
+        <v>0.301</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.018</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -680,42 +676,44 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.163</v>
+        <v>0.162</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.14</v>
+        <v>0.211</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.167</v>
+        <v>0.234</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.203</v>
+        <v>0.169</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.2</v>
+        <v>0.066</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.043</v>
+        <v>0.013</v>
       </c>
       <c r="K6" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="M6" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="L6" s="1" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="N6" s="1" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="O6" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P6" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
@@ -735,33 +733,37 @@
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" s="1" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" s="1" t="n">
-        <v>0.118</v>
+        <v>0.006</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.327</v>
+        <v>0.076</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.326</v>
+        <v>0.322</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.177</v>
+        <v>0.447</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.024</v>
+        <v>0.075</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.007</v>
+        <v>0.047</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+        <v>0.013</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -772,7 +774,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -782,40 +784,44 @@
         <v>6</v>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>0.074</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" s="1" t="n">
-        <v>0.164</v>
+        <v>0.004</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.301</v>
+        <v>0.017</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.334</v>
+        <v>0.1</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.064</v>
+        <v>0.228</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.026</v>
+        <v>0.155</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.011</v>
+        <v>0.122</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.003</v>
+        <v>0.111</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+        <v>0.107</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0.005</v>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -823,7 +829,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -837,43 +843,43 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="I9" s="1" t="n">
-        <v>0.102</v>
-      </c>
       <c r="J9" s="1" t="n">
-        <v>0.37</v>
+        <v>0.079</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.193</v>
+        <v>0.15</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.107</v>
+        <v>0.151</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.047</v>
+        <v>0.155</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.032</v>
+        <v>0.112</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.033</v>
+        <v>0.093</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.019</v>
+        <v>0.054</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.013</v>
+        <v>0.023</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.004</v>
+        <v>0.012</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="U9" t="inlineStr"/>
     </row>
@@ -892,117 +898,105 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="H10" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.054</v>
+        <v>0.033</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.175</v>
+        <v>0.105</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.213</v>
+        <v>0.133</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.154</v>
+        <v>0.111</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.136</v>
+        <v>0.128</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.059</v>
+        <v>0.11</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.054</v>
+        <v>0.106</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.038</v>
+        <v>0.074</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.027</v>
+        <v>0.05</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.006</v>
+        <v>0.016</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0.042</v>
+      </c>
       <c r="G11" s="1" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="L11" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9980000000000001</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1011,55 +1005,57 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="I12" s="1" t="n">
-        <v>0.006</v>
+        <v>0.017</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.034</v>
+        <v>0.061</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.094</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.14</v>
+        <v>0.106</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.159</v>
+        <v>0.11</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.152</v>
+        <v>0.116</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.132</v>
+        <v>0.105</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.097</v>
+        <v>0.131</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.065</v>
+        <v>0.103</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.056</v>
+        <v>0.096</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.028</v>
+        <v>0.045</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9960000000000001</v>
+        <v>0.9970000000000001</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1067,54 +1063,60 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="G13" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0.074</v>
+      </c>
       <c r="J13" s="1" t="n">
-        <v>0.011</v>
+        <v>0.178</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.025</v>
+        <v>0.139</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.106</v>
       </c>
       <c r="M13" s="1" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="R13" s="1" t="n">
         <v>0.096</v>
       </c>
-      <c r="N13" s="1" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0.101</v>
-      </c>
       <c r="S13" s="1" t="n">
-        <v>0.057</v>
+        <v>0.052</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.022</v>
+        <v>0.04</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9880000000000001</v>
+        <v>0.9900000000000001</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1123,57 +1125,55 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" s="1" t="n">
-        <v>0.002</v>
+        <v>0.013</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.018</v>
+        <v>0.051</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.032</v>
+        <v>0.061</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.076</v>
+        <v>0.09</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.098</v>
+        <v>0.132</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.118</v>
+        <v>0.107</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.138</v>
+        <v>0.096</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.141</v>
+        <v>0.09</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.11</v>
+        <v>0.078</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.096</v>
+        <v>0.082</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.043</v>
+        <v>0.048</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.031</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9810000000000001</v>
+        <v>0.984</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1181,58 +1181,58 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" s="1" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" s="1" t="n">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.056</v>
+        <v>0.035</v>
       </c>
       <c r="K15" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="P15" s="1" t="n">
         <v>0.112</v>
       </c>
-      <c r="L15" s="1" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="N15" s="1" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="O15" s="1" t="n">
+      <c r="Q15" s="1" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="P15" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>0.074</v>
-      </c>
       <c r="R15" s="1" t="n">
-        <v>0.073</v>
+        <v>0.068</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.063</v>
+        <v>0.045</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.052</v>
+        <v>0.061</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.042</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9800000000000001</v>
+        <v>0.9770000000000001</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1243,53 +1243,53 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.022</v>
+        <v>0.006</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.053</v>
+        <v>0.012</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.048</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.099</v>
+        <v>0.081</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.121</v>
+        <v>0.144</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.119</v>
+        <v>0.185</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.12</v>
+        <v>0.178</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.095</v>
+        <v>0.122</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.102</v>
+        <v>0.076</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.064</v>
+        <v>0.058</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.041</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.928</v>
+        <v>0.9349999999999998</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1297,56 +1297,60 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="I17" s="1" t="n">
-        <v>0.001</v>
+        <v>0.038</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.005</v>
+        <v>0.119</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.005</v>
+        <v>0.128</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.01</v>
+        <v>0.122</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.03</v>
+        <v>0.114</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.041</v>
+        <v>0.057</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.116</v>
+        <v>0.034</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.157</v>
+        <v>0.031</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.174</v>
+        <v>0.054</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.162</v>
+        <v>0.068</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.9040000000000001</v>
+        <v>0.889</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1356,54 +1360,48 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>0.063</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" s="1" t="n">
-        <v>0.073</v>
+        <v>0.001</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.108</v>
+        <v>0.008</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.097</v>
+        <v>0.024</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.106</v>
+        <v>0.058</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.099</v>
+        <v>0.092</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.075</v>
+        <v>0.216</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.052</v>
+        <v>0.205</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.047</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.777</v>
+        <v>0.8460000000000001</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1417,38 +1415,42 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="O19" s="1" t="n">
-        <v>0.008</v>
+        <v>0.029</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.022</v>
+        <v>0.043</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.039</v>
+        <v>0.106</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.099</v>
+        <v>0.149</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.16</v>
+        <v>0.182</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.228</v>
+        <v>0.176</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.221</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Mihmbox</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.467</v>
+        <v>0.448</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1458,54 +1460,48 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="3" t="n">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0.01</v>
-      </c>
       <c r="M20" s="3" t="n">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.017</v>
+        <v>0.005</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.021</v>
+        <v>0.014</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.039</v>
+        <v>0.059</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.054</v>
+        <v>0.068</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.097</v>
+        <v>0.089</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.111</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.458</v>
+        <v>0.39</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1518,45 +1514,43 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" s="1" t="n">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="M21" s="1" t="n">
-        <v>0.003</v>
-      </c>
       <c r="N21" s="1" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.019</v>
+        <v>0.007</v>
       </c>
       <c r="P21" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Q21" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q21" s="1" t="n">
+      <c r="R21" s="1" t="n">
         <v>0.049</v>
       </c>
-      <c r="R21" s="1" t="n">
-        <v>0.081</v>
-      </c>
       <c r="S21" s="1" t="n">
-        <v>0.078</v>
+        <v>0.063</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.09</v>
+        <v>0.092</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.096</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>Mihmbox</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.219</v>
+        <v>0.257</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1570,32 +1564,42 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+      <c r="M22" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>0.014</v>
+      </c>
       <c r="R22" s="1" t="n">
-        <v>0.006</v>
+        <v>0.028</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.015</v>
+        <v>0.054</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.067</v>
+        <v>0.063</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.131</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.158</v>
+        <v>0.17</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1612,33 +1616,31 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" s="1" t="n">
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="R23" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="Q23" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <v>0.011</v>
-      </c>
       <c r="S23" s="1" t="n">
-        <v>0.019</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.041</v>
+        <v>0.03</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.083</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.129</v>
+        <v>0.107</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1655,33 +1657,29 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
+          <t>Amaney</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1700,27 +1698,23 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S25" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>sl1dbygad</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1741,7 +1735,9 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+      <c r="T26" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="U26" s="1" t="n">
         <v>0.002</v>
       </c>
@@ -1749,11 +1745,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>finch79</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1773,19 +1769,23 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" s="1" t="n">
+      <c r="S27" s="1" t="n">
         <v>0.001</v>
       </c>
+      <c r="T27" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Пассажир</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>Сокол</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="C28" t="n">
         <v>26</v>
       </c>
@@ -1805,13 +1805,15 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+      <c r="T28" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1840,7 +1842,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1869,7 +1871,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1898,7 +1900,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1927,7 +1929,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1956,7 +1958,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1985,7 +1987,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -2014,7 +2016,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2043,7 +2045,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2072,7 +2074,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2101,7 +2103,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2130,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Добряк</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2159,7 +2161,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2188,7 +2190,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2217,7 +2219,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2246,7 +2248,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>АРАМАИСКА</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2275,7 +2277,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Абеляр</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2304,7 +2306,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2362,7 +2364,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2391,7 +2393,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2420,7 +2422,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>finch79</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2449,7 +2451,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dama_pica</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2478,7 +2480,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>Кесадилия</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -555,15 +555,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.839</v>
+        <v>0.851</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.148</v>
+        <v>0.137</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>0.011</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -592,23 +594,21 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.144</v>
+        <v>0.131</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.178</v>
+        <v>0.184</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.083</v>
+        <v>0.094</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0.003</v>
-      </c>
+        <v>0.031</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -635,19 +635,19 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.129</v>
+        <v>0.149</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.55</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.301</v>
+        <v>0.275</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -676,44 +676,42 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.162</v>
+        <v>0.153</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.211</v>
+        <v>0.203</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.234</v>
+        <v>0.263</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.169</v>
+        <v>0.214</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.066</v>
+        <v>0.013</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.013</v>
+        <v>0.018</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>0.03</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>0.013</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
@@ -723,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -733,37 +731,31 @@
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="F7" s="1" t="n">
-        <v>0.006</v>
+        <v>0.043</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.076</v>
+        <v>0.348</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.322</v>
+        <v>0.52</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.447</v>
+        <v>0.075</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.075</v>
+        <v>0.011</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="O7" s="1" t="n">
         <v>0.002</v>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -790,38 +782,36 @@
         <v>0.004</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.017</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I8" s="1" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="L8" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="J8" s="1" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>0.122</v>
-      </c>
       <c r="M8" s="1" t="n">
-        <v>0.111</v>
+        <v>0.102</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.107</v>
+        <v>0.075</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.038</v>
+        <v>0.034</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>0.005</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -829,7 +819,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -841,52 +831,56 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" s="1" t="n">
+        <v>0.01</v>
+      </c>
       <c r="H9" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="I9" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -898,95 +892,103 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="S10" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="I10" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" s="1" t="n">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="F11" s="1" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>0.297</v>
-      </c>
       <c r="H11" s="1" t="n">
-        <v>0.408</v>
+        <v>0.019</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.186</v>
+        <v>0.134</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.05</v>
+        <v>0.108</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.014</v>
+        <v>0.096</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+        <v>0.095</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -996,7 +998,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.9990000000000001</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1006,56 +1008,56 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.017</v>
+        <v>0.032</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.061</v>
+        <v>0.075</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.106</v>
+        <v>0.074</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.116</v>
+        <v>0.154</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.105</v>
+        <v>0.159</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.131</v>
+        <v>0.129</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.103</v>
+        <v>0.117</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.096</v>
+        <v>0.053</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.045</v>
+        <v>0.023</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.029</v>
+        <v>0.005</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9970000000000001</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1063,60 +1065,58 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" s="1" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.074</v>
+        <v>0.046</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.178</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.139</v>
+        <v>0.076</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.106</v>
+        <v>0.067</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.066</v>
+        <v>0.117</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.055</v>
+        <v>0.131</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.047</v>
+        <v>0.12</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.044</v>
+        <v>0.114</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.067</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.096</v>
+        <v>0.075</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.052</v>
+        <v>0.056</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.04</v>
+        <v>0.029</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9900000000000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1125,55 +1125,45 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="I14" s="1" t="n">
-        <v>0.013</v>
+        <v>0.054</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.051</v>
+        <v>0.163</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.061</v>
+        <v>0.318</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.09</v>
+        <v>0.291</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.106</v>
+        <v>0.124</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.132</v>
+        <v>0.037</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>0.036</v>
-      </c>
+        <v>0.007</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.984</v>
+        <v>0.9840000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1186,53 +1176,53 @@
         <v>0.001</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.035</v>
+        <v>0.012</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.055</v>
+        <v>0.02</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.097</v>
+        <v>0.031</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.12</v>
+        <v>0.067</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.135</v>
+        <v>0.181</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.112</v>
+        <v>0.218</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.144</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.068</v>
+        <v>0.083</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.045</v>
+        <v>0.041</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.061</v>
+        <v>0.025</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.032</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9770000000000001</v>
+        <v>0.9420000000000002</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1240,56 +1230,60 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>0.042</v>
+      </c>
       <c r="I16" s="1" t="n">
-        <v>0.001</v>
+        <v>0.121</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.006</v>
+        <v>0.116</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.012</v>
+        <v>0.095</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.032</v>
+        <v>0.098</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.048</v>
+        <v>0.079</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.081</v>
+        <v>0.066</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.144</v>
+        <v>0.057</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.185</v>
+        <v>0.041</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.178</v>
+        <v>0.025</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.122</v>
+        <v>0.036</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.076</v>
+        <v>0.039</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.058</v>
+        <v>0.054</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.034</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9349999999999998</v>
+        <v>0.8810000000000002</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1297,60 +1291,50 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="K17" s="1" t="n">
-        <v>0.128</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" s="1" t="n">
-        <v>0.122</v>
+        <v>0.002</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.114</v>
+        <v>0.003</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.057</v>
+        <v>0.01</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.058</v>
+        <v>0.042</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.04</v>
+        <v>0.081</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.034</v>
+        <v>0.139</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.031</v>
+        <v>0.199</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.054</v>
+        <v>0.195</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.068</v>
+        <v>0.141</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.065</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.889</v>
+        <v>0.8680000000000001</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1364,44 +1348,44 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.001</v>
+        <v>0.011</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.008</v>
+        <v>0.019</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.058</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.092</v>
+        <v>0.131</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.133</v>
+        <v>0.192</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.216</v>
+        <v>0.167</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.205</v>
+        <v>0.143</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.151</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.8460000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1415,32 +1399,24 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="1" t="n">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="N19" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="O19" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>0.106</v>
-      </c>
       <c r="R19" s="1" t="n">
-        <v>0.149</v>
+        <v>0.019</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.182</v>
+        <v>0.151</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.176</v>
+        <v>0.29</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.153</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="20">
@@ -1450,7 +1426,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.448</v>
+        <v>0.511</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1463,35 +1439,33 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="3" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.014</v>
+        <v>0.026</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.028</v>
+        <v>0.036</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.059</v>
+        <v>0.082</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.068</v>
+        <v>0.098</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.081</v>
+        <v>0.108</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.089</v>
+        <v>0.077</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.101</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="21">
@@ -1501,7 +1475,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.39</v>
+        <v>0.417</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1514,33 +1488,35 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="M21" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>0.014</v>
+        <v>0.031</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.03</v>
+        <v>0.057</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.049</v>
+        <v>0.061</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.063</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.092</v>
+        <v>0.077</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.133</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="22">
@@ -1550,7 +1526,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.257</v>
+        <v>0.289</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1561,35 +1537,39 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.014</v>
+        <v>0.04</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.028</v>
+        <v>0.044</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.076</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="23">
@@ -1599,7 +1579,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1615,22 +1595,26 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="O23" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q23" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.03</v>
+        <v>0.037</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.128</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="24">
@@ -1658,18 +1642,20 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="R24" s="1" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.062</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="25">
@@ -1679,7 +1665,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.005</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1699,9 +1685,11 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T25" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="U25" s="1" t="n">
         <v>0.004</v>
@@ -1732,12 +1720,12 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" s="1" t="n">
         <v>0.002</v>
       </c>
@@ -1769,13 +1757,11 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T27" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" s="1" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1784,7 +1770,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -1808,12 +1794,14 @@
       <c r="T28" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1842,7 +1830,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1871,7 +1859,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1900,7 +1888,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -2016,7 +2004,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2045,7 +2033,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2074,7 +2062,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2103,7 +2091,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2132,7 +2120,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2161,7 +2149,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2190,7 +2178,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2219,7 +2207,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2248,7 +2236,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2277,7 +2265,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>АРАМАИСКА</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2306,7 +2294,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2335,7 +2323,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2364,7 +2352,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2393,7 +2381,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>finch79</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2422,7 +2410,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>finch79</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2451,7 +2439,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2480,7 +2468,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Кесадилия</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -555,17 +555,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.851</v>
+        <v>0.617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.383</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -594,20 +590,16 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.131</v>
+        <v>0.383</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.555</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0.031</v>
-      </c>
+        <v>0.062</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -634,20 +626,18 @@
       <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>0.149</v>
+        <v>0.057</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.275</v>
+        <v>0.068</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -666,7 +656,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -675,42 +665,28 @@
       <c r="C6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>0.017</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>0.153</v>
+        <v>0.004</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.203</v>
+        <v>0.045</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.263</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.214</v>
+        <v>0.362</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.032</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -721,7 +697,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -735,25 +711,29 @@
         <v>0.001</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.043</v>
+        <v>0.026</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.348</v>
+        <v>0.355</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.52</v>
+        <v>0.246</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.011</v>
+        <v>0.14</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>0.126</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -766,7 +746,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -778,39 +758,31 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" s="1" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.242</v>
+        <v>0.253</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.177</v>
+        <v>0.373</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.111</v>
+        <v>0.243</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.102</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="Q8" s="1" t="n">
-        <v>0.003</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -819,7 +791,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -832,55 +804,49 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" s="1" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.056</v>
+        <v>0.212</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.21</v>
+        <v>0.349</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.131</v>
+        <v>0.058</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.079</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L9" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="P9" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="M9" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0.064</v>
-      </c>
       <c r="Q9" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -892,50 +858,50 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="H10" s="1" t="n">
-        <v>0.013</v>
+        <v>0.045</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.068</v>
+        <v>0.135</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.116</v>
+        <v>0.131</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.104</v>
+        <v>0.14</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.134</v>
+        <v>0.154</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.162</v>
+        <v>0.152</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.154</v>
+        <v>0.13</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.125</v>
+        <v>0.078</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.068</v>
+        <v>0.025</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.031</v>
+        <v>0.008</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>0.008</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -947,54 +913,52 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>0.019</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" s="1" t="n">
-        <v>0.134</v>
+        <v>0.004</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.108</v>
+        <v>0.028</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.096</v>
+        <v>0.077</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.095</v>
+        <v>0.16</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.118</v>
+        <v>0.199</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.132</v>
+        <v>0.128</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.097</v>
+        <v>0.142</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.064</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.036</v>
+        <v>0.061</v>
       </c>
       <c r="S11" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="T11" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="T11" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1008,52 +972,52 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.075</v>
+        <v>0.028</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.064</v>
+        <v>0.062</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.074</v>
+        <v>0.107</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>0.109</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.154</v>
+        <v>0.14</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.159</v>
+        <v>0.122</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.129</v>
+        <v>0.099</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.117</v>
+        <v>0.118</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.053</v>
+        <v>0.096</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.023</v>
+        <v>0.08</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.005</v>
+        <v>0.021</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1067,56 +1031,56 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.046</v>
+        <v>0.021</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.076</v>
+        <v>0.055</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.067</v>
+        <v>0.105</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.117</v>
+        <v>0.121</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.131</v>
+        <v>0.1</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.12</v>
+        <v>0.091</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.114</v>
+        <v>0.093</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.075</v>
+        <v>0.119</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.056</v>
+        <v>0.093</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.029</v>
+        <v>0.045</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1125,45 +1089,53 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>0.054</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" s="1" t="n">
-        <v>0.163</v>
+        <v>0.001</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.318</v>
+        <v>0.002</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.291</v>
+        <v>0.015</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.124</v>
+        <v>0.023</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.037</v>
+        <v>0.06</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+        <v>0.107</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>0.032</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9840000000000001</v>
+        <v>0.989</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1171,58 +1143,60 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="H15" s="1" t="n">
-        <v>0.001</v>
+        <v>0.042</v>
       </c>
       <c r="I15" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="O15" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="J15" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K15" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L15" s="1" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="N15" s="1" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>0.181</v>
-      </c>
       <c r="P15" s="1" t="n">
-        <v>0.218</v>
+        <v>0.01</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.144</v>
+        <v>0.015</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.083</v>
+        <v>0.053</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.041</v>
+        <v>0.093</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.025</v>
+        <v>0.122</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.028</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9420000000000002</v>
+        <v>0.9760000000000001</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1230,60 +1204,50 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>0.095</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" s="1" t="n">
-        <v>0.098</v>
+        <v>0.002</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.079</v>
+        <v>0.006</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.066</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.057</v>
+        <v>0.023</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.041</v>
+        <v>0.065</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.025</v>
+        <v>0.107</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.036</v>
+        <v>0.169</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.039</v>
+        <v>0.217</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.054</v>
+        <v>0.246</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.8810000000000002</v>
+        <v>0.9650000000000001</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1293,48 +1257,54 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>0.017</v>
+      </c>
       <c r="L17" s="1" t="n">
-        <v>0.002</v>
+        <v>0.035</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.003</v>
+        <v>0.063</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.042</v>
+        <v>0.107</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.081</v>
+        <v>0.167</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.139</v>
+        <v>0.163</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.199</v>
+        <v>0.121</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.195</v>
+        <v>0.077</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.141</v>
+        <v>0.063</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.8680000000000001</v>
+        <v>0.965</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1345,47 +1315,51 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>0.025</v>
+      </c>
       <c r="L18" s="1" t="n">
-        <v>0.003</v>
+        <v>0.062</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.011</v>
+        <v>0.091</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.019</v>
+        <v>0.132</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.025</v>
+        <v>0.126</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.131</v>
+        <v>0.093</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.192</v>
+        <v>0.048</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.167</v>
+        <v>0.043</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.143</v>
+        <v>0.102</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.093</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1394,29 +1368,47 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="H19" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>0.05</v>
+      </c>
       <c r="Q19" s="1" t="n">
-        <v>0.002</v>
+        <v>0.03</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.151</v>
+        <v>0.014</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.29</v>
+        <v>0.077</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.351</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="20">
@@ -1426,7 +1418,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.511</v>
+        <v>0.53</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1439,33 +1431,33 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="3" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="L20" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="3" t="n">
         <v>0.014</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.026</v>
+        <v>0.032</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.036</v>
+        <v>0.059</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.082</v>
+        <v>0.093</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.098</v>
+        <v>0.114</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.108</v>
+        <v>0.111</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.066</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="21">
@@ -1475,7 +1467,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.417</v>
+        <v>0.364</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1488,35 +1480,29 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M21" s="1" t="n">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="N21" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>0.012</v>
-      </c>
       <c r="P21" s="1" t="n">
-        <v>0.031</v>
+        <v>0.005</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.057</v>
+        <v>0.011</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.061</v>
+        <v>0.015</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.054</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.077</v>
+        <v>0.09</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.104</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="22">
@@ -1526,7 +1512,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.289</v>
+        <v>0.156</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1537,39 +1523,29 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K22" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="1" t="n">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="N22" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="O22" s="1" t="n">
-        <v>0.014</v>
-      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.004</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" s="1" t="n">
-        <v>0.044</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.053</v>
+        <v>0.024</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.06</v>
+        <v>0.034</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.053</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="23">
@@ -1579,7 +1555,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.172</v>
+        <v>0.078</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1595,26 +1571,16 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" s="1" t="n">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="P23" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>0.037</v>
-      </c>
       <c r="U23" s="1" t="n">
-        <v>0.099</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="24">
@@ -1624,7 +1590,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.107</v>
+        <v>0.054</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1642,20 +1608,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="R24" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="S24" s="1" t="n">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="T24" s="1" t="n">
-        <v>0.036</v>
-      </c>
       <c r="U24" s="1" t="n">
-        <v>0.051</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="25">
@@ -1665,7 +1625,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.003</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1685,25 +1645,19 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T25" s="1" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>0.003</v>
-      </c>
+          <t>Сокол</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>24</v>
       </c>
@@ -1720,25 +1674,19 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Пассажир</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>0.002</v>
-      </c>
+          <t>sl1dbygad</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>25</v>
       </c>
@@ -1759,19 +1707,15 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Сокол</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>0.002</v>
-      </c>
+          <t>Плейбой в карты</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>26</v>
       </c>
@@ -1791,17 +1735,13 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U28" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1830,7 +1770,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1859,7 +1799,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1888,7 +1828,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1917,7 +1857,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1946,7 +1886,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1975,7 +1915,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -2004,7 +1944,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2062,7 +2002,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2091,7 +2031,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2120,7 +2060,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2149,7 +2089,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2178,7 +2118,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2207,7 +2147,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>vovaa_25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2236,7 +2176,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2265,7 +2205,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2294,7 +2234,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2352,7 +2292,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>finch79</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2381,7 +2321,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>finch79</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2439,7 +2379,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2468,7 +2408,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>АРАМАИСКА</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -555,10 +555,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.617</v>
+        <v>0.638</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.383</v>
+        <v>0.362</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -590,15 +590,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.383</v>
+        <v>0.362</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.555</v>
+        <v>0.58</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>0.054</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -628,16 +630,16 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.867</v>
+        <v>0.855</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.068</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -666,23 +668,25 @@
         <v>4</v>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" s="1" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" s="1" t="n">
-        <v>0.045</v>
+        <v>0.049</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.494</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.362</v>
+        <v>0.296</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+        <v>0.144</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -708,33 +712,35 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.026</v>
+        <v>0.042</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.355</v>
+        <v>0.315</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>0.246</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.06</v>
+        <v>0.068</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.14</v>
+        <v>0.146</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.04</v>
+        <v>0.051</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>0.001</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -758,28 +764,28 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" s="1" t="n">
+        <v>0.094</v>
+      </c>
       <c r="H8" s="1" t="n">
-        <v>0.067</v>
+        <v>0.37</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.253</v>
+        <v>0.4</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.373</v>
+        <v>0.1</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.243</v>
+        <v>0.028</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.054</v>
+        <v>0.006</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -804,40 +810,40 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" s="1" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.212</v>
+        <v>0.061</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.349</v>
+        <v>0.256</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.058</v>
+        <v>0.298</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.049</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.063</v>
+        <v>0.056</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.092</v>
+        <v>0.081</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.107</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.059</v>
+        <v>0.053</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -858,38 +864,36 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" s="1" t="n">
-        <v>0.045</v>
+        <v>0.014</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.135</v>
+        <v>0.056</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.131</v>
+        <v>0.137</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.154</v>
+        <v>0.19</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.13</v>
+        <v>0.136</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.078</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.025</v>
+        <v>0.034</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="R10" s="1" t="n">
         <v>0.001</v>
@@ -915,44 +919,42 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" s="1" t="n">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <v>0.004</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>0.001</v>
       </c>
     </row>
     <row r="12">
@@ -971,47 +973,45 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.028</v>
+        <v>0.021</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.062</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.107</v>
+        <v>0.129</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.109</v>
+        <v>0.142</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.122</v>
+        <v>0.114</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.099</v>
+        <v>0.103</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.118</v>
+        <v>0.103</v>
       </c>
       <c r="R12" s="1" t="n">
         <v>0.096</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.08</v>
+        <v>0.061</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.021</v>
+        <v>0.032</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="13">
@@ -1031,46 +1031,46 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.021</v>
+        <v>0.007</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.055</v>
+        <v>0.064</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.105</v>
+        <v>0.091</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.1</v>
+        <v>0.109</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.091</v>
+        <v>0.106</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.093</v>
+        <v>0.09</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.104</v>
+        <v>0.117</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="S13" s="1" t="n">
         <v>0.093</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.045</v>
+        <v>0.036</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="14">
@@ -1091,41 +1091,39 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.023</v>
+        <v>0.025</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.06</v>
+        <v>0.052</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.16</v>
+        <v>0.172</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.176</v>
+        <v>0.194</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.17</v>
+        <v>0.168</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.15</v>
+        <v>0.163</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.104</v>
+        <v>0.092</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.032</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="15">
@@ -1135,7 +1133,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.989</v>
+        <v>0.994</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1143,50 +1141,48 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" s="1" t="n">
-        <v>0.042</v>
+        <v>0.007</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.097</v>
+        <v>0.052</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.145</v>
+        <v>0.146</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.151</v>
+        <v>0.193</v>
       </c>
       <c r="L15" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="S15" s="1" t="n">
         <v>0.125</v>
       </c>
-      <c r="M15" s="1" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="N15" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="R15" s="1" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="S15" s="1" t="n">
-        <v>0.093</v>
-      </c>
       <c r="T15" s="1" t="n">
-        <v>0.122</v>
+        <v>0.127</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.055</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="16">
@@ -1196,7 +1192,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9760000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1210,34 +1206,34 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.023</v>
+        <v>0.042</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.065</v>
+        <v>0.079</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.107</v>
+        <v>0.091</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.169</v>
+        <v>0.151</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.217</v>
+        <v>0.209</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.246</v>
+        <v>0.244</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.132</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="17">
@@ -1247,7 +1243,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9650000000000001</v>
+        <v>0.9610000000000001</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1257,44 +1253,42 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="M17" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="U17" s="1" t="n">
         <v>0.063</v>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="S17" s="1" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="T17" s="1" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="U17" s="1" t="n">
-        <v>0.066</v>
       </c>
     </row>
     <row r="18">
@@ -1304,7 +1298,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.965</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1316,7 +1310,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="1" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>0.025</v>
@@ -1325,31 +1319,31 @@
         <v>0.062</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.091</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.132</v>
+        <v>0.122</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.126</v>
+        <v>0.151</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.13</v>
+        <v>0.124</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.093</v>
+        <v>0.08</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.043</v>
+        <v>0.054</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.102</v>
+        <v>0.092</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.107</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="19">
@@ -1359,7 +1353,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.92</v>
+        <v>0.893</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1369,46 +1363,46 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" s="1" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.035</v>
+        <v>0.014</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.093</v>
+        <v>0.116</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0.122</v>
+        <v>0.118</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.058</v>
+        <v>0.054</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.05</v>
+        <v>0.054</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.077</v>
+        <v>0.082</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.164</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="20">
@@ -1432,32 +1426,34 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+        <v>0.003</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>0.006</v>
+      </c>
       <c r="N20" s="3" t="n">
-        <v>0.014</v>
+        <v>0.008</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.032</v>
+        <v>0.026</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.114</v>
+        <v>0.123</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="21">
@@ -1467,7 +1463,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.364</v>
+        <v>0.388</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1487,22 +1483,22 @@
         <v>0.002</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.054</v>
+        <v>0.043</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.09</v>
+        <v>0.101</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.187</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="22">
@@ -1512,7 +1508,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.156</v>
+        <v>0.167</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1527,25 +1523,25 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="R22" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.024</v>
+        <v>0.013</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.034</v>
+        <v>0.041</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.083</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="23">
@@ -1555,7 +1551,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.078</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1577,10 +1573,10 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.077</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="24">
@@ -1590,7 +1586,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1612,10 +1608,10 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.045</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="25">
@@ -1625,7 +1621,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1648,13 +1644,13 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>sl1dbygad</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1683,7 +1679,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1712,7 +1708,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1741,7 +1737,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1770,7 +1766,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1799,7 +1795,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1828,7 +1824,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1857,7 +1853,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1886,7 +1882,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1944,7 +1940,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1973,7 +1969,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2002,7 +1998,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2031,7 +2027,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>finch79</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2089,7 +2085,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2147,7 +2143,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>vovaa_25</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2176,7 +2172,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2234,7 +2230,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2263,7 +2259,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2292,7 +2288,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>finch79</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2321,7 +2317,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2350,7 +2346,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>АРАМАИСКА</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2379,7 +2375,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2408,7 +2404,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
+          <t>Кесадилия</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:V52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -540,6 +540,11 @@
           <t>Rank 18</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Rank 19</t>
+        </is>
+      </c>
     </row>
     <row r="2"/>
     <row r="3">
@@ -555,10 +560,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.638</v>
+        <v>0.605</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.362</v>
+        <v>0.395</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -576,6 +581,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -590,16 +596,16 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.362</v>
+        <v>0.395</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.58</v>
+        <v>0.544</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.054</v>
+        <v>0.058</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -615,11 +621,12 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -630,19 +637,23 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>0.056</v>
+        <v>0.001</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.855</v>
+        <v>0.05</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.506</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+        <v>0.276</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0.027</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -654,11 +665,12 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -668,27 +680,33 @@
         <v>4</v>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="F6" s="1" t="n">
-        <v>0.049</v>
+        <v>0.03</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.494</v>
+        <v>0.311</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.296</v>
+        <v>0.28</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.144</v>
+        <v>0.074</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.015</v>
+        <v>0.15</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>0.114</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -697,11 +715,12 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -711,36 +730,30 @@
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>0.042</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" s="1" t="n">
-        <v>0.315</v>
+        <v>0.103</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.246</v>
+        <v>0.364</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.068</v>
+        <v>0.387</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.146</v>
+        <v>0.083</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.128</v>
+        <v>0.045</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.051</v>
+        <v>0.017</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="N7" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -748,11 +761,12 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -765,39 +779,52 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" s="1" t="n">
-        <v>0.094</v>
+        <v>0.003</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.37</v>
+        <v>0.057</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.4</v>
+        <v>0.255</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.1</v>
+        <v>0.306</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.028</v>
+        <v>0.039</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.006</v>
+        <v>0.029</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+        <v>0.057</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -809,50 +836,57 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" s="1" t="n">
-        <v>0.008</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" s="1" t="n">
-        <v>0.061</v>
+        <v>0.012</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.256</v>
+        <v>0.049</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.298</v>
+        <v>0.138</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.049</v>
+        <v>0.204</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.024</v>
+        <v>0.128</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.056</v>
+        <v>0.066</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.081</v>
+        <v>0.03</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.053</v>
+        <v>0.006</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.022</v>
+        <v>0.005</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+        <v>0.048</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -865,47 +899,52 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="1" t="n">
-        <v>0.014</v>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" s="1" t="n">
-        <v>0.056</v>
+        <v>0.003</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.137</v>
+        <v>0.024</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.21</v>
+        <v>0.076</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.149</v>
+        <v>0.159</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.136</v>
+        <v>0.159</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.119</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.034</v>
+        <v>0.111</v>
       </c>
       <c r="Q10" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U10" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="R10" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -919,48 +958,51 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="J11" s="1" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.092</v>
+        <v>0.09</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.159</v>
+        <v>0.112</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.174</v>
+        <v>0.139</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.153</v>
+        <v>0.114</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.1</v>
+        <v>0.106</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="Q11" s="1" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="R11" s="1" t="n">
         <v>0.091</v>
       </c>
-      <c r="R11" s="1" t="n">
-        <v>0.054</v>
-      </c>
       <c r="S11" s="1" t="n">
-        <v>0.045</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.02</v>
+        <v>0.037</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -975,112 +1017,96 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.021</v>
+        <v>0.042</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.129</v>
+        <v>0.124</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.142</v>
+        <v>0.109</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.12</v>
+        <v>0.113</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.114</v>
+        <v>0.092</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.103</v>
+        <v>0.096</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.103</v>
+        <v>0.113</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.096</v>
+        <v>0.112</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.061</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.032</v>
+        <v>0.04</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="E13" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0.074</v>
+      </c>
       <c r="H13" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="U13" s="1" t="n">
-        <v>0.007</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1089,51 +1115,50 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="H14" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0.15</v>
+      </c>
       <c r="K14" s="1" t="n">
-        <v>0.005</v>
+        <v>0.202</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.01</v>
+        <v>0.182</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.025</v>
+        <v>0.164</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.052</v>
+        <v>0.121</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.094</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.172</v>
+        <v>0.034</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>0.025</v>
-      </c>
+        <v>0.007</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.994</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1142,48 +1167,43 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="I15" s="1" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="J15" s="1" t="n">
-        <v>0.146</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" s="1" t="n">
-        <v>0.193</v>
+        <v>0.002</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.119</v>
+        <v>0.013</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.06</v>
+        <v>0.026</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.014</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.011</v>
+        <v>0.095</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.008</v>
+        <v>0.144</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.017</v>
+        <v>0.18</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.054</v>
+        <v>0.178</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.125</v>
+        <v>0.17</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.127</v>
+        <v>0.097</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.061</v>
-      </c>
+        <v>0.024</v>
+      </c>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1192,7 +1212,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.98</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1204,46 +1224,51 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L16" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.079</v>
+        <v>0.063</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.091</v>
+        <v>0.114</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.151</v>
+        <v>0.146</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.209</v>
+        <v>0.219</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.244</v>
+        <v>0.236</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.133</v>
+        <v>0.14</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>0.019</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9610000000000001</v>
+        <v>0.996</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1255,50 +1280,53 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.017</v>
+        <v>0.036</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.037</v>
+        <v>0.076</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.058</v>
+        <v>0.093</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.093</v>
+        <v>0.113</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.142</v>
+        <v>0.137</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.136</v>
+        <v>0.129</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.144</v>
+        <v>0.065</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.135</v>
+        <v>0.05</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.078</v>
+        <v>0.057</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.052</v>
+        <v>0.089</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.063</v>
+        <v>0.117</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.9950000000000001</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1310,40 +1338,43 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="1" t="n">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.025</v>
+        <v>0.017</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.062</v>
+        <v>0.034</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.122</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.151</v>
+        <v>0.133</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.124</v>
+        <v>0.15</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.08</v>
+        <v>0.168</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.049</v>
+        <v>0.136</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.054</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.092</v>
+        <v>0.061</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.101</v>
+        <v>0.061</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>0.026</v>
       </c>
     </row>
     <row r="19">
@@ -1353,7 +1384,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.893</v>
+        <v>0.986</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1362,143 +1393,150 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" s="1" t="n">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.116</v>
+        <v>0.11</v>
       </c>
       <c r="L19" s="1" t="n">
         <v>0.118</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.109</v>
+        <v>0.12</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.095</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.054</v>
+        <v>0.078</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.054</v>
+        <v>0.043</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="R19" s="1" t="n">
         <v>0.022</v>
       </c>
       <c r="S19" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ПокерНЕок</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="C20" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>0.277</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Добросердечный</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>0.016</v>
-      </c>
-      <c r="T19" s="1" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="U19" s="1" t="n">
-        <v>0.126</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Добросердечный</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>0.034</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ПокерНЕок</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="C21" t="n">
-        <v>19</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P21" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="R21" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="S21" s="1" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="T21" s="1" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="U21" s="1" t="n">
-        <v>0.215</v>
       </c>
     </row>
     <row r="22">
@@ -1508,7 +1546,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.167</v>
+        <v>0.31</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1524,9 +1562,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" s="1" t="n">
         <v>0.001</v>
@@ -1535,13 +1571,16 @@
         <v>0.007</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="T22" s="1" t="n">
         <v>0.041</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.104</v>
+        <v>0.099</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>0.146</v>
       </c>
     </row>
     <row r="23">
@@ -1551,7 +1590,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.306</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1571,12 +1610,17 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T23" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.067</v>
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>0.233</v>
       </c>
     </row>
     <row r="24">
@@ -1586,7 +1630,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.053</v>
+        <v>0.217</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1608,10 +1652,13 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.051</v>
+        <v>0.062</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="25">
@@ -1621,7 +1668,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1643,17 +1690,20 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" s="1" t="n">
-        <v>0.004</v>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" s="1" t="n">
+        <v>0.017</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>Сокол</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="C26" t="n">
         <v>24</v>
       </c>
@@ -1674,15 +1724,22 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Сокол</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>Пассажир</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="C27" t="n">
         <v>25</v>
       </c>
@@ -1703,15 +1760,20 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Пассажир</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>sl1dbygad</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="C28" t="n">
         <v>26</v>
       </c>
@@ -1732,12 +1794,15 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1762,11 +1827,12 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1791,11 +1857,12 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1820,11 +1887,12 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1849,11 +1917,12 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1878,11 +1947,12 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1907,11 +1977,12 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1936,11 +2007,12 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1965,11 +2037,12 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1994,11 +2067,12 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2023,11 +2097,12 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>finch79</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2052,11 +2127,12 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2081,11 +2157,12 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2110,6 +2187,7 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2139,11 +2217,12 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2168,11 +2247,12 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2197,11 +2277,12 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2226,11 +2307,12 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>finch79</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2255,11 +2337,12 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2284,11 +2367,12 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2313,11 +2397,12 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2342,6 +2427,7 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2371,11 +2457,12 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>Кесадилия</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2400,11 +2487,12 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Кесадилия</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2429,6 +2517,7 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B52">
@@ -2443,7 +2532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:U52">
+  <conditionalFormatting sqref="D2:V52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2457,7 +2546,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C52">
     <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="0">
-      <formula>18</formula>
+      <formula>19</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -540,17 +540,12 @@
           <t>Rank 18</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Rank 19</t>
-        </is>
-      </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Roman_Furtatov</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -559,12 +554,8 @@
       <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>0.395</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -580,13 +571,14 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="U3" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Roman_Furtatov</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -596,17 +588,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>0.544</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.003</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -621,12 +607,11 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -637,23 +622,13 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.027</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -665,12 +640,11 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -680,33 +654,17 @@
         <v>4</v>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>0.006</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -715,12 +673,11 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -733,26 +690,14 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" s="1" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -761,12 +706,11 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -778,53 +722,28 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" s="1" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="Q8" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -837,56 +756,27 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" s="1" t="n">
-        <v>0.012</v>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" s="1" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="V9" s="1" t="n">
-        <v>0.003</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -900,46 +790,21 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U10" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -958,51 +823,26 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>0.021</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" s="1" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="V11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1016,79 +856,46 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.063</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" s="1" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>0.862</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1097,16 +904,15 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1115,41 +921,22 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="L14" s="1" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>0.164</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" s="1" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>0.007</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1158,7 +945,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1170,49 +957,28 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L15" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="N15" s="1" t="n">
-        <v>0.07099999999999999</v>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="R15" s="1" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="S15" s="1" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T15" s="1" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="U15" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="V15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9989999999999999</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1224,51 +990,28 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L16" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="M16" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>0.036</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" s="1" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="U16" s="1" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>0.019</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1279,54 +1022,29 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="K17" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="L17" s="1" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>0.129</v>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" s="1" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S17" s="1" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="T17" s="1" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="U17" s="1" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="V17" s="1" t="n">
-        <v>0.03</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.9950000000000001</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1337,54 +1055,29 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="L18" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="M18" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N18" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O18" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="P18" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>0.168</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" s="1" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="T18" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="U18" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="V18" s="1" t="n">
-        <v>0.026</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1394,150 +1087,83 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K19" s="1" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="L19" s="1" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="M19" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="N19" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="O19" s="1" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="R19" s="1" t="n">
-        <v>0.022</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="T19" s="1" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="U19" s="1" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>0.08</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ПокерНЕок</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="C20" t="n">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Niko</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="R20" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="U20" s="1" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>0.277</v>
-      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Добросердечный</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="C21" s="2" t="n">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="n">
         <v>19</v>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>0.016</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1545,9 +1171,7 @@
           <t>Mihmbox</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>20</v>
       </c>
@@ -1564,34 +1188,19 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="R22" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="S22" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="T22" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="U22" s="1" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>0.146</v>
-      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Obscur</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>0.306</v>
-      </c>
+          <t>Vitos2049</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>21</v>
       </c>
@@ -1610,28 +1219,17 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>0.233</v>
-      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>0.217</v>
-      </c>
+          <t>Obscur</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>22</v>
       </c>
@@ -1651,15 +1249,8 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="U24" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="V24" s="1" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1667,9 +1258,7 @@
           <t>Amaney</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
-        <v>0.017</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>23</v>
       </c>
@@ -1691,19 +1280,14 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" s="1" t="n">
-        <v>0.017</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Сокол</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>0.003</v>
-      </c>
+          <t>sl1dbygad</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>24</v>
       </c>
@@ -1724,22 +1308,15 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="V26" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Пассажир</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>0.001</v>
-      </c>
+          <t>Викусик</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>25</v>
       </c>
@@ -1760,20 +1337,15 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>0.001</v>
-      </c>
+          <t>Сокол</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>26</v>
       </c>
@@ -1794,15 +1366,12 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1827,12 +1396,11 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1857,12 +1425,11 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1887,12 +1454,11 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1917,12 +1483,11 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1947,12 +1512,11 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1977,12 +1541,11 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -2007,12 +1570,11 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>TryFraiz</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2037,12 +1599,11 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2067,12 +1628,11 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2097,12 +1657,11 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2127,12 +1686,11 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2157,12 +1715,11 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2187,12 +1744,11 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2217,12 +1773,11 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2247,12 +1802,11 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>ЛЕНИН</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2277,12 +1831,11 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2307,12 +1860,11 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>finch79</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2337,12 +1889,11 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Комарик</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2367,12 +1918,11 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2397,12 +1947,11 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>finch79</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2427,12 +1976,11 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2457,12 +2005,11 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Кесадилия</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2487,12 +2034,11 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2517,7 +2063,6 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B52">
@@ -2532,7 +2077,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:V52">
+  <conditionalFormatting sqref="D2:U52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2546,7 +2091,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C52">
     <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="0">
-      <formula>19</formula>
+      <formula>18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:V52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -538,6 +538,11 @@
       <c r="U1" t="inlineStr">
         <is>
           <t>Rank 18</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Rank 19</t>
         </is>
       </c>
     </row>
@@ -574,11 +579,12 @@
       <c r="U3" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Roman_Furtatov</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -587,9 +593,7 @@
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -607,11 +611,14 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Roman_Furtatov</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -620,10 +627,10 @@
       <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="D5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -640,11 +647,12 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -654,10 +662,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="E6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -673,11 +681,12 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -688,10 +697,10 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="F7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -706,11 +715,12 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -722,10 +732,10 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="G8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -739,11 +749,12 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -756,10 +767,10 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -772,11 +783,12 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -790,10 +802,10 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="I10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -805,11 +817,12 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -824,10 +837,10 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="J11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -838,11 +851,12 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -858,10 +872,10 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="K12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -871,11 +885,12 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -892,10 +907,10 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="L13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -904,11 +919,12 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -926,10 +942,10 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -937,11 +953,12 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -960,21 +977,22 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="N15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -994,20 +1012,21 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1028,19 +1047,20 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="P17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1062,18 +1082,19 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -1096,17 +1117,18 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="R19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -1130,19 +1152,22 @@
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="S20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
       <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>Niko</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="C21" t="n">
         <v>19</v>
       </c>
@@ -1162,8 +1187,11 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="T21" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1193,6 +1221,7 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1222,6 +1251,7 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1251,6 +1281,7 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1280,6 +1311,7 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1309,6 +1341,7 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1338,6 +1371,7 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1367,6 +1401,7 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1396,6 +1431,7 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1425,6 +1461,7 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1454,6 +1491,7 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1483,6 +1521,7 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1512,6 +1551,7 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1541,6 +1581,7 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1570,6 +1611,7 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1599,6 +1641,7 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1628,6 +1671,7 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1657,6 +1701,7 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1686,6 +1731,7 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1715,6 +1761,7 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1744,6 +1791,7 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1773,6 +1821,7 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1802,6 +1851,7 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,6 +1881,7 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1860,6 +1911,7 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1889,6 +1941,7 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1918,6 +1971,7 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1947,6 +2001,7 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1976,6 +2031,7 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2005,6 +2061,7 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2034,6 +2091,7 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2063,6 +2121,7 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B52">
@@ -2077,7 +2136,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:U52">
+  <conditionalFormatting sqref="D2:V52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -540,17 +540,12 @@
           <t>Rank 18</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Rank 19</t>
-        </is>
-      </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>Rabie</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -579,12 +574,11 @@
       <c r="U3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -593,7 +587,9 @@
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -611,14 +607,11 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" s="1" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Roman_Furtatov</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -627,10 +620,10 @@
       <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -647,12 +640,11 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -662,10 +654,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -681,12 +673,11 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -697,10 +688,10 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -715,12 +706,11 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -732,10 +722,10 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -749,12 +739,11 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -767,10 +756,10 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -783,12 +772,11 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -802,10 +790,10 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -817,12 +805,11 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -837,10 +824,10 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -851,12 +838,11 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>dolMy</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -872,10 +858,10 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -885,12 +871,11 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -907,10 +892,10 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -919,12 +904,11 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -942,10 +926,10 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -953,12 +937,11 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -977,22 +960,21 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1012,21 +994,20 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Laches1</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1047,20 +1028,19 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1082,19 +1062,18 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -1117,18 +1096,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -1152,22 +1130,19 @@
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="U20" s="2" t="inlineStr"/>
-      <c r="V20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Niko</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>1</v>
-      </c>
+          <t>ksuhony</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>19</v>
       </c>
@@ -1187,16 +1162,13 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mihmbox</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1221,12 +1193,11 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>AlexBluff</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1251,12 +1222,11 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>emilian_s</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1281,12 +1251,11 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>sfv</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1311,12 +1280,11 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
+          <t>Julia_2499</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1341,12 +1309,11 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>gvrdkn</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1371,12 +1338,11 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>TryFraiz</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1401,12 +1367,11 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>1С</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1431,12 +1396,11 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>bogdanov</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1461,12 +1425,11 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Davit</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1491,12 +1454,11 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1521,12 +1483,11 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1551,12 +1512,11 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1581,12 +1541,11 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Alina_97</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1611,12 +1570,11 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TryFraiz</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1641,12 +1599,11 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Son_Ton</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1671,12 +1628,11 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Аннэтт</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1701,12 +1657,11 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>springbulk</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1731,12 +1686,11 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1761,12 +1715,11 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1791,12 +1744,11 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1821,12 +1773,11 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1851,12 +1802,11 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ЛЕНИН</t>
+          <t>.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1881,12 +1831,11 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>mflameee</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1911,12 +1860,11 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>Davydovpussy</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1941,12 +1889,11 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Комарик</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1971,12 +1918,11 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>mrCelviano</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2001,12 +1947,11 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>finch79</t>
+          <t>Gur4an</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2031,12 +1976,11 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Qrexi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2061,12 +2005,11 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2091,12 +2034,11 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Адольф</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2121,7 +2063,6 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B52">
@@ -2136,7 +2077,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:V52">
+  <conditionalFormatting sqref="D2:U52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:W52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -540,28 +540,54 @@
           <t>Rank 18</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Raw Top 18 Prob</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Sample Multiplier</t>
+        </is>
+      </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rabie</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="D3" s="1" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -571,32 +597,50 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" s="1" t="n">
-        <v>1</v>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" s="1" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>0.343</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -607,31 +651,55 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" s="1" t="n">
+        <v>0.127</v>
+      </c>
       <c r="E5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>0.298</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -640,114 +708,202 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="F6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>0.031</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>1</v>
+        <v>1.0989</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.017</v>
+      </c>
       <c r="G7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+        <v>0.125</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" s="1" t="n">
+        <v>1.998</v>
+      </c>
+      <c r="W7" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1</v>
+        <v>1.0989</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="E8" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.58</v>
+      </c>
       <c r="H8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+        <v>0.169</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="Q8" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" s="1" t="n">
+        <v>1.998</v>
+      </c>
+      <c r="W8" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>1</v>
+        <v>1.0934</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
@@ -755,23 +911,57 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.01</v>
+      </c>
       <c r="I9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+        <v>0.049</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -780,7 +970,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>1</v>
+        <v>1.089</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
@@ -788,32 +978,66 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="G10" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.139</v>
+      </c>
       <c r="J10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+        <v>0.351</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W10" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>лучший игрок</t>
+          <t>dolMy</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1</v>
+        <v>1.0791</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
@@ -822,31 +1046,63 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="H11" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0.183</v>
+      </c>
       <c r="K11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+        <v>0.227</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>1.962</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dolMy</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>1</v>
+        <v>1.056</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -856,30 +1112,60 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.091</v>
+      </c>
       <c r="L12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+        <v>0.14</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W12" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>1</v>
+        <v>1.0274</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -889,30 +1175,60 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="I13" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0.118</v>
+      </c>
       <c r="M13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+        <v>0.171</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>1.868</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>1</v>
+        <v>1.0065</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -922,30 +1238,60 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="I14" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.113</v>
+      </c>
       <c r="N14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+        <v>0.129</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>1</v>
+        <v>0.9603000000000002</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -955,30 +1301,60 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0.121</v>
+      </c>
       <c r="O15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>1.746</v>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>1</v>
+        <v>0.9195999999999999</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -989,20 +1365,48 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="J16" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0.094</v>
+      </c>
       <c r="P16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+        <v>0.116</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>1.672</v>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1011,7 +1415,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>1</v>
+        <v>0.9152000000000001</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1022,29 +1426,57 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="J17" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.105</v>
+      </c>
       <c r="Q17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+        <v>0.123</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>1.664</v>
+      </c>
+      <c r="W17" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>1</v>
+        <v>0.8084999999999999</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1055,20 +1487,48 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="J18" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
       <c r="R18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+        <v>0.092</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W18" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1077,7 +1537,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>1</v>
+        <v>0.7997000000000001</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1089,28 +1549,54 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="K19" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>0.079</v>
+      </c>
       <c r="S19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+        <v>0.11</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>1.454</v>
+      </c>
+      <c r="W19" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Rabie</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1</v>
+        <v>0.4356</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1123,18 +1609,42 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
+      <c r="L20" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>0.074</v>
+      </c>
       <c r="T20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" s="2" t="inlineStr"/>
+        <v>0.079</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1142,7 +1652,9 @@
           <t>ksuhony</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" s="1" t="n">
+        <v>0.4191</v>
+      </c>
       <c r="C21" t="n">
         <v>19</v>
       </c>
@@ -1154,16 +1666,42 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="L21" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="W21" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1171,7 +1709,9 @@
           <t>nesmotri_v_shelll1</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" s="1" t="n">
+        <v>0.3663000000000001</v>
+      </c>
       <c r="C22" t="n">
         <v>20</v>
       </c>
@@ -1183,16 +1723,42 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+      <c r="L22" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="W22" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1200,7 +1766,9 @@
           <t>AlexBluff</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" s="1" t="n">
+        <v>0.2959000000000001</v>
+      </c>
       <c r="C23" t="n">
         <v>21</v>
       </c>
@@ -1213,15 +1781,39 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="M23" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="W23" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1229,7 +1821,9 @@
           <t>emilian_s</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" s="1" t="n">
+        <v>0.2805</v>
+      </c>
       <c r="C24" t="n">
         <v>22</v>
       </c>
@@ -1243,22 +1837,46 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="N24" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q24" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="R24" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="W24" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sfv</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>Julia_2499</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>0.2222</v>
+      </c>
       <c r="C25" t="n">
         <v>23</v>
       </c>
@@ -1270,24 +1888,48 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="O25" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="Q25" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="V25" s="1" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Julia_2499</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>sfv</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>0.1947</v>
+      </c>
       <c r="C26" t="n">
         <v>24</v>
       </c>
@@ -1301,14 +1943,36 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="N26" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="Q26" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="W26" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1316,7 +1980,9 @@
           <t>gvrdkn</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" s="1" t="n">
+        <v>0.1782</v>
+      </c>
       <c r="C27" t="n">
         <v>25</v>
       </c>
@@ -1330,14 +1996,36 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="N27" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="Q27" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="W27" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1345,7 +2033,9 @@
           <t>TryFraiz</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" s="1" t="n">
+        <v>0.03850000000000001</v>
+      </c>
       <c r="C28" t="n">
         <v>26</v>
       </c>
@@ -1362,11 +2052,27 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+      <c r="Q28" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W28" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1374,7 +2080,9 @@
           <t>1С</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" s="1" t="n">
+        <v>0.007700000000000001</v>
+      </c>
       <c r="C29" t="n">
         <v>27</v>
       </c>
@@ -1391,19 +2099,35 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="Q29" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R29" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+      <c r="T29" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V29" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="W29" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bogdanov</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>Davit</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>0.0044</v>
+      </c>
       <c r="C30" t="n">
         <v>28</v>
       </c>
@@ -1423,16 +2147,28 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="T30" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V30" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="W30" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Davit</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>bogdanov</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>0.0033</v>
+      </c>
       <c r="C31" t="n">
         <v>29</v>
       </c>
@@ -1450,10 +2186,20 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+      <c r="R31" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="V31" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="W31" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1461,7 +2207,9 @@
           <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" s="1" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="C32" t="n">
         <v>30</v>
       </c>
@@ -1482,12 +2230,20 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V32" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="W32" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1512,11 +2268,15 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1541,11 +2301,15 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alina_97</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1570,11 +2334,15 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>Alina_97</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1599,11 +2367,15 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Son_Ton</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1628,11 +2400,15 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Аннэтт</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1657,11 +2433,15 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>springbulk</t>
+          <t>Gur4an</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1686,11 +2466,15 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>Аннэтт</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1715,11 +2499,15 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>Son_Ton</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1744,11 +2532,15 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1773,11 +2565,15 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>mflameee</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1802,11 +2598,15 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1831,11 +2631,15 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mflameee</t>
+          <t>mrCelviano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1860,11 +2664,15 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1889,11 +2697,15 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1918,11 +2730,15 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>mrCelviano</t>
+          <t>He3hAy</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1947,11 +2763,15 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gur4an</t>
+          <t>springbulk</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1976,11 +2796,15 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Qrexi</t>
+          <t>DARI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2005,11 +2829,15 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2034,11 +2862,15 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Адольф</t>
+          <t>Davydovpussy</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2063,6 +2895,10 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" s="1" t="n">
+        <v>0.55</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B52">
@@ -2077,7 +2913,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:U52">
+  <conditionalFormatting sqref="D2:W52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -540,16 +540,6 @@
           <t>Rank 18</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Raw Top 18 Prob</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Sample Multiplier</t>
-        </is>
-      </c>
     </row>
     <row r="2"/>
     <row r="3">
@@ -559,37 +549,37 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.53</v>
+        <v>0.515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.299</v>
+        <v>0.287</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.144</v>
+        <v>0.164</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="J3" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="K3" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -598,12 +588,6 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="W3" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,35 +596,33 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.343</v>
+        <v>0.372</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.391</v>
+        <v>0.394</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.221</v>
+        <v>0.186</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K4" s="1" t="n">
         <v>0.001</v>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -651,12 +633,6 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="W4" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -665,41 +641,37 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.298</v>
+        <v>0.3</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.457</v>
+        <v>0.467</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.067</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.025</v>
+        <v>0.028</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="L5" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -708,202 +680,174 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="W5" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="E6" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="K6" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.031</v>
-      </c>
       <c r="L6" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="M6" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="N6" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="W6" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>1.0989</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O7" s="1" t="n">
+      <c r="Q7" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" s="1" t="n">
-        <v>1.998</v>
-      </c>
-      <c r="W7" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1.0989</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.58</v>
+        <v>0.145</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.169</v>
+        <v>0.326</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.082</v>
+        <v>0.399</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.015</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.005</v>
+        <v>0.023</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" s="1" t="n">
-        <v>1.998</v>
-      </c>
-      <c r="W8" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>лучший игрок</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>1.0934</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
@@ -912,65 +856,59 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.049</v>
+        <v>0.12</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.256</v>
+        <v>0.364</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.264</v>
+        <v>0.219</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.162</v>
+        <v>0.102</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.093</v>
+        <v>0.062</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.06</v>
+        <v>0.029</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.024</v>
+        <v>0.017</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.015</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="R9" s="1" t="n">
         <v>0.01</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.003</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="V9" s="1" t="n">
-        <v>1.988</v>
-      </c>
-      <c r="W9" s="1" t="n">
-        <v>0.55</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G_rant_999</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>1.089</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
@@ -982,52 +920,46 @@
         <v>0.001</v>
       </c>
       <c r="H10" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="P10" s="1" t="n">
         <v>0.024</v>
       </c>
-      <c r="I10" s="1" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>0.012</v>
-      </c>
       <c r="Q10" s="1" t="n">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="T10" s="1" t="n">
         <v>0.007</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="V10" s="1" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W10" s="1" t="n">
-        <v>0.55</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="11">
@@ -1037,7 +969,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1.0791</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
@@ -1047,53 +979,47 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.039</v>
+        <v>0.031</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.183</v>
+        <v>0.191</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.227</v>
+        <v>0.266</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.203</v>
+        <v>0.18</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.111</v>
+        <v>0.094</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.061</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.046</v>
+        <v>0.049</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.027</v>
+        <v>0.018</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.022</v>
+        <v>0.016</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="U11" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="V11" s="1" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="W11" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1102,7 +1028,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>1.056</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1113,49 +1039,43 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.091</v>
+        <v>0.093</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.14</v>
+        <v>0.158</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.15</v>
+        <v>0.152</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.146</v>
+        <v>0.128</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.093</v>
+        <v>0.078</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.059</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.062</v>
+        <v>0.045</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.044</v>
+        <v>0.035</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W12" s="1" t="n">
-        <v>0.55</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13">
@@ -1165,7 +1085,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>1.0274</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1176,59 +1096,53 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.067</v>
+        <v>0.045</v>
       </c>
       <c r="L13" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="O13" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="M13" s="1" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0.117</v>
-      </c>
       <c r="P13" s="1" t="n">
-        <v>0.079</v>
+        <v>0.104</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.08</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="V13" s="1" t="n">
-        <v>1.868</v>
-      </c>
-      <c r="W13" s="1" t="n">
-        <v>0.55</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>1.0065</v>
+        <v>0.9790000000000002</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1238,60 +1152,52 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" s="1" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.026</v>
+        <v>0.023</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.077</v>
+        <v>0.056</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.113</v>
+        <v>0.114</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.129</v>
+        <v>0.111</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.124</v>
+        <v>0.115</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.119</v>
+        <v>0.11</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.092</v>
+        <v>0.107</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.06</v>
+        <v>0.075</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.046</v>
+        <v>0.049</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="V14" s="1" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W14" s="1" t="n">
-        <v>0.55</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9603000000000002</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1301,50 +1207,42 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.06</v>
+        <v>0.079</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.101</v>
+        <v>0.117</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.121</v>
+        <v>0.141</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.1</v>
+        <v>0.113</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.11</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.055</v>
+        <v>0.045</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="V15" s="1" t="n">
-        <v>1.746</v>
-      </c>
-      <c r="W15" s="1" t="n">
-        <v>0.55</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="16">
@@ -1354,7 +1252,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9195999999999999</v>
+        <v>0.9218000000000002</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1369,43 +1267,37 @@
         <v>0.002</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.005</v>
+        <v>0.017</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
       <c r="M16" s="1" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="U16" s="1" t="n">
         <v>0.046</v>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="U16" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>1.672</v>
-      </c>
-      <c r="W16" s="1" t="n">
-        <v>0.55</v>
       </c>
     </row>
     <row r="17">
@@ -1415,7 +1307,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9152000000000001</v>
+        <v>0.9075000000000002</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1430,53 +1322,47 @@
         <v>0.003</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.038</v>
+        <v>0.033</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.059</v>
+        <v>0.062</v>
       </c>
       <c r="N17" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="O17" s="1" t="n">
         <v>0.098</v>
       </c>
-      <c r="O17" s="1" t="n">
+      <c r="P17" s="1" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="Q17" s="1" t="n">
         <v>0.104</v>
       </c>
-      <c r="P17" s="1" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>0.123</v>
-      </c>
       <c r="R17" s="1" t="n">
-        <v>0.095</v>
+        <v>0.098</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.073</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.066</v>
+        <v>0.062</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="V17" s="1" t="n">
-        <v>1.664</v>
-      </c>
-      <c r="W17" s="1" t="n">
-        <v>0.55</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.8084999999999999</v>
+        <v>0.8392999999999999</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1488,56 +1374,50 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.026</v>
+        <v>0.051</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.059</v>
+        <v>0.048</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.094</v>
+        <v>0.106</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.105</v>
+        <v>0.113</v>
       </c>
       <c r="Q18" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="S18" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="R18" s="1" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>0.102</v>
-      </c>
       <c r="T18" s="1" t="n">
-        <v>0.081</v>
+        <v>0.075</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="V18" s="1" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W18" s="1" t="n">
-        <v>0.55</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.7997000000000001</v>
+        <v>0.7964</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1553,40 +1433,34 @@
         <v>0.008</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.046</v>
+        <v>0.031</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.066</v>
+        <v>0.054</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.093</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.089</v>
+        <v>0.077</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.078</v>
+        <v>0.109</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.079</v>
+        <v>0.096</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.11</v>
+        <v>0.095</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>1.454</v>
-      </c>
-      <c r="W19" s="1" t="n">
-        <v>0.55</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="20">
@@ -1596,7 +1470,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.4356</v>
+        <v>0.4455000000000001</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1609,51 +1483,43 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="3" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.02</v>
+        <v>0.037</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.043</v>
+        <v>0.035</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.061</v>
+        <v>0.056</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.079</v>
+        <v>0.075</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>0.55</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.4191</v>
+        <v>0.3927</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1667,50 +1533,44 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="N21" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="O21" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="O21" s="1" t="n">
-        <v>0.013</v>
-      </c>
       <c r="P21" s="1" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.033</v>
+        <v>0.028</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.066</v>
+        <v>0.057</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="W21" s="1" t="n">
-        <v>0.55</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.3663000000000001</v>
+        <v>0.3872</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1723,41 +1583,31 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M22" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.044</v>
+        <v>0.057</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.058</v>
+        <v>0.067</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="W22" s="1" t="n">
-        <v>0.55</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="23">
@@ -1767,7 +1617,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.2959000000000001</v>
+        <v>0.3069000000000001</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1781,38 +1631,30 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.031</v>
+        <v>0.025</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.039</v>
+        <v>0.028</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.051</v>
+        <v>0.055</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="W23" s="1" t="n">
-        <v>0.55</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="24">
@@ -1822,7 +1664,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.2805</v>
+        <v>0.2816</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1841,41 +1683,35 @@
         <v>0.002</v>
       </c>
       <c r="O24" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P24" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="P24" s="1" t="n">
-        <v>0.01</v>
-      </c>
       <c r="Q24" s="1" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.026</v>
+        <v>0.051</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.039</v>
+        <v>0.041</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.064</v>
+        <v>0.068</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="V24" s="1" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="W24" s="1" t="n">
-        <v>0.55</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Julia_2499</t>
+          <t>gvrdkn</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.2222</v>
+        <v>0.2002</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1888,47 +1724,39 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.006</v>
+        <v>0.016</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.038</v>
+        <v>0.026</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="V25" s="1" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="W25" s="1" t="n">
-        <v>0.55</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>Julia_2499</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.1947</v>
+        <v>0.1969</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1947,41 +1775,35 @@
         <v>0.001</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.023</v>
+        <v>0.016</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.038</v>
+        <v>0.034</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="V26" s="1" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="W26" s="1" t="n">
-        <v>0.55</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gvrdkn</t>
+          <t>sfv</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.1782</v>
+        <v>0.1881</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -2000,31 +1822,25 @@
         <v>0.001</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.032</v>
+        <v>0.05</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="W27" s="1" t="n">
-        <v>0.55</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="28">
@@ -2034,7 +1850,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.03850000000000001</v>
+        <v>0.05280000000000001</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -2050,28 +1866,24 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" s="1" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="O28" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="V28" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W28" s="1" t="n">
-        <v>0.55</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="29">
@@ -2081,7 +1893,7 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.007700000000000001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="C29" t="n">
         <v>27</v>
@@ -2099,34 +1911,28 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="T29" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="V29" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="W29" s="1" t="n">
-        <v>0.55</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Davit</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.0044</v>
+        <v>0.0011</v>
       </c>
       <c r="C30" t="n">
         <v>28</v>
@@ -2146,28 +1952,20 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" s="1" t="n">
+      <c r="S30" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="U30" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="V30" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="W30" s="1" t="n">
-        <v>0.55</v>
-      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bogdanov</t>
+          <t>Davit</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.0033</v>
+        <v>0.0011</v>
       </c>
       <c r="C31" t="n">
         <v>29</v>
@@ -2186,20 +1984,12 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" s="1" t="n">
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="V31" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="W31" s="1" t="n">
-        <v>0.55</v>
-      </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2207,9 +1997,7 @@
           <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
-        <v>0.0011</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>30</v>
       </c>
@@ -2230,20 +2018,12 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="V32" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="W32" s="1" t="n">
-        <v>0.55</v>
-      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>Davydovpussy</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -2268,15 +2048,11 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>Alina_97</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -2301,15 +2077,11 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>springbulk</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -2334,15 +2106,11 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alina_97</t>
+          <t>Son_Ton</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2367,15 +2135,11 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2400,15 +2164,11 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2433,15 +2193,11 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gur4an</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2466,15 +2222,11 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Аннэтт</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2499,15 +2251,11 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Son_Ton</t>
+          <t>Аннэтт</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2532,15 +2280,11 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>DARI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2565,10 +2309,6 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2598,15 +2338,11 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>bogdanov</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2631,15 +2367,11 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mrCelviano</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2664,10 +2396,6 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2697,15 +2425,11 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>Mar_u_shka</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2730,15 +2454,11 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>He3hAy</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2763,15 +2483,11 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>springbulk</t>
+          <t>mrCelviano</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2796,15 +2512,11 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DARI</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2829,15 +2541,11 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2862,15 +2570,11 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
+          <t>repe_kate</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2895,10 +2599,6 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" s="1" t="n">
-        <v>0.55</v>
-      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B52">
@@ -2913,7 +2613,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:W52">
+  <conditionalFormatting sqref="D2:U52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -545,41 +545,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.515</v>
+        <v>0.387</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.287</v>
+        <v>0.343</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.164</v>
+        <v>0.222</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.019</v>
+        <v>0.03</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -592,32 +592,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.372</v>
+        <v>0.11</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.394</v>
+        <v>0.333</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.186</v>
+        <v>0.455</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.033</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>0.001</v>
@@ -637,43 +637,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.112</v>
+        <v>0.001</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.3</v>
+        <v>0.013</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.467</v>
+        <v>0.134</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.507</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.028</v>
+        <v>0.201</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.016</v>
+        <v>0.108</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.004</v>
+        <v>0.024</v>
       </c>
       <c r="K5" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="L5" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -684,47 +692,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -739,49 +741,45 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>1</v>
+        <v>0.297702</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" s="1" t="n">
-        <v>0.031</v>
+        <v>0.026</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.217</v>
+        <v>0.216</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.408</v>
+        <v>0.403</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.261</v>
+        <v>0.272</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>0.048</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.015</v>
+        <v>0.022</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="Q7" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -794,48 +792,54 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1</v>
+        <v>0.2974040000000001</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.145</v>
+        <v>0.158</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.399</v>
+        <v>0.374</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>0.023</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>0.002</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="O8" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="P8" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q8" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -847,7 +851,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>1</v>
+        <v>0.296212</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
@@ -856,49 +860,49 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>0.019</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.12</v>
+        <v>0.127</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.364</v>
+        <v>0.388</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.219</v>
+        <v>0.189</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.102</v>
+        <v>0.096</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.029</v>
+        <v>0.041</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.017</v>
+        <v>0.022</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="10">
@@ -908,7 +912,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>1</v>
+        <v>0.2950200000000001</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
@@ -916,50 +920,48 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" s="1" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="T10" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="U10" s="1" t="n">
         <v>0.006</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="U10" s="1" t="n">
-        <v>0.004</v>
       </c>
     </row>
     <row r="11">
@@ -969,7 +971,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1</v>
+        <v>0.2941260000000001</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
@@ -982,43 +984,43 @@
         <v>0.004</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.031</v>
+        <v>0.041</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.191</v>
+        <v>0.168</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.266</v>
+        <v>0.252</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.18</v>
+        <v>0.217</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.094</v>
+        <v>0.107</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.049</v>
+        <v>0.052</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="12">
@@ -1028,7 +1030,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>1</v>
+        <v>0.281908</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1039,43 +1041,43 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="J12" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="U12" s="1" t="n">
         <v>0.022</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="13">
@@ -1085,7 +1087,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>1</v>
+        <v>0.2813120000000001</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1096,53 +1098,53 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.045</v>
+        <v>0.048</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.104</v>
+        <v>0.111</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.164</v>
+        <v>0.149</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.125</v>
+        <v>0.134</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.118</v>
+        <v>0.114</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.079</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.055</v>
+        <v>0.063</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.04</v>
+        <v>0.049</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.9790000000000002</v>
+        <v>0.268796</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -1154,50 +1156,50 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.056</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.114</v>
+        <v>0.124</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.111</v>
+        <v>0.126</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.115</v>
+        <v>0.122</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.11</v>
+        <v>0.104</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.107</v>
+        <v>0.091</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.078</v>
+        <v>0.091</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.075</v>
+        <v>0.055</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.2684980000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1209,50 +1211,50 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.021</v>
+        <v>0.031</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>0.117</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.141</v>
+        <v>0.125</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.113</v>
+        <v>0.103</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.079</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.048</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.045</v>
+        <v>0.062</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Laches1</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.9218000000000002</v>
+        <v>0.2488300000000001</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1262,52 +1264,54 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J16" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.031</v>
+        <v>0.039</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.057</v>
+        <v>0.06</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.108</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.103</v>
+        <v>0.113</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.101</v>
+        <v>0.107</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.113</v>
+        <v>0.116</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.107</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.095</v>
+        <v>0.068</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.079</v>
+        <v>0.064</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.046</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Laches1</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.9075000000000002</v>
+        <v>0.243466</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1319,40 +1323,40 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.013</v>
+        <v>0.008</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.097</v>
+        <v>0.078</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.098</v>
+        <v>0.094</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.114</v>
+        <v>0.105</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.104</v>
+        <v>0.11</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.098</v>
+        <v>0.112</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.093</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.062</v>
+        <v>0.075</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="18">
@@ -1362,7 +1366,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.8392999999999999</v>
+        <v>0.230056</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1374,40 +1378,40 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K18" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="K18" s="1" t="n">
-        <v>0.001</v>
-      </c>
       <c r="L18" s="1" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.051</v>
+        <v>0.034</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.048</v>
+        <v>0.061</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.106</v>
+        <v>0.083</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.113</v>
+        <v>0.104</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.097</v>
+        <v>0.105</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.097</v>
+        <v>0.112</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.075</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.064</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="19">
@@ -1417,7 +1421,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.7964</v>
+        <v>0.2190300000000001</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1428,39 +1432,41 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="K19" s="1" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.031</v>
+        <v>0.041</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.054</v>
+        <v>0.041</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.077</v>
+        <v>0.098</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.109</v>
+        <v>0.105</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.096</v>
+        <v>0.101</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.095</v>
+        <v>0.107</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.098</v>
+        <v>0.075</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.068</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1470,7 +1476,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.4455000000000001</v>
+        <v>0.12069</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1483,43 +1489,45 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="M20" s="3" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.037</v>
+        <v>0.027</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.035</v>
+        <v>0.044</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.076</v>
+        <v>0.058</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.075</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.096</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.3927</v>
+        <v>0.105194</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1532,45 +1540,43 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.057</v>
+        <v>0.048</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.081</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.3872</v>
+        <v>0.09476400000000003</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1584,12 +1590,14 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="N22" s="1" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="P22" s="1" t="n">
         <v>0.016</v>
@@ -1598,16 +1606,16 @@
         <v>0.033</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.057</v>
+        <v>0.04</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.067</v>
+        <v>0.061</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.076</v>
+        <v>0.061</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.095</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1617,7 +1625,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.3069000000000001</v>
+        <v>0.08612200000000002</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1631,30 +1639,32 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="N23" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.028</v>
+        <v>0.034</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.055</v>
+        <v>0.062</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.066</v>
+        <v>0.061</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="24">
@@ -1664,7 +1674,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.2816</v>
+        <v>0.073606</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1676,29 +1686,33 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="N24" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.051</v>
+        <v>0.032</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.041</v>
+        <v>0.047</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.068</v>
+        <v>0.065</v>
       </c>
       <c r="U24" s="1" t="n">
         <v>0.063</v>
@@ -1707,11 +1721,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gvrdkn</t>
+          <t>sfv</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.2002</v>
+        <v>0.055726</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1728,35 +1742,35 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="P25" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.021</v>
+        <v>0.028</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.026</v>
+        <v>0.029</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.046</v>
+        <v>0.054</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.067</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Julia_2499</t>
+          <t>gvrdkn</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.1969</v>
+        <v>0.049766</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1769,41 +1783,45 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="N26" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="O26" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P26" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="P26" s="1" t="n">
-        <v>0.01</v>
-      </c>
       <c r="Q26" s="1" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.047</v>
+        <v>0.043</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.056</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>Julia_2499</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.1881</v>
+        <v>0.04946800000000001</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1817,30 +1835,30 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="N27" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O27" s="1" t="n">
-        <v>0.003</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.023</v>
+        <v>0.031</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.05</v>
+        <v>0.039</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.056</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="28">
@@ -1850,7 +1868,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.05280000000000001</v>
+        <v>0.012814</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -1866,34 +1884,30 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P28" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="S28" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1С</t>
+          <t>Davit</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0005960000000000001</v>
       </c>
       <c r="C29" t="n">
         <v>27</v>
@@ -1912,27 +1926,23 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="T29" s="1" t="n">
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" s="1" t="n">
         <v>0.001</v>
-      </c>
-      <c r="U29" s="1" t="n">
-        <v>0.005</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.0011</v>
+        <v>0.000298</v>
       </c>
       <c r="C30" t="n">
         <v>28</v>
@@ -1952,20 +1962,20 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" s="1" t="n">
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Davit</t>
+          <t>1С</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.0011</v>
+        <v>0.000298</v>
       </c>
       <c r="C31" t="n">
         <v>29</v>
@@ -1985,19 +1995,21 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" s="1" t="n">
+      <c r="S31" s="1" t="n">
         <v>0.001</v>
       </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>bogdanov</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>0.000298</v>
+      </c>
       <c r="C32" t="n">
         <v>30</v>
       </c>
@@ -2017,13 +2029,15 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+      <c r="T32" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -2052,7 +2066,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alina_97</t>
+          <t>.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -2081,7 +2095,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>springbulk</t>
+          <t>Son_Ton</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -2110,7 +2124,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Son_Ton</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2139,7 +2153,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2168,7 +2182,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>Аннэтт</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2197,7 +2211,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>Alina_97</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2226,7 +2240,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2255,7 +2269,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Аннэтт</t>
+          <t>Davydovpussy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2284,7 +2298,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DARI</t>
+          <t>Qrexi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2313,7 +2327,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mflameee</t>
+          <t>Адольф</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2342,7 +2356,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bogdanov</t>
+          <t>DARI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2371,7 +2385,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2400,7 +2414,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2429,7 +2443,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mar_u_shka</t>
+          <t>Gur4an</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2458,7 +2472,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2487,7 +2501,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mrCelviano</t>
+          <t>springbulk</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2516,7 +2530,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>mrCelviano</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2545,7 +2559,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2574,7 +2588,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>repe_kate</t>
+          <t>He3hAy</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:U102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -545,661 +545,769 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0.298</v>
+        <v>0.376</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.387</v>
+        <v>0.005</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.343</v>
+        <v>0.058</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.222</v>
+        <v>0.131</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.03</v>
+        <v>0.28</v>
       </c>
       <c r="H3" s="1" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="N3" s="1" t="n">
         <v>0.011</v>
       </c>
-      <c r="I3" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J3" s="1" t="n">
+      <c r="O3" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="Q3" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="R3" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="T3" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0.298</v>
+        <v>0.376</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>0.11</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" s="1" t="n">
-        <v>0.333</v>
+        <v>0.001</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.455</v>
+        <v>0.008</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.031</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.022</v>
+        <v>0.106</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.179</v>
       </c>
       <c r="J4" s="1" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" s="1" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.298</v>
+        <v>0.374872</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.298</v>
+        <v>0.373744</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>0.502</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>0.309</v>
+        <v>0.001</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.154</v>
+        <v>0.014</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.01</v>
+        <v>0.061</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
+        <v>0.091</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0.127</v>
+      </c>
       <c r="K6" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+        <v>0.132</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.297702</v>
+        <v>0.365096</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" s="1" t="n">
-        <v>0.026</v>
-      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" s="1" t="n">
-        <v>0.216</v>
+        <v>0.006</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.403</v>
+        <v>0.011</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.272</v>
+        <v>0.039</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.022</v>
+        <v>0.101</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.006</v>
+        <v>0.123</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.003</v>
+        <v>0.137</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>0.129</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.113</v>
+      </c>
       <c r="P7" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.2974040000000001</v>
+        <v>0.361712</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.158</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" s="1" t="n">
-        <v>0.327</v>
+        <v>0.001</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.374</v>
+        <v>0.006</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.075</v>
+        <v>0.015</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.023</v>
+        <v>0.028</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.015</v>
+        <v>0.057</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.002</v>
+        <v>0.101</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.003</v>
+        <v>0.127</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.001</v>
+        <v>0.139</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.004</v>
+        <v>0.127</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.002</v>
+        <v>0.123</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G_rant_999</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.296212</v>
+        <v>0.298</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="D9" s="1" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.129</v>
+      </c>
       <c r="G9" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="P9" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0.008</v>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>лучший игрок</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.2950200000000001</v>
+        <v>0.298</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" s="1" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0.059</v>
+      </c>
       <c r="H10" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="P10" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="I10" s="1" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>0.027</v>
-      </c>
       <c r="Q10" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>0.007</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="T10" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="U10" s="1" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dolMy</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.2941260000000001</v>
+        <v>0.297702</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="D11" s="1" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>0.082</v>
+      </c>
       <c r="H11" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P11" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="I11" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>0.217</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>0.021</v>
-      </c>
       <c r="Q11" s="1" t="n">
-        <v>0.024</v>
+        <v>0.003</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.015</v>
+        <v>0.001</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.281908</v>
+        <v>0.2959140000000001</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="D12" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0.147</v>
+      </c>
       <c r="I12" s="1" t="n">
-        <v>0.001</v>
+        <v>0.139</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.017</v>
+        <v>0.111</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.078</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.147</v>
+        <v>0.064</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.148</v>
+        <v>0.045</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.13</v>
+        <v>0.033</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.135</v>
+        <v>0.029</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.08</v>
+        <v>0.025</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.076</v>
+        <v>0.015</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.049</v>
+        <v>0.011</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.036</v>
+        <v>0.011</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0.022</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.2813120000000001</v>
+        <v>0.293232</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0.097</v>
+      </c>
       <c r="I13" s="1" t="n">
-        <v>0.001</v>
+        <v>0.094</v>
       </c>
       <c r="J13" s="1" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S13" s="1" t="n">
         <v>0.019</v>
       </c>
-      <c r="K13" s="1" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>0.049</v>
-      </c>
       <c r="T13" s="1" t="n">
-        <v>0.042</v>
+        <v>0.012</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.03</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>nk_telller</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.268796</v>
+        <v>0.29055</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="E14" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0.116</v>
+      </c>
       <c r="J14" s="1" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="U14" s="1" t="n">
         <v>0.005</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="L14" s="1" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="N14" s="1" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>0.042</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>ustayonmymind</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.2684980000000001</v>
+        <v>0.2795240000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -1208,43 +1316,47 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>0.016</v>
+      </c>
       <c r="J15" s="1" t="n">
-        <v>0.002</v>
+        <v>0.04</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.031</v>
+        <v>0.053</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.078</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.117</v>
+        <v>0.108</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.125</v>
+        <v>0.131</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.103</v>
+        <v>0.143</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.112</v>
+        <v>0.108</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.083</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.049</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.062</v>
+        <v>0.042</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.033</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="16">
@@ -1254,7 +1366,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.2488300000000001</v>
+        <v>0.271472</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
@@ -1263,55 +1375,55 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="H16" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.039</v>
+        <v>0.013</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.06</v>
+        <v>0.033</v>
       </c>
       <c r="N16" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="Q16" s="1" t="n">
         <v>0.108</v>
       </c>
-      <c r="O16" s="1" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>0.116</v>
-      </c>
       <c r="R16" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.108</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.068</v>
+        <v>0.108</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.064</v>
+        <v>0.082</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.058</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.243466</v>
+        <v>0.251214</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1321,52 +1433,54 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J17" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.024</v>
+        <v>0.031</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.059</v>
+        <v>0.043</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.078</v>
+        <v>0.066</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.094</v>
+        <v>0.081</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.105</v>
+        <v>0.121</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.11</v>
+        <v>0.137</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.112</v>
+        <v>0.117</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.093</v>
+        <v>0.104</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.075</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.058</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Lancelot</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.230056</v>
+        <v>0.247936</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1376,52 +1490,54 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J18" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.016</v>
+        <v>0.03</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.034</v>
+        <v>0.05</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.061</v>
+        <v>0.073</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.083</v>
+        <v>0.093</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.104</v>
+        <v>0.131</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.105</v>
+        <v>0.115</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.112</v>
+        <v>0.098</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.099</v>
+        <v>0.089</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.068</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>dolMy</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.2190300000000001</v>
+        <v>0.208004</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1432,51 +1548,47 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K19" s="1" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" s="1" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.041</v>
+        <v>0.014</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.041</v>
+        <v>0.028</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.078</v>
+        <v>0.045</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.098</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.105</v>
+        <v>0.112</v>
       </c>
       <c r="R19" s="1" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="T19" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="S19" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="T19" s="1" t="n">
-        <v>0.075</v>
-      </c>
       <c r="U19" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Rabie</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.12069</v>
+        <v>0.152656</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1490,44 +1602,44 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M20" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="M20" s="3" t="n">
-        <v>0.006</v>
-      </c>
       <c r="N20" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.044</v>
+        <v>0.033</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.058</v>
+        <v>0.065</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.093</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.102</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>gvrdkn</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.105194</v>
+        <v>0.12596</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1539,44 +1651,46 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="Q21" s="1" t="n">
         <v>0.027</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.095</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>danalanaaa</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.09476400000000003</v>
+        <v>0.11473</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1590,42 +1704,40 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O22" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="O22" s="1" t="n">
-        <v>0.012</v>
-      </c>
       <c r="P22" s="1" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.04</v>
+        <v>0.056</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.061</v>
+        <v>0.073</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.061</v>
+        <v>0.097</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AlexBluff</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.08612200000000002</v>
+        <v>0.108174</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1640,41 +1752,41 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="N23" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.034</v>
+        <v>0.042</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.062</v>
+        <v>0.073</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.061</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.076</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>emilian_s</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.073606</v>
+        <v>0.09059200000000003</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1686,46 +1798,40 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="1" t="n">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" s="1" t="n">
         <v>0.002</v>
-      </c>
-      <c r="N24" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="O24" s="1" t="n">
-        <v>0.006</v>
       </c>
       <c r="P24" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.032</v>
+        <v>0.051</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.047</v>
+        <v>0.05</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.065</v>
+        <v>0.079</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.063</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>AlexBluff</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.055726</v>
+        <v>0.07582861841488138</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1741,36 +1847,26 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="P25" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="R25" s="1" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="S25" s="1" t="n">
-        <v>0.029</v>
-      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" s="1" t="n">
-        <v>0.054</v>
+        <v>0.06361461276416222</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.061</v>
+        <v>0.1908438382924867</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gvrdkn</t>
+          <t>emilian_s</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.049766</v>
+        <v>0.07459564796542284</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1783,45 +1879,29 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M26" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N26" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O26" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P26" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q26" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="R26" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="S26" s="1" t="n">
-        <v>0.036</v>
-      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" s="1" t="n">
-        <v>0.043</v>
+        <v>0.06258024158173056</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.046</v>
+        <v>0.1877407247451917</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Julia_2499</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.04946800000000001</v>
+        <v>0.07336943360318099</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1835,40 +1915,34 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N27" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" s="1" t="n">
-        <v>0.008</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" s="1" t="n">
-        <v>0.012</v>
+        <v>0.006206877807499379</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.02</v>
+        <v>0.01241375561499876</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.031</v>
+        <v>0.05379294099832794</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.039</v>
+        <v>0.06413773734416024</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.053</v>
+        <v>0.1096548412658223</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TryFraiz</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.012814</v>
+        <v>0.0721500127594341</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -1887,27 +1961,25 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" s="1" t="n">
-        <v>0.005</v>
+        <v>0.05380314150591654</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.016</v>
+        <v>0.08070471225887481</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.02</v>
+        <v>0.1076062830118331</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Davit</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.0005960000000000001</v>
+        <v>0.07093742349459842</v>
       </c>
       <c r="C29" t="n">
         <v>27</v>
@@ -1928,21 +2000,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
+        <v>0.04760900905677745</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>0.0952180181135549</v>
+      </c>
       <c r="U29" s="1" t="n">
-        <v>0.001</v>
+        <v>0.0952180181135549</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.000298</v>
+        <v>0.06973170451605233</v>
       </c>
       <c r="C30" t="n">
         <v>28</v>
@@ -1961,21 +2035,27 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+      <c r="R30" s="1" t="n">
+        <v>0.008999961863197256</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>0.04049982838438764</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>0.08549963770037391</v>
+      </c>
       <c r="U30" s="1" t="n">
-        <v>0.001</v>
+        <v>0.0989995804951698</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1С</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.000298</v>
+        <v>0.0685328951966757</v>
       </c>
       <c r="C31" t="n">
         <v>29</v>
@@ -1996,19 +2076,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+        <v>0.06075611276301036</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>0.06075611276301036</v>
+      </c>
+      <c r="U31" s="1" t="n">
+        <v>0.06075611276301036</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bogdanov</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.000298</v>
+        <v>0.06734103559414174</v>
       </c>
       <c r="C32" t="n">
         <v>30</v>
@@ -2026,21 +2110,31 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="Q32" s="1" t="n">
+        <v>0.008581390994071241</v>
+      </c>
+      <c r="R32" s="1" t="n">
+        <v>0.0200232456528329</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>0.02860463664690414</v>
+      </c>
       <c r="T32" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U32" t="inlineStr"/>
+        <v>0.07723251894664118</v>
+      </c>
+      <c r="U32" s="1" t="n">
+        <v>0.09153483727009325</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Suruchik</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>Rabie</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>0.0661561664710008</v>
+      </c>
       <c r="C33" t="n">
         <v>31</v>
       </c>
@@ -2060,16 +2154,22 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="T33" s="1" t="n">
+        <v>0.05550013965687986</v>
+      </c>
+      <c r="U33" s="1" t="n">
+        <v>0.1665004189706396</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>mflameee</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>0.06380756636387483</v>
+      </c>
       <c r="C34" t="n">
         <v>32</v>
       </c>
@@ -2090,15 +2190,19 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" s="1" t="n">
+        <v>0.06380756636387483</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Son_Ton</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>Davit</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>0.06264392062208754</v>
+      </c>
       <c r="C35" t="n">
         <v>33</v>
       </c>
@@ -2119,15 +2223,19 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+      <c r="U35" s="1" t="n">
+        <v>0.06264392062208754</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>БОЛЬШОЙ МИХА</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>0.06148743589051903</v>
+      </c>
       <c r="C36" t="n">
         <v>34</v>
       </c>
@@ -2148,15 +2256,19 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="1" t="n">
+        <v>0.06148743589051903</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Yars</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>Yrs</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>0.06033815678821391</v>
+      </c>
       <c r="C37" t="n">
         <v>35</v>
       </c>
@@ -2177,15 +2289,19 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" s="1" t="n">
+        <v>0.06033815678821391</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Аннэтт</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>Julia_2499</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>0.05919612877881077</v>
+      </c>
       <c r="C38" t="n">
         <v>36</v>
       </c>
@@ -2206,15 +2322,19 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="1" t="n">
+        <v>0.1986447274456737</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alina_97</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>Настя дай стек</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>0.05806139819752901</v>
+      </c>
       <c r="C39" t="n">
         <v>37</v>
       </c>
@@ -2232,18 +2352,28 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="R39" s="1" t="n">
+        <v>0.01187835478672852</v>
+      </c>
+      <c r="S39" s="1" t="n">
+        <v>0.01187835478672852</v>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>0.04751341914691408</v>
+      </c>
+      <c r="U39" s="1" t="n">
+        <v>0.08314848350709965</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cordell</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>TryFraiz</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>0.05693401227937889</v>
+      </c>
       <c r="C40" t="n">
         <v>38</v>
       </c>
@@ -2264,15 +2394,19 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" s="1" t="n">
+        <v>0.05693401227937889</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>1С</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>0.05581401918866635</v>
+      </c>
       <c r="C41" t="n">
         <v>39</v>
       </c>
@@ -2293,15 +2427,19 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" s="1" t="n">
+        <v>0.05581401918866635</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Qrexi</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>Yars</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>0.05470146804987068</v>
+      </c>
       <c r="C42" t="n">
         <v>40</v>
       </c>
@@ -2322,15 +2460,19 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
+      <c r="U42" s="1" t="n">
+        <v>0.05470146804987068</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Адольф</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>bogdanov</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>0.05359640897997774</v>
+      </c>
       <c r="C43" t="n">
         <v>41</v>
       </c>
@@ -2351,15 +2493,19 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+      <c r="U43" s="1" t="n">
+        <v>0.05359640897997774</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DARI</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>Son_Ton</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>0.05249889312235841</v>
+      </c>
       <c r="C44" t="n">
         <v>42</v>
       </c>
@@ -2380,15 +2526,19 @@
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="U44" s="1" t="n">
+        <v>0.05249889312235841</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Никита</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>Serg</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>0.05140897268228851</v>
+      </c>
       <c r="C45" t="n">
         <v>43</v>
       </c>
@@ -2409,15 +2559,19 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" s="1" t="n">
+        <v>0.05140897268228851</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Retbin</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>Davydovpussy</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>0.05032670096421398</v>
+      </c>
       <c r="C46" t="n">
         <v>44</v>
       </c>
@@ -2438,15 +2592,19 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
+      <c r="U46" s="1" t="n">
+        <v>0.05032670096421398</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Gur4an</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>mrCelviano</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>0.04925213241087281</v>
+      </c>
       <c r="C47" t="n">
         <v>45</v>
       </c>
@@ -2467,15 +2625,19 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
+      <c r="U47" s="1" t="n">
+        <v>0.04925213241087281</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>0.04818532264439485</v>
+      </c>
       <c r="C48" t="n">
         <v>46</v>
       </c>
@@ -2496,15 +2658,19 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
+      <c r="U48" s="1" t="n">
+        <v>0.04818532264439485</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>springbulk</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>FireSnail</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>0.04712632850950954</v>
+      </c>
       <c r="C49" t="n">
         <v>47</v>
       </c>
@@ -2525,15 +2691,19 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
+      <c r="U49" s="1" t="n">
+        <v>0.04712632850950954</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>mrCelviano</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>sfv</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>0.04607520811900299</v>
+      </c>
       <c r="C50" t="n">
         <v>48</v>
       </c>
@@ -2554,15 +2724,19 @@
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
+      <c r="U50" s="1" t="n">
+        <v>0.04607520811900299</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>Alina_97</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>0.04503202090157695</v>
+      </c>
       <c r="C51" t="n">
         <v>49</v>
       </c>
@@ -2583,15 +2757,19 @@
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
+      <c r="U51" s="1" t="n">
+        <v>0.04503202090157695</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>He3hAy</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>Ryumon_Hozukimaruu</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>0.04399682765227547</v>
+      </c>
       <c r="C52" t="n">
         <v>50</v>
       </c>
@@ -2612,10 +2790,1662 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
+      <c r="U52" s="1" t="n">
+        <v>0.04399682765227547</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Никитос</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>0.04296969058565925</v>
+      </c>
+      <c r="C53" t="n">
+        <v>51</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" s="1" t="n">
+        <v>0.04296969058565925</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Suruchik</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>0.04195067339192299</v>
+      </c>
+      <c r="C54" t="n">
+        <v>52</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" s="1" t="n">
+        <v>0.04195067339192299</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DARI</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>0.04093984129616881</v>
+      </c>
+      <c r="C55" t="n">
+        <v>53</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" s="1" t="n">
+        <v>0.04093984129616881</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ajolana</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>0.03993726112106739</v>
+      </c>
+      <c r="C56" t="n">
+        <v>54</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" s="1" t="n">
+        <v>0.03993726112106739</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>springbulk</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>0.03894300135316024</v>
+      </c>
+      <c r="C57" t="n">
+        <v>55</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" s="1" t="n">
+        <v>0.03894300135316024</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Викусик</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>0.03795713221307947</v>
+      </c>
+      <c r="C58" t="n">
+        <v>56</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" s="1" t="n">
+        <v>0.03795713221307947</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Retbin</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>0.03697972572998796</v>
+      </c>
+      <c r="C59" t="n">
+        <v>57</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" s="1" t="n">
+        <v>0.03697972572998796</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Никита</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>0.03601085582057174</v>
+      </c>
+      <c r="C60" t="n">
+        <v>58</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" s="1" t="n">
+        <v>0.03601085582057174</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>He3hAy</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>0.03505059837294876</v>
+      </c>
+      <c r="C61" t="n">
+        <v>59</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" s="1" t="n">
+        <v>0.03505059837294876</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Mar_u_shka</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>0.0340990313358949</v>
+      </c>
+      <c r="C62" t="n">
+        <v>60</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" s="1" t="n">
+        <v>0.0340990313358949</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Qrexi</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>0.03315623481382806</v>
+      </c>
+      <c r="C63" t="n">
+        <v>61</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" s="1" t="n">
+        <v>0.03315623481382806</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Gur4an</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>0.03222229116803758</v>
+      </c>
+      <c r="C64" t="n">
+        <v>62</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" s="1" t="n">
+        <v>0.03222229116803758</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>lubashley</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>0.03129728512469662</v>
+      </c>
+      <c r="C65" t="n">
+        <v>63</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" s="1" t="n">
+        <v>0.03129728512469662</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>szrvi</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>0.03038130389025371</v>
+      </c>
+      <c r="C66" t="n">
+        <v>64</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" s="1" t="n">
+        <v>0.03038130389025371</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Аннэтт</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>0.02947443727486424</v>
+      </c>
+      <c r="C67" t="n">
+        <v>65</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" s="1" t="n">
+        <v>0.02947443727486424</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ромчик</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>0.02857677782459717</v>
+      </c>
+      <c r="C68" t="n">
+        <v>66</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" s="1" t="n">
+        <v>0.02857677782459717</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Стич</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>0.02768842096323552</v>
+      </c>
+      <c r="C69" t="n">
+        <v>67</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" s="1" t="n">
+        <v>0.02768842096323552</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Chesters</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>0.02680946514458487</v>
+      </c>
+      <c r="C70" t="n">
+        <v>68</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" s="1" t="n">
+        <v>0.02680946514458487</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>0.02594001201631272</v>
+      </c>
+      <c r="C71" t="n">
+        <v>69</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" s="1" t="n">
+        <v>0.02594001201631272</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Адольф</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>0.02508016659646623</v>
+      </c>
+      <c r="C72" t="n">
+        <v>70</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" s="1" t="n">
+        <v>0.02508016659646623</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>sasha12039</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>0.02423003746395818</v>
+      </c>
+      <c r="C73" t="n">
+        <v>71</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" s="1" t="n">
+        <v>0.02423003746395818</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>avveev</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>0.02338973696447539</v>
+      </c>
+      <c r="C74" t="n">
+        <v>72</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" s="1" t="n">
+        <v>0.02338973696447539</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>imt360_ATDK</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>0.02255938143345327</v>
+      </c>
+      <c r="C75" t="n">
+        <v>73</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" s="1" t="n">
+        <v>0.02255938143345327</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>twewefe</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>0.02173909143797955</v>
+      </c>
+      <c r="C76" t="n">
+        <v>74</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" s="1" t="n">
+        <v>0.02173909143797955</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Schwepp1S</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>0.02092899203974462</v>
+      </c>
+      <c r="C77" t="n">
+        <v>75</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" s="1" t="n">
+        <v>0.02092899203974462</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>repe_kate</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>0.02012921308145349</v>
+      </c>
+      <c r="C78" t="n">
+        <v>76</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" s="1" t="n">
+        <v>0.02012921308145349</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STG</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>0.01933988949946142</v>
+      </c>
+      <c r="C79" t="n">
+        <v>77</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" s="1" t="n">
+        <v>0.01933988949946142</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>artyomkalina</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>0.01856116166580371</v>
+      </c>
+      <c r="C80" t="n">
+        <v>78</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" s="1" t="n">
+        <v>0.01856116166580371</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>kornaakov</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>0.01779317576327163</v>
+      </c>
+      <c r="C81" t="n">
+        <v>79</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" s="1" t="n">
+        <v>0.01779317576327163</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>3y6a</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>0.01703608419775665</v>
+      </c>
+      <c r="C82" t="n">
+        <v>80</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" s="1" t="n">
+        <v>0.01703608419775665</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Fara</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>0.01629004605276425</v>
+      </c>
+      <c r="C83" t="n">
+        <v>81</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" s="1" t="n">
+        <v>0.01629004605276425</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Ruslan1</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>0.0155552275918099</v>
+      </c>
+      <c r="C84" t="n">
+        <v>82</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" s="1" t="n">
+        <v>0.0155552275918099</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>elli</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>0.01483180281538541</v>
+      </c>
+      <c r="C85" t="n">
+        <v>83</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" s="1" t="n">
+        <v>0.01483180281538541</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>lifechampagne</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>0.01411995408036231</v>
+      </c>
+      <c r="C86" t="n">
+        <v>84</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" s="1" t="n">
+        <v>0.01411995408036231</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>juliezh</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>0.01341987279113142</v>
+      </c>
+      <c r="C87" t="n">
+        <v>85</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" s="1" t="n">
+        <v>0.01341987279113142</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Yandi</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>0.01273176017352867</v>
+      </c>
+      <c r="C88" t="n">
+        <v>86</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" s="1" t="n">
+        <v>0.01273176017352867</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>OlgaaGeorgieva</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>0.01205582814475193</v>
+      </c>
+      <c r="C89" t="n">
+        <v>87</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" s="1" t="n">
+        <v>0.01205582814475193</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>John Fisher</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>0.01139230029514338</v>
+      </c>
+      <c r="C90" t="n">
+        <v>88</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" s="1" t="n">
+        <v>0.01139230029514338</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Vitos2049</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>0.01074141300104382</v>
+      </c>
+      <c r="C91" t="n">
+        <v>89</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" s="1" t="n">
+        <v>0.01074141300104382</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Настя дай ребай блат</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>0.010103416692117</v>
+      </c>
+      <c r="C92" t="n">
+        <v>90</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" s="1" t="n">
+        <v>0.010103416692117</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>avomerfe</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>0.009478577301860172</v>
+      </c>
+      <c r="C93" t="n">
+        <v>91</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" s="1" t="n">
+        <v>0.009478577301860172</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>frida_hk</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>0.008867177936824802</v>
+      </c>
+      <c r="C94" t="n">
+        <v>92</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" s="1" t="n">
+        <v>0.008867177936824802</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>etovadikk</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>0.0082695208088751</v>
+      </c>
+      <c r="C95" t="n">
+        <v>93</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" s="1" t="n">
+        <v>0.0082695208088751</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>veronesss</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>0.007685929486314879</v>
+      </c>
+      <c r="C96" t="n">
+        <v>94</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" s="1" t="n">
+        <v>0.007685929486314879</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>dance_with_vlad</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>0.007116751534922361</v>
+      </c>
+      <c r="C97" t="n">
+        <v>95</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" s="1" t="n">
+        <v>0.007116751534922361</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Leomane</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>0.006562361640294801</v>
+      </c>
+      <c r="C98" t="n">
+        <v>96</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" s="1" t="n">
+        <v>0.006562361640294801</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>katerina_boc</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>0.006023165330549357</v>
+      </c>
+      <c r="C99" t="n">
+        <v>97</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" s="1" t="n">
+        <v>0.006023165330549357</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>kuromi</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>0.005499603456534434</v>
+      </c>
+      <c r="C100" t="n">
+        <v>98</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" s="1" t="n">
+        <v>0.005499603456534434</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>0.004992157640133424</v>
+      </c>
+      <c r="C101" t="n">
+        <v>99</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" s="1" t="n">
+        <v>0.004992157640133424</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Tim19</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>0.004501356977571467</v>
+      </c>
+      <c r="C102" t="n">
+        <v>100</v>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" s="1" t="n">
+        <v>0.004501356977571467</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B52">
+  <conditionalFormatting sqref="B2:B102">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2627,7 +4457,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:U52">
+  <conditionalFormatting sqref="D2:U102">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2639,7 +4469,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C52">
+  <conditionalFormatting sqref="C3:C102">
     <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="0">
       <formula>18</formula>
     </cfRule>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -545,189 +545,173 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0.376</v>
+        <v>0.454</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.005</v>
+        <v>0.967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.058</v>
+        <v>0.02</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.131</v>
+        <v>0.007</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0.178</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" s="1" t="n">
-        <v>0.11</v>
+        <v>0.001</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="Q3" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="R3" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="T3" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0.376</v>
+        <v>0.4530919999999999</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" s="1" t="n">
+        <v>0.007</v>
+      </c>
       <c r="E4" s="1" t="n">
-        <v>0.001</v>
+        <v>0.258</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.008</v>
+        <v>0.175</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.031</v>
+        <v>0.15</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.106</v>
+        <v>0.074</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.179</v>
+        <v>0.062</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.191</v>
+        <v>0.043</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.169</v>
+        <v>0.051</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0.133</v>
+        <v>0.054</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>0.082</v>
+        <v>0.039</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>0.062</v>
+        <v>0.032</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>0.018</v>
       </c>
       <c r="P4" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="Q4" s="1" t="n">
         <v>0.011</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>0.003</v>
       </c>
       <c r="R4" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="T4" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="U4" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.374872</v>
+        <v>0.4530919999999999</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="S5" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
       <c r="T5" s="1" t="n">
         <v>0.001</v>
       </c>
@@ -736,808 +720,860 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>лучший игрок</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.373744</v>
+        <v>0.452638</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.025</v>
+        <v>0.04</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.061</v>
+        <v>0.075</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.091</v>
+        <v>0.08</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.127</v>
+        <v>0.151</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.132</v>
+        <v>0.145</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.149</v>
+        <v>0.123</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>0.104</v>
+        <v>0.083</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>0.061</v>
+        <v>0.066</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="T6" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.365096</v>
+        <v>0.44492</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0.023</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.042</v>
+      </c>
       <c r="G7" s="1" t="n">
-        <v>0.006</v>
+        <v>0.047</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.011</v>
+        <v>0.081</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.039</v>
+        <v>0.076</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.05</v>
+        <v>0.091</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.101</v>
+        <v>0.089</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.123</v>
+        <v>0.089</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.137</v>
+        <v>0.081</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.129</v>
+        <v>0.081</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.113</v>
+        <v>0.089</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.09</v>
+        <v>0.056</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.073</v>
+        <v>0.053</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.046</v>
+        <v>0.028</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.023</v>
+        <v>0.031</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.361712</v>
+        <v>0.37412</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="D8" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.138</v>
+      </c>
       <c r="H8" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="T8" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="I8" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="Q8" s="1" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>0.041</v>
-      </c>
       <c r="U8" s="1" t="n">
-        <v>0.03</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.298</v>
+        <v>0.373744</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.499</v>
+        <v>0.003</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>0.257</v>
+        <v>0.104</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.129</v>
+        <v>0.121</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.046</v>
+        <v>0.098</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.022</v>
+        <v>0.1</v>
       </c>
       <c r="I9" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="T9" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="K9" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.298</v>
+        <v>0.367728</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>0.352</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" s="1" t="n">
-        <v>0.31</v>
+        <v>0.017</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.167</v>
+        <v>0.047</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.032</v>
+        <v>0.076</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.016</v>
+        <v>0.083</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.014</v>
+        <v>0.081</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.013</v>
+        <v>0.091</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.011</v>
+        <v>0.08</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.008</v>
+        <v>0.078</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0.004</v>
+        <v>0.078</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0.003</v>
+        <v>0.053</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <v>0.049</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>0.036</v>
+      </c>
       <c r="S10" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+        <v>0.018</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>0.012</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.297702</v>
+        <v>0.356824</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>0.137</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>0.314</v>
+        <v>0.007</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.289</v>
+        <v>0.016</v>
       </c>
       <c r="G11" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="O11" s="1" t="n">
         <v>0.082</v>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="K11" s="1" t="n">
+      <c r="P11" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <v>0.016</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>0.002</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.2959140000000001</v>
+        <v>0.355696</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="E12" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="U12" s="1" t="n">
         <v>0.022</v>
       </c>
-      <c r="F12" s="1" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>emilian_s</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.293232</v>
+        <v>0.350056</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" s="1" t="n">
+        <v>0.017</v>
+      </c>
       <c r="F13" s="1" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.097</v>
+        <v>0.046</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.094</v>
+        <v>0.068</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.116</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.125</v>
+        <v>0.056</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>0.112</v>
+        <v>0.081</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.106</v>
+        <v>0.081</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>0.075</v>
+        <v>0.078</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0.077</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>0.047</v>
+        <v>0.078</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.028</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.02</v>
+        <v>0.041</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.019</v>
+        <v>0.043</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.012</v>
+        <v>0.041</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.006</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nk_telller</t>
+          <t>Чека-чека</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.29055</v>
+        <v>0.34968</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" s="1" t="n">
+        <v>0.005</v>
+      </c>
       <c r="E14" s="1" t="n">
-        <v>0.002</v>
+        <v>0.099</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.019</v>
+        <v>0.08</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.073</v>
+        <v>0.091</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.097</v>
+        <v>0.066</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.116</v>
+        <v>0.067</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.122</v>
+        <v>0.054</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.121</v>
+        <v>0.059</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.08</v>
+        <v>0.061</v>
       </c>
       <c r="N14" s="1" t="n">
         <v>0.063</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.074</v>
+        <v>0.056</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.038</v>
+        <v>0.048</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.026</v>
+        <v>0.047</v>
       </c>
       <c r="R14" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="S14" s="1" t="n">
         <v>0.021</v>
       </c>
-      <c r="S14" s="1" t="n">
+      <c r="T14" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="T14" s="1" t="n">
+      <c r="U14" s="1" t="n">
         <v>0.012</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>0.005</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ustayonmymind</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.2795240000000001</v>
+        <v>0.348928</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0.065</v>
+      </c>
       <c r="H15" s="1" t="n">
-        <v>0.011</v>
+        <v>0.067</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.016</v>
+        <v>0.057</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.04</v>
+        <v>0.058</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.053</v>
+        <v>0.075</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.108</v>
+        <v>0.076</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.131</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.143</v>
+        <v>0.06</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.108</v>
+        <v>0.067</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.043</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.062</v>
+        <v>0.051</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.049</v>
+        <v>0.031</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.042</v>
+        <v>0.027</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Laches1</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.271472</v>
+        <v>0.326744</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="E16" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>0.036</v>
+      </c>
       <c r="H16" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>0.042</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.058</v>
+      </c>
       <c r="J16" s="1" t="n">
-        <v>0.003</v>
+        <v>0.047</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.005</v>
+        <v>0.055</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.013</v>
+        <v>0.051</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.033</v>
+        <v>0.065</v>
       </c>
       <c r="N16" s="1" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="T16" s="1" t="n">
         <v>0.045</v>
       </c>
-      <c r="O16" s="1" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>0.082</v>
-      </c>
       <c r="U16" s="1" t="n">
-        <v>0.074</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G_rant_999</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.251214</v>
+        <v>0.295912</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="L17" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="M17" s="1" t="n">
         <v>0.031</v>
       </c>
-      <c r="M17" s="1" t="n">
-        <v>0.043</v>
-      </c>
       <c r="N17" s="1" t="n">
-        <v>0.066</v>
+        <v>0.055</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0.081</v>
+        <v>0.065</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>0.121</v>
+        <v>0.082</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.137</v>
+        <v>0.102</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.117</v>
+        <v>0.128</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.104</v>
+        <v>0.109</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.044</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lancelot</t>
+          <t>turkoid</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.247936</v>
+        <v>0.250792</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="E18" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>0.014</v>
+      </c>
       <c r="I18" s="1" t="n">
-        <v>0.001</v>
+        <v>0.018</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="L18" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="M18" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="M18" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="N18" s="1" t="n">
-        <v>0.073</v>
+        <v>0.038</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.093</v>
+        <v>0.065</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.131</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.115</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.098</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.089</v>
+        <v>0.077</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.055</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dolMy</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.208004</v>
+        <v>0.236504</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1546,49 +1582,57 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="H19" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L19" s="1" t="n">
-        <v>0.004</v>
+        <v>0.012</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0.014</v>
+        <v>0.023</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.028</v>
+        <v>0.038</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.045</v>
+        <v>0.051</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.112</v>
+        <v>0.09</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.109</v>
+        <v>0.095</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.126</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.101</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.152656</v>
+        <v>0.198152</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
@@ -1597,49 +1641,55 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="H20" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="K20" s="3" t="n">
+        <v>0.002</v>
+      </c>
       <c r="L20" s="3" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.021</v>
+        <v>0.042</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.033</v>
+        <v>0.077</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.055</v>
+        <v>0.08</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.065</v>
+        <v>0.081</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.093</v>
+        <v>0.089</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.12</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gvrdkn</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.12596</v>
+        <v>0.124832</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1651,46 +1701,44 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.05</v>
+        <v>0.037</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.058</v>
+        <v>0.068</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.075</v>
+        <v>0.081</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>danalanaaa</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.11473</v>
+        <v>0.120764</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1706,38 +1754,38 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O22" s="1" t="n">
         <v>0.001</v>
-      </c>
-      <c r="O22" s="1" t="n">
-        <v>0.006</v>
       </c>
       <c r="P22" s="1" t="n">
         <v>0.014</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.03</v>
+        <v>0.019</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.056</v>
+        <v>0.033</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.073</v>
+        <v>0.046</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.097</v>
+        <v>0.067</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.108</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>by_twentyseven</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.108174</v>
+        <v>0.117412</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
@@ -1748,45 +1796,49 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="M23" s="1" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>0.007</v>
+        <v>0.018</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>0.016</v>
+        <v>0.036</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.025</v>
+        <v>0.032</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.042</v>
+        <v>0.048</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.073</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.111</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.09059200000000003</v>
+        <v>0.098512</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1796,42 +1848,52 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="L24" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="O24" s="1" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.02</v>
+        <v>0.026</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.05</v>
+        <v>0.044</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.079</v>
+        <v>0.042</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.093</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AlexBluff</t>
+          <t>Похороное бюро «улыбка»</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.07582861841488138</v>
+        <v>0.06705000000000001</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1841,32 +1903,44 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+      <c r="O25" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="Q25" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>0.051</v>
+      </c>
       <c r="T25" s="1" t="n">
-        <v>0.06361461276416222</v>
+        <v>0.058</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.1908438382924867</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>emilian_s</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.07459564796542284</v>
+        <v>0.05112393125925473</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1881,27 +1955,39 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+      <c r="N26" s="1" t="n">
+        <v>0.00312569890310924</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>0.00156284945155462</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <v>0.00156284945155462</v>
+      </c>
+      <c r="Q26" s="1" t="n">
+        <v>0.00312569890310924</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>0.007814247257773101</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>0.02969413957953778</v>
+      </c>
       <c r="T26" s="1" t="n">
-        <v>0.06258024158173056</v>
+        <v>0.04063408574042012</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.1877407247451917</v>
+        <v>0.04844833299819322</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.07336943360318099</v>
+        <v>0.04722243547402335</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1920,29 +2006,29 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" s="1" t="n">
-        <v>0.006206877807499379</v>
+        <v>0.006977310205972716</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.01241375561499876</v>
+        <v>0.01162885034328786</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.05379294099832794</v>
+        <v>0.03488655102986358</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.06413773734416024</v>
+        <v>0.02558347075523329</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.1096548412658223</v>
+        <v>0.04651540137315144</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.0721500127594341</v>
+        <v>0.04683799349314793</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -1962,24 +2048,20 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" s="1" t="n">
-        <v>0.05380314150591654</v>
-      </c>
-      <c r="T28" s="1" t="n">
-        <v>0.08070471225887481</v>
-      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" s="1" t="n">
-        <v>0.1076062830118331</v>
+        <v>0.103167386548784</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>swapblet</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.07093742349459842</v>
+        <v>0.04645460047045818</v>
       </c>
       <c r="C29" t="n">
         <v>27</v>
@@ -1999,24 +2081,20 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" s="1" t="n">
-        <v>0.04760900905677745</v>
-      </c>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" s="1" t="n">
-        <v>0.0952180181135549</v>
-      </c>
-      <c r="U29" s="1" t="n">
-        <v>0.0952180181135549</v>
-      </c>
+        <v>0.1235494693363249</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.06973170451605233</v>
+        <v>0.04607225928378138</v>
       </c>
       <c r="C30" t="n">
         <v>28</v>
@@ -2033,29 +2111,31 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" s="1" t="n">
+        <v>0.005834885927530571</v>
+      </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" s="1" t="n">
-        <v>0.008999961863197256</v>
+        <v>0.005834885927530571</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0.04049982838438764</v>
+        <v>0.01750465778259171</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.08549963770037391</v>
+        <v>0.03500931556518343</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.0989995804951698</v>
+        <v>0.05834885927530571</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.0685328951966757</v>
+        <v>0.04569097283476169</v>
       </c>
       <c r="C31" t="n">
         <v>29</v>
@@ -2075,24 +2155,20 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" s="1" t="n">
-        <v>0.06075611276301036</v>
-      </c>
-      <c r="T31" s="1" t="n">
-        <v>0.06075611276301036</v>
-      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" s="1" t="n">
-        <v>0.06075611276301036</v>
+        <v>0.04569097283476169</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.06734103559414174</v>
+        <v>0.04531074404919047</v>
       </c>
       <c r="C32" t="n">
         <v>30</v>
@@ -2110,30 +2186,22 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" s="1" t="n">
-        <v>0.008581390994071241</v>
-      </c>
-      <c r="R32" s="1" t="n">
-        <v>0.0200232456528329</v>
-      </c>
-      <c r="S32" s="1" t="n">
-        <v>0.02860463664690414</v>
-      </c>
-      <c r="T32" s="1" t="n">
-        <v>0.07723251894664118</v>
-      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" s="1" t="n">
-        <v>0.09153483727009325</v>
+        <v>0.04531074404919047</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rabie</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.0661561664710008</v>
+        <v>0.0449315758773431</v>
       </c>
       <c r="C33" t="n">
         <v>31</v>
@@ -2155,20 +2223,20 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" s="1" t="n">
-        <v>0.05550013965687986</v>
+        <v>0.04948411440236025</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.1665004189706396</v>
+        <v>0.04948411440236025</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mflameee</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.06380756636387483</v>
+        <v>0.04455347129432236</v>
       </c>
       <c r="C34" t="n">
         <v>32</v>
@@ -2188,20 +2256,24 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+      <c r="S34" s="1" t="n">
+        <v>0.02616943982045366</v>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>0.01962707986534025</v>
+      </c>
       <c r="U34" s="1" t="n">
-        <v>0.06380756636387483</v>
+        <v>0.05233887964090733</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Davit</t>
+          <t>Julia_2499</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.06264392062208754</v>
+        <v>0.0441764333004086</v>
       </c>
       <c r="C35" t="n">
         <v>33</v>
@@ -2217,24 +2289,36 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+      <c r="O35" s="1" t="n">
+        <v>0.002216802152770404</v>
+      </c>
+      <c r="P35" s="1" t="n">
+        <v>0.004433604305540808</v>
+      </c>
+      <c r="Q35" s="1" t="n">
+        <v>0.008867208611081616</v>
+      </c>
+      <c r="R35" s="1" t="n">
+        <v>0.006650406458311211</v>
+      </c>
+      <c r="S35" s="1" t="n">
+        <v>0.01330081291662242</v>
+      </c>
+      <c r="T35" s="1" t="n">
+        <v>0.02881842798601525</v>
+      </c>
       <c r="U35" s="1" t="n">
-        <v>0.06264392062208754</v>
+        <v>0.05320325166648969</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
+          <t>mary_muse7</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>0.06148743589051903</v>
+        <v>0.04380046492141694</v>
       </c>
       <c r="C36" t="n">
         <v>34</v>
@@ -2253,21 +2337,27 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="R36" s="1" t="n">
+        <v>0.02261252706319924</v>
+      </c>
+      <c r="S36" s="1" t="n">
+        <v>0.02261252706319924</v>
+      </c>
+      <c r="T36" s="1" t="n">
+        <v>0.03391879059479886</v>
+      </c>
       <c r="U36" s="1" t="n">
-        <v>0.06148743589051903</v>
+        <v>0.06783758118959772</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Yrs</t>
+          <t>KidPoker</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>0.06033815678821391</v>
+        <v>0.04342556920906147</v>
       </c>
       <c r="C37" t="n">
         <v>35</v>
@@ -2284,23 +2374,33 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="P37" s="1" t="n">
+        <v>0.009963992246672739</v>
+      </c>
+      <c r="Q37" s="1" t="n">
+        <v>0.00498199612333637</v>
+      </c>
+      <c r="R37" s="1" t="n">
+        <v>0.0161914874008432</v>
+      </c>
+      <c r="S37" s="1" t="n">
+        <v>0.02490998061668185</v>
+      </c>
+      <c r="T37" s="1" t="n">
+        <v>0.03611947189418868</v>
+      </c>
       <c r="U37" s="1" t="n">
-        <v>0.06033815678821391</v>
+        <v>0.05355645832586597</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Julia_2499</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>0.05919612877881077</v>
+        <v>0.04305174924132686</v>
       </c>
       <c r="C38" t="n">
         <v>36</v>
@@ -2323,17 +2423,17 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" s="1" t="n">
-        <v>0.1986447274456737</v>
+        <v>0.04305174924132686</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>szrvi</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>0.05806139819752901</v>
+        <v>0.04267900812284747</v>
       </c>
       <c r="C39" t="n">
         <v>37</v>
@@ -2349,30 +2449,34 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" s="1" t="n">
+        <v>0.003330654606122013</v>
+      </c>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" s="1" t="n">
+        <v>0.003330654606122013</v>
+      </c>
       <c r="R39" s="1" t="n">
-        <v>0.01187835478672852</v>
+        <v>0.003330654606122013</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>0.01187835478672852</v>
+        <v>0.01665327303061006</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>0.04751341914691408</v>
+        <v>0.02997589145509811</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.08314848350709965</v>
+        <v>0.08659701975917232</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TryFraiz</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>0.05693401227937889</v>
+        <v>0.04230734898529415</v>
       </c>
       <c r="C40" t="n">
         <v>38</v>
@@ -2395,17 +2499,17 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" s="1" t="n">
-        <v>0.05693401227937889</v>
+        <v>0.1125195451736546</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1С</t>
+          <t>gvrdkn</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>0.05581401918866635</v>
+        <v>0.04193677498776889</v>
       </c>
       <c r="C41" t="n">
         <v>39</v>
@@ -2428,17 +2532,17 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" s="1" t="n">
-        <v>0.05581401918866635</v>
+        <v>0.04193677498776889</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>bogdanov</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>0.05470146804987068</v>
+        <v>0.0415672893172077</v>
       </c>
       <c r="C42" t="n">
         <v>40</v>
@@ -2461,17 +2565,17 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" s="1" t="n">
-        <v>0.05470146804987068</v>
+        <v>0.0415672893172077</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bogdanov</t>
+          <t>dzhemus</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>0.05359640897997774</v>
+        <v>0.04119889518879176</v>
       </c>
       <c r="C43" t="n">
         <v>41</v>
@@ -2490,21 +2594,25 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
+      <c r="R43" s="1" t="n">
+        <v>0.02304188768948084</v>
+      </c>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
+      <c r="T43" s="1" t="n">
+        <v>0.02304188768948084</v>
+      </c>
       <c r="U43" s="1" t="n">
-        <v>0.05359640897997774</v>
+        <v>0.09216755075792338</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Son_Ton</t>
+          <t>Nolekri</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>0.05249889312235841</v>
+        <v>0.04083159584636702</v>
       </c>
       <c r="C44" t="n">
         <v>42</v>
@@ -2527,17 +2635,17 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" s="1" t="n">
-        <v>0.05249889312235841</v>
+        <v>0.04083159584636702</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>duy27</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>0.05140897268228851</v>
+        <v>0.04046539456287284</v>
       </c>
       <c r="C45" t="n">
         <v>43</v>
@@ -2560,17 +2668,17 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" s="1" t="n">
-        <v>0.05140897268228851</v>
+        <v>0.04046539456287284</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>0.05032670096421398</v>
+        <v>0.03973629941253434</v>
       </c>
       <c r="C46" t="n">
         <v>44</v>
@@ -2593,17 +2701,17 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" s="1" t="n">
-        <v>0.05032670096421398</v>
+        <v>0.03973629941253434</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mrCelviano</t>
+          <t>Лудоданя</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>0.04925213241087281</v>
+        <v>0.03937341224101946</v>
       </c>
       <c r="C47" t="n">
         <v>45</v>
@@ -2626,17 +2734,17 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" s="1" t="n">
-        <v>0.04925213241087281</v>
+        <v>0.03937341224101946</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>0.04818532264439485</v>
+        <v>0.03901163652001634</v>
       </c>
       <c r="C48" t="n">
         <v>46</v>
@@ -2659,17 +2767,17 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" s="1" t="n">
-        <v>0.04818532264439485</v>
+        <v>0.03901163652001634</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FireSnail</t>
+          <t>Ташкент</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>0.04712632850950954</v>
+        <v>0.03865097567468272</v>
       </c>
       <c r="C49" t="n">
         <v>47</v>
@@ -2692,17 +2800,17 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" s="1" t="n">
-        <v>0.04712632850950954</v>
+        <v>0.03865097567468272</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>artyomkalina</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>0.04607520811900299</v>
+        <v>0.0382914331620389</v>
       </c>
       <c r="C50" t="n">
         <v>48</v>
@@ -2725,17 +2833,17 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" s="1" t="n">
-        <v>0.04607520811900299</v>
+        <v>0.0382914331620389</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alina_97</t>
+          <t>Bereza</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>0.04503202090157695</v>
+        <v>0.03793301247146485</v>
       </c>
       <c r="C51" t="n">
         <v>49</v>
@@ -2758,17 +2866,17 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" s="1" t="n">
-        <v>0.04503202090157695</v>
+        <v>0.03793301247146485</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>Комар</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>0.04399682765227547</v>
+        <v>0.0375757171252082</v>
       </c>
       <c r="C52" t="n">
         <v>50</v>
@@ -2791,17 +2899,17 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" s="1" t="n">
-        <v>0.04399682765227547</v>
+        <v>0.0375757171252082</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>FreSko</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>0.04296969058565925</v>
+        <v>0.03721955067890352</v>
       </c>
       <c r="C53" t="n">
         <v>51</v>
@@ -2824,17 +2932,17 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" s="1" t="n">
-        <v>0.04296969058565925</v>
+        <v>0.03721955067890352</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>z9</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>0.04195067339192299</v>
+        <v>0.03686451672210309</v>
       </c>
       <c r="C54" t="n">
         <v>52</v>
@@ -2857,17 +2965,17 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" s="1" t="n">
-        <v>0.04195067339192299</v>
+        <v>0.03686451672210309</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DARI</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>0.04093984129616881</v>
+        <v>0.03651061887881965</v>
       </c>
       <c r="C55" t="n">
         <v>53</v>
@@ -2886,21 +2994,23 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
+      <c r="R55" s="1" t="n">
+        <v>0.04855135489204741</v>
+      </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" s="1" t="n">
-        <v>0.04093984129616881</v>
+        <v>0.04855135489204741</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ajolana</t>
+          <t>sl1dbygad</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>0.03993726112106739</v>
+        <v>0.03615786080808129</v>
       </c>
       <c r="C56" t="n">
         <v>54</v>
@@ -2923,17 +3033,17 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" s="1" t="n">
-        <v>0.03993726112106739</v>
+        <v>0.03615786080808129</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>springbulk</t>
+          <t>Татьяна Юрьевна Р.</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>0.03894300135316024</v>
+        <v>0.03580624620449899</v>
       </c>
       <c r="C57" t="n">
         <v>55</v>
@@ -2956,17 +3066,17 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" s="1" t="n">
-        <v>0.03894300135316024</v>
+        <v>0.03580624620449899</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>3y6a</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>0.03795713221307947</v>
+        <v>0.03545577879884717</v>
       </c>
       <c r="C58" t="n">
         <v>56</v>
@@ -2989,17 +3099,17 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" s="1" t="n">
-        <v>0.03795713221307947</v>
+        <v>0.03545577879884717</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>Deroz</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>0.03697972572998796</v>
+        <v>0.03510646235865738</v>
       </c>
       <c r="C59" t="n">
         <v>57</v>
@@ -3022,17 +3132,17 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" s="1" t="n">
-        <v>0.03697972572998796</v>
+        <v>0.03510646235865738</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>GodЗИЛLa</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>0.03601085582057174</v>
+        <v>0.03475830068882603</v>
       </c>
       <c r="C60" t="n">
         <v>58</v>
@@ -3055,17 +3165,17 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" s="1" t="n">
-        <v>0.03601085582057174</v>
+        <v>0.03475830068882603</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>He3hAy</t>
+          <t>MAKKSMIR</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>0.03505059837294876</v>
+        <v>0.03441129763223605</v>
       </c>
       <c r="C61" t="n">
         <v>59</v>
@@ -3088,17 +3198,17 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" s="1" t="n">
-        <v>0.03505059837294876</v>
+        <v>0.03441129763223605</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mar_u_shka</t>
+          <t>sasha12039</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>0.0340990313358949</v>
+        <v>0.03406545707039319</v>
       </c>
       <c r="C62" t="n">
         <v>60</v>
@@ -3121,17 +3231,17 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" s="1" t="n">
-        <v>0.0340990313358949</v>
+        <v>0.03406545707039319</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Qrexi</t>
+          <t>Maza</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>0.03315623481382806</v>
+        <v>0.0337207829240774</v>
       </c>
       <c r="C63" t="n">
         <v>61</v>
@@ -3154,17 +3264,17 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" s="1" t="n">
-        <v>0.03315623481382806</v>
+        <v>0.0337207829240774</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Gur4an</t>
+          <t>Rabie</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>0.03222229116803758</v>
+        <v>0.03337727915400955</v>
       </c>
       <c r="C64" t="n">
         <v>62</v>
@@ -3187,17 +3297,17 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" s="1" t="n">
-        <v>0.03222229116803758</v>
+        <v>0.03337727915400955</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>lubashley</t>
+          <t>wasapmaaan</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>0.03129728512469662</v>
+        <v>0.03303494976153436</v>
       </c>
       <c r="C65" t="n">
         <v>63</v>
@@ -3220,17 +3330,17 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" s="1" t="n">
-        <v>0.03129728512469662</v>
+        <v>0.03303494976153436</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>szrvi</t>
+          <t>AlexBluff</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>0.03038130389025371</v>
+        <v>0.03269379878931949</v>
       </c>
       <c r="C66" t="n">
         <v>64</v>
@@ -3253,17 +3363,17 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" s="1" t="n">
-        <v>0.03038130389025371</v>
+        <v>0.03269379878931949</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Аннэтт</t>
+          <t>vovaa_25</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>0.02947443727486424</v>
+        <v>0.0323538303220718</v>
       </c>
       <c r="C67" t="n">
         <v>65</v>
@@ -3286,17 +3396,17 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" s="1" t="n">
-        <v>0.02947443727486424</v>
+        <v>0.0323538303220718</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ромчик</t>
+          <t>dunkaeva</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>0.02857677782459717</v>
+        <v>0.03201504848727102</v>
       </c>
       <c r="C68" t="n">
         <v>66</v>
@@ -3319,17 +3429,17 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" s="1" t="n">
-        <v>0.02857677782459717</v>
+        <v>0.03201504848727102</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Стич</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>0.02768842096323552</v>
+        <v>0.03167745745592151</v>
       </c>
       <c r="C69" t="n">
         <v>67</v>
@@ -3352,17 +3462,17 @@
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" s="1" t="n">
-        <v>0.02768842096323552</v>
+        <v>0.03167745745592151</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>FISHer</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>0.02680946514458487</v>
+        <v>0.03134106144332265</v>
       </c>
       <c r="C70" t="n">
         <v>68</v>
@@ -3385,17 +3495,17 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" s="1" t="n">
-        <v>0.02680946514458487</v>
+        <v>0.03134106144332265</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>0.02594001201631272</v>
+        <v>0.03100586470985838</v>
       </c>
       <c r="C71" t="n">
         <v>69</v>
@@ -3418,17 +3528,17 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" s="1" t="n">
-        <v>0.02594001201631272</v>
+        <v>0.03100586470985838</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Адольф</t>
+          <t>Leomane</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>0.02508016659646623</v>
+        <v>0.03067187156180675</v>
       </c>
       <c r="C72" t="n">
         <v>70</v>
@@ -3451,17 +3561,17 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" s="1" t="n">
-        <v>0.02508016659646623</v>
+        <v>0.03067187156180675</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>sasha12039</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>0.02423003746395818</v>
+        <v>0.03033908635216977</v>
       </c>
       <c r="C73" t="n">
         <v>71</v>
@@ -3484,17 +3594,17 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" s="1" t="n">
-        <v>0.02423003746395818</v>
+        <v>0.03033908635216977</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>avveev</t>
+          <t>Kichatov</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>0.02338973696447539</v>
+        <v>0.03000751348152453</v>
       </c>
       <c r="C74" t="n">
         <v>72</v>
@@ -3517,17 +3627,17 @@
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" s="1" t="n">
-        <v>0.02338973696447539</v>
+        <v>0.03000751348152453</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>imt360_ATDK</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>0.02255938143345327</v>
+        <v>0.02967715739889623</v>
       </c>
       <c r="C75" t="n">
         <v>73</v>
@@ -3550,17 +3660,17 @@
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" s="1" t="n">
-        <v>0.02255938143345327</v>
+        <v>0.02967715739889623</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>twewefe</t>
+          <t>Laches1</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>0.02173909143797955</v>
+        <v>0.0293480226026537</v>
       </c>
       <c r="C76" t="n">
         <v>74</v>
@@ -3581,19 +3691,19 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" s="1" t="n">
-        <v>0.02173909143797955</v>
-      </c>
+      <c r="T76" s="1" t="n">
+        <v>0.07805325160280238</v>
+      </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Schwepp1S</t>
+          <t>Holmes</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>0.02092899203974462</v>
+        <v>0.0290201136414283</v>
       </c>
       <c r="C77" t="n">
         <v>75</v>
@@ -3616,17 +3726,17 @@
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" s="1" t="n">
-        <v>0.02092899203974462</v>
+        <v>0.0290201136414283</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>repe_kate</t>
+          <t>TryFraiz</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>0.02012921308145349</v>
+        <v>0.02869343511505701</v>
       </c>
       <c r="C78" t="n">
         <v>76</v>
@@ -3649,17 +3759,17 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" s="1" t="n">
-        <v>0.02012921308145349</v>
+        <v>0.02869343511505701</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STG</t>
+          <t>Катала</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>0.01933988949946142</v>
+        <v>0.0283679916755504</v>
       </c>
       <c r="C79" t="n">
         <v>77</v>
@@ -3682,17 +3792,17 @@
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
       <c r="U79" s="1" t="n">
-        <v>0.01933988949946142</v>
+        <v>0.0283679916755504</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>artyomkalina</t>
+          <t>kuromi</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>0.01856116166580371</v>
+        <v>0.02804378802808648</v>
       </c>
       <c r="C80" t="n">
         <v>78</v>
@@ -3715,17 +3825,17 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
       <c r="U80" s="1" t="n">
-        <v>0.01856116166580371</v>
+        <v>0.02804378802808648</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kornaakov</t>
+          <t>ustayonmymind</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>0.01779317576327163</v>
+        <v>0.02772082893203124</v>
       </c>
       <c r="C81" t="n">
         <v>79</v>
@@ -3748,17 +3858,17 @@
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
       <c r="U81" s="1" t="n">
-        <v>0.01779317576327163</v>
+        <v>0.02772082893203124</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3y6a</t>
+          <t>Кубус</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>0.01703608419775665</v>
+        <v>0.02739911920198678</v>
       </c>
       <c r="C82" t="n">
         <v>80</v>
@@ -3781,17 +3891,17 @@
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" s="1" t="n">
-        <v>0.01703608419775665</v>
+        <v>0.02739911920198678</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Fara</t>
+          <t>ajolana</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>0.01629004605276425</v>
+        <v>0.02707866370886813</v>
       </c>
       <c r="C83" t="n">
         <v>81</v>
@@ -3814,17 +3924,17 @@
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" s="1" t="n">
-        <v>0.01629004605276425</v>
+        <v>0.02707866370886813</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ruslan1</t>
+          <t>Катальня</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>0.0155552275918099</v>
+        <v>0.02675946738100961</v>
       </c>
       <c r="C84" t="n">
         <v>82</v>
@@ -3847,17 +3957,17 @@
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
       <c r="U84" s="1" t="n">
-        <v>0.0155552275918099</v>
+        <v>0.02675946738100961</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>elli</t>
+          <t>Chimedaschool1</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>0.01483180281538541</v>
+        <v>0.02644153520530191</v>
       </c>
       <c r="C85" t="n">
         <v>83</v>
@@ -3880,17 +3990,17 @@
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
       <c r="U85" s="1" t="n">
-        <v>0.01483180281538541</v>
+        <v>0.02644153520530191</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>lifechampagne</t>
+          <t>МВика</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>0.01411995408036231</v>
+        <v>0.02612487222836092</v>
       </c>
       <c r="C86" t="n">
         <v>84</v>
@@ -3913,17 +4023,17 @@
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
       <c r="U86" s="1" t="n">
-        <v>0.01411995408036231</v>
+        <v>0.02612487222836092</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>juliezh</t>
+          <t>lethalpresence</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>0.01341987279113142</v>
+        <v>0.02580948355772955</v>
       </c>
       <c r="C87" t="n">
         <v>85</v>
@@ -3946,17 +4056,17 @@
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" s="1" t="n">
-        <v>0.01341987279113142</v>
+        <v>0.02580948355772955</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Yandi</t>
+          <t>витя доезд</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>0.01273176017352867</v>
+        <v>0.02549537436311357</v>
       </c>
       <c r="C88" t="n">
         <v>86</v>
@@ -3979,17 +4089,17 @@
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" s="1" t="n">
-        <v>0.01273176017352867</v>
+        <v>0.02549537436311357</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OlgaaGeorgieva</t>
+          <t>Бутербродский</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>0.01205582814475193</v>
+        <v>0.02518254987765292</v>
       </c>
       <c r="C89" t="n">
         <v>87</v>
@@ -4012,17 +4122,17 @@
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
       <c r="U89" s="1" t="n">
-        <v>0.01205582814475193</v>
+        <v>0.02518254987765292</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>John Fisher</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>0.01139230029514338</v>
+        <v>0.02487101539922969</v>
       </c>
       <c r="C90" t="n">
         <v>88</v>
@@ -4045,17 +4155,17 @@
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
       <c r="U90" s="1" t="n">
-        <v>0.01139230029514338</v>
+        <v>0.02487101539922969</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>0.01074141300104382</v>
+        <v>0.02456077629181419</v>
       </c>
       <c r="C91" t="n">
         <v>89</v>
@@ -4078,17 +4188,17 @@
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
       <c r="U91" s="1" t="n">
-        <v>0.01074141300104382</v>
+        <v>0.02456077629181419</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Настя дай ребай блат</t>
+          <t>dolMy</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>0.010103416692117</v>
+        <v>0.02425183798685053</v>
       </c>
       <c r="C92" t="n">
         <v>90</v>
@@ -4111,17 +4221,17 @@
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
       <c r="U92" s="1" t="n">
-        <v>0.010103416692117</v>
+        <v>0.02425183798685053</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>avomerfe</t>
+          <t>Sabina</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>0.009478577301860172</v>
+        <v>0.02394420598468314</v>
       </c>
       <c r="C93" t="n">
         <v>91</v>
@@ -4144,17 +4254,17 @@
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" s="1" t="n">
-        <v>0.009478577301860172</v>
+        <v>0.02394420598468314</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>frida_hk</t>
+          <t>Maxim</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>0.008867177936824802</v>
+        <v>0.02363788585602602</v>
       </c>
       <c r="C94" t="n">
         <v>92</v>
@@ -4177,17 +4287,17 @@
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" s="1" t="n">
-        <v>0.008867177936824802</v>
+        <v>0.02363788585602602</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>etovadikk</t>
+          <t>Фиш</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>0.0082695208088751</v>
+        <v>0.02333288324347607</v>
       </c>
       <c r="C95" t="n">
         <v>93</v>
@@ -4210,17 +4320,17 @@
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" s="1" t="n">
-        <v>0.0082695208088751</v>
+        <v>0.02333288324347607</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>veronesss</t>
+          <t>willy &lt;/3</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>0.007685929486314879</v>
+        <v>0.02302920386307251</v>
       </c>
       <c r="C96" t="n">
         <v>94</v>
@@ -4243,17 +4353,17 @@
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" s="1" t="n">
-        <v>0.007685929486314879</v>
+        <v>0.02302920386307251</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>dance_with_vlad</t>
+          <t>whitecurly_rr</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>0.007116751534922361</v>
+        <v>0.02272685350590401</v>
       </c>
       <c r="C97" t="n">
         <v>95</v>
@@ -4276,17 +4386,17 @@
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
       <c r="U97" s="1" t="n">
-        <v>0.007116751534922361</v>
+        <v>0.02272685350590401</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Leomane</t>
+          <t>Даша 12 см</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>0.006562361640294801</v>
+        <v>0.02242583803976547</v>
       </c>
       <c r="C98" t="n">
         <v>96</v>
@@ -4309,17 +4419,17 @@
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
       <c r="U98" s="1" t="n">
-        <v>0.006562361640294801</v>
+        <v>0.02242583803976547</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>katerina_boc</t>
+          <t>mvp</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>0.006023165330549357</v>
+        <v>0.02212616341086655</v>
       </c>
       <c r="C99" t="n">
         <v>97</v>
@@ -4342,17 +4452,17 @@
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
       <c r="U99" s="1" t="n">
-        <v>0.006023165330549357</v>
+        <v>0.02212616341086655</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kuromi</t>
+          <t>bron</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>0.005499603456534434</v>
+        <v>0.02182783564559384</v>
       </c>
       <c r="C100" t="n">
         <v>98</v>
@@ -4375,17 +4485,17 @@
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
       <c r="U100" s="1" t="n">
-        <v>0.005499603456534434</v>
+        <v>0.02182783564559384</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>0.004992157640133424</v>
+        <v>0.02153086085232912</v>
       </c>
       <c r="C101" t="n">
         <v>99</v>
@@ -4408,17 +4518,17 @@
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
       <c r="U101" s="1" t="n">
-        <v>0.004992157640133424</v>
+        <v>0.02153086085232912</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tim19</t>
+          <t>Artemon</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>0.004501356977571467</v>
+        <v>0.0212352452233257</v>
       </c>
       <c r="C102" t="n">
         <v>100</v>
@@ -4441,7 +4551,7 @@
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
       <c r="U102" s="1" t="n">
-        <v>0.004501356977571467</v>
+        <v>0.0212352452233257</v>
       </c>
     </row>
   </sheetData>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -545,583 +545,545 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0.60695</v>
+        <v>0.8068640000000001</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.037</v>
-      </c>
       <c r="H3" s="1" t="n">
-        <v>0.074</v>
+        <v>0.005</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.111</v>
+        <v>0.024</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0.141</v>
+        <v>0.05</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.12</v>
+        <v>0.082</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>0.123</v>
+        <v>0.128</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.139</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>0.092</v>
+        <v>0.133</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>0.057</v>
+        <v>0.113</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>0.042</v>
+        <v>0.079</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>0.041</v>
+        <v>0.075</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>0.019</v>
+        <v>0.05</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>0.016</v>
+        <v>0.029</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>0.007</v>
+        <v>0.025</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>0.006</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0.60329</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" s="1" t="n">
+        <v>0.602</v>
+      </c>
       <c r="E4" s="1" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>0.08</v>
-      </c>
       <c r="K4" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="S4" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="T4" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U4" s="1" t="n">
-        <v>0.011</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.59231</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" s="1" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.417</v>
+      </c>
       <c r="F5" s="1" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0.107</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" s="1" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="S5" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="T5" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="U5" s="1" t="n">
-        <v>0.018</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.532</v>
+        <v>0.685248</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.243</v>
+        <v>0.003</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.317</v>
+        <v>0.02</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.169</v>
+        <v>0.148</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.104</v>
+        <v>0.314</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.059</v>
+        <v>0.222</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.033</v>
+        <v>0.12</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.019</v>
+        <v>0.083</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.017</v>
+        <v>0.039</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="O6" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R6" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="P6" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>лучший игрок</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.5298720000000001</v>
+        <v>0.6549759999999999</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>0.174</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>0.222</v>
+        <v>0.001</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.205</v>
+        <v>0.019</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.146</v>
+        <v>0.037</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.079</v>
+        <v>0.098</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.06</v>
+        <v>0.119</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.023</v>
+        <v>0.149</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.019</v>
+        <v>0.133</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.017</v>
+        <v>0.09</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.012</v>
+        <v>0.076</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.007</v>
+        <v>0.058</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.012</v>
+        <v>0.052</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.006</v>
+        <v>0.035</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.002</v>
+        <v>0.018</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>0.011</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.5234880000000001</v>
+        <v>0.60939</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.047</v>
+        <v>0.027</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.097</v>
+        <v>0.143</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.129</v>
+        <v>0.242</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.117</v>
+        <v>0.189</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.104</v>
+        <v>0.149</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.109</v>
+        <v>0.092</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.076</v>
+        <v>0.049</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.062</v>
+        <v>0.034</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.055</v>
+        <v>0.021</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.048</v>
+        <v>0.019</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.029</v>
+        <v>0.012</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0.032</v>
+        <v>0.003</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.02</v>
+        <v>0.006</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.025</v>
+        <v>0.004</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>Чека-чека</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.5107200000000001</v>
+        <v>0.60573</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.004</v>
+        <v>0.216</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>0.028</v>
+        <v>0.256</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.079</v>
+        <v>0.253</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.1</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.093</v>
+        <v>0.031</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>0.064</v>
+        <v>0.008</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.051</v>
+        <v>0.007</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0.055</v>
+        <v>0.005</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>0.037</v>
+        <v>0.001</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.029</v>
+        <v>0.002</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.037</v>
+        <v>0.003</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.026</v>
+        <v>0.001</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>0.015</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.45173</v>
+        <v>0.59414</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>0.49</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" s="1" t="n">
-        <v>0.174</v>
+        <v>0.007</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.108</v>
+        <v>0.038</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0.075</v>
+        <v>0.107</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.022</v>
+        <v>0.178</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.019</v>
+        <v>0.12</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.018</v>
+        <v>0.097</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.046</v>
       </c>
       <c r="N10" s="1" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="U10" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="O10" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.444012</v>
+        <v>0.5788899999999999</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>0.045</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>0.107</v>
+        <v>0.004</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.133</v>
+        <v>0.012</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.135</v>
+        <v>0.051</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.102</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.095</v>
+        <v>0.13</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.078</v>
+        <v>0.129</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.054</v>
+        <v>0.142</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.048</v>
+        <v>0.106</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.038</v>
+        <v>0.079</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.036</v>
+        <v>0.055</v>
       </c>
       <c r="O11" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R11" s="1" t="n">
         <v>0.021</v>
       </c>
-      <c r="P11" s="1" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>0.02</v>
-      </c>
       <c r="S11" s="1" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U11" s="1" t="n">
         <v>0.011</v>
@@ -1130,342 +1092,310 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.4431039999999999</v>
+        <v>0.55571</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>0.062</v>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" s="1" t="n">
-        <v>0.091</v>
+        <v>0.012</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.106</v>
+        <v>0.03</v>
       </c>
       <c r="I12" s="1" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="K12" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="J12" s="1" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.08500000000000001</v>
-      </c>
       <c r="L12" s="1" t="n">
-        <v>0.067</v>
+        <v>0.125</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.074</v>
+        <v>0.095</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.059</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0.051</v>
+        <v>0.08</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.037</v>
+        <v>0.052</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.045</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.028</v>
+        <v>0.047</v>
       </c>
       <c r="S12" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="U12" s="1" t="n">
         <v>0.017</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0.014</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>gvrdkn</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.427668</v>
+        <v>0.4853</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="G13" s="1" t="n">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="Q13" s="1" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.047</v>
-      </c>
       <c r="R13" s="1" t="n">
-        <v>0.031</v>
+        <v>0.078</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.031</v>
+        <v>0.089</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.019</v>
+        <v>0.068</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.023</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.351396</v>
+        <v>0.47214</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E14" s="1" t="n">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="H14" s="1" t="n">
         <v>0.011</v>
       </c>
-      <c r="G14" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H14" s="1" t="n">
+      <c r="I14" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="U14" s="1" t="n">
         <v>0.024</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="L14" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="N14" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>0.052</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.34731</v>
+        <v>0.3904000000000001</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>0.019</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" s="1" t="n">
-        <v>0.026</v>
+        <v>0.002</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.026</v>
+        <v>0.002</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.036</v>
+        <v>0.007</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.053</v>
+        <v>0.015</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.045</v>
+        <v>0.018</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.058</v>
+        <v>0.054</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.053</v>
+        <v>0.073</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.049</v>
+        <v>0.078</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.066</v>
+        <v>0.079</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.057</v>
+        <v>0.064</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.061</v>
+        <v>0.065</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.061</v>
+        <v>0.075</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.067</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.3341439999999999</v>
+        <v>0.3572979999999999</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="F16" s="1" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.006</v>
+        <v>0.057</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.005</v>
+        <v>0.066</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.016</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.018</v>
+        <v>0.094</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0.044</v>
+        <v>0.058</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.048</v>
+        <v>0.068</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0.064</v>
+        <v>0.039</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.074</v>
+        <v>0.033</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.064</v>
+        <v>0.04</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.092</v>
+        <v>0.029</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.023</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.021</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.066</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.285566</v>
+        <v>0.3309040000000001</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1473,62 +1403,62 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.011</v>
+        <v>0.024</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.017</v>
+        <v>0.04</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.029</v>
+        <v>0.045</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.022</v>
+        <v>0.052</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.019</v>
+        <v>0.061</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.042</v>
+        <v>0.061</v>
       </c>
       <c r="O17" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="P17" s="1" t="n">
         <v>0.055</v>
       </c>
-      <c r="P17" s="1" t="n">
-        <v>0.058</v>
-      </c>
       <c r="Q17" s="1" t="n">
-        <v>0.077</v>
+        <v>0.047</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.073</v>
+        <v>0.057</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.08</v>
+        <v>0.037</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.049</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>szrvi</t>
+          <t>Maxim</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.271492</v>
+        <v>0.312816</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -1536,180 +1466,158 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="I18" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0.018</v>
+        <v>0.033</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0.027</v>
+        <v>0.04</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.032</v>
+        <v>0.045</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0.044</v>
+        <v>0.057</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>0.068</v>
+        <v>0.064</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.068</v>
+        <v>0.06</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.083</v>
+        <v>0.06</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.068</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Чека-чека</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.254176</v>
+        <v>0.234396</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="J19" s="1" t="n">
+      <c r="N19" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="R19" s="1" t="n">
         <v>0.042</v>
       </c>
-      <c r="K19" s="1" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="L19" s="1" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="M19" s="1" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="N19" s="1" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="O19" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="R19" s="1" t="n">
-        <v>0.043</v>
-      </c>
       <c r="S19" s="1" t="n">
-        <v>0.045</v>
+        <v>0.052</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.053</v>
+        <v>0.065</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.042</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.237632</v>
+        <v>0.22509</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J20" s="3" t="n">
         <v>0.002</v>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0.031</v>
-      </c>
       <c r="K20" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="M20" s="3" t="n">
         <v>0.022</v>
       </c>
-      <c r="L20" s="3" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0.039</v>
-      </c>
       <c r="N20" s="3" t="n">
-        <v>0.044</v>
+        <v>0.034</v>
       </c>
       <c r="O20" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="U20" s="3" t="n">
         <v>0.043</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>0.048</v>
       </c>
     </row>
     <row r="21">
@@ -1719,196 +1627,170 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.213944</v>
+        <v>0.2043</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="H21" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="I21" s="1" t="n">
-        <v>0.011</v>
-      </c>
       <c r="J21" s="1" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.013</v>
+        <v>0.023</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>0.027</v>
+        <v>0.037</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.02</v>
+        <v>0.037</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.026</v>
+        <v>0.029</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
       <c r="P21" s="1" t="n">
         <v>0.06</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.049</v>
+        <v>0.036</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.078</v>
+        <v>0.056</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.063</v>
+        <v>0.033</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.083</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.205296</v>
+        <v>0.200208</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" s="1" t="n">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="G22" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H22" s="1" t="n">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="I22" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="J22" s="1" t="n">
+      <c r="N22" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="K22" s="1" t="n">
+      <c r="O22" s="1" t="n">
         <v>0.014</v>
       </c>
-      <c r="L22" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="M22" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="N22" s="1" t="n">
+      <c r="P22" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q22" s="1" t="n">
         <v>0.035</v>
       </c>
-      <c r="O22" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="P22" s="1" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>0.063</v>
-      </c>
       <c r="R22" s="1" t="n">
-        <v>0.067</v>
+        <v>0.035</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.08</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.183416</v>
+        <v>0.185072</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" s="1" t="n">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K23" s="1" t="n">
-        <v>0.01</v>
-      </c>
       <c r="L23" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>0.016</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>0.02</v>
+        <v>0.007</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.045</v>
+        <v>0.027</v>
       </c>
       <c r="R23" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="U23" s="1" t="n">
         <v>0.052</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.09715599999999999</v>
+        <v>0.181146</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1916,52 +1798,60 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="G24" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>0.007</v>
+      </c>
       <c r="J24" s="1" t="n">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>0.022</v>
+      </c>
       <c r="M24" s="1" t="n">
-        <v>0.003</v>
+        <v>0.024</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>0.013</v>
+        <v>0.04</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.041</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.017</v>
+        <v>0.034</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.023</v>
+        <v>0.042</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.04</v>
+        <v>0.036</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.056</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>turkoid</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.095128</v>
+        <v>0.15738</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1969,12 +1859,8 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" s="1" t="n">
         <v>0.001</v>
       </c>
@@ -1982,47 +1868,47 @@
         <v>0.004</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>0.008</v>
+        <v>0.032</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>0.014</v>
+        <v>0.027</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="Q25" s="1" t="n">
         <v>0.022</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>0.045</v>
+        <v>0.039</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.044</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>szrvi</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.05107200000000001</v>
+        <v>0.133</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -2032,40 +1918,52 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="K26" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>0.025</v>
+      </c>
       <c r="P26" s="1" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.004</v>
+        <v>0.029</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.017</v>
+        <v>0.032</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.025</v>
+        <v>0.041</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Dima!</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.047216</v>
+        <v>0.104152</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -2073,48 +1971,60 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="G27" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>0.028</v>
+      </c>
       <c r="M27" s="1" t="n">
-        <v>0.003</v>
+        <v>0.025</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>0.001</v>
+        <v>0.018</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>0.007</v>
+        <v>0.033</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>0.001</v>
+        <v>0.028</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.011</v>
+        <v>0.026</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ustayonmymind</t>
+          <t>gara_077</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.03574662978285533</v>
+        <v>0.09624799999999999</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -2125,35 +2035,51 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="J28" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="Q28" s="1" t="n">
+        <v>0.022</v>
+      </c>
       <c r="R28" s="1" t="n">
-        <v>0.003656570149637411</v>
+        <v>0.023</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.007313140299274823</v>
+        <v>0.026</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.01828285074818706</v>
+        <v>0.025</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.06581826269347339</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>by_twentyseven</t>
+          <t>artyomkalina</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.03534271546324529</v>
+        <v>0.07501200000000001</v>
       </c>
       <c r="C29" t="n">
         <v>27</v>
@@ -2167,36 +2093,42 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="M29" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>0.013</v>
+      </c>
       <c r="P29" s="1" t="n">
-        <v>0.01162742316858971</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>0.009301938534871768</v>
+        <v>0.011</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>0.01395290780230765</v>
+        <v>0.019</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0.01162742316858971</v>
+        <v>0.03</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.03488226950576913</v>
+        <v>0.023</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.03720775413948707</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>swapblet</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.03514133277271893</v>
+        <v>0.06490399999999999</v>
       </c>
       <c r="C30" t="n">
         <v>28</v>
@@ -2207,35 +2139,51 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="J30" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="N30" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="O30" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q30" s="1" t="n">
+        <v>0.014</v>
+      </c>
       <c r="R30" s="1" t="n">
-        <v>0.01045997522702671</v>
+        <v>0.022</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0.006275985136216025</v>
+        <v>0.017</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.0251039405448641</v>
+        <v>0.024</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.03556391577189081</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>Фил</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.03494033403452016</v>
+        <v>0.03754800000000001</v>
       </c>
       <c r="C31" t="n">
         <v>29</v>
@@ -2245,30 +2193,54 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="I31" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="N31" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="P31" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="Q31" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="R31" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>0.008</v>
+      </c>
       <c r="U31" s="1" t="n">
-        <v>0.03494033403452016</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gvrdkn</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.03473971998348936</v>
+        <v>0.03721</v>
       </c>
       <c r="C32" t="n">
         <v>30</v>
@@ -2283,25 +2255,39 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+      <c r="N32" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O32" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q32" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="R32" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>0.012</v>
+      </c>
       <c r="U32" s="1" t="n">
-        <v>0.05695036062867109</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Julia_2499</t>
+          <t>3y6a</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.03433964890351104</v>
+        <v>0.03538</v>
       </c>
       <c r="C33" t="n">
         <v>31</v>
@@ -2315,26 +2301,42 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+      <c r="M33" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O33" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P33" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="Q33" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="R33" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="S33" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>0.007</v>
+      </c>
       <c r="U33" s="1" t="n">
-        <v>0.09132885346678467</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.03414019336558526</v>
+        <v>0.031648</v>
       </c>
       <c r="C34" t="n">
         <v>32</v>
@@ -2352,22 +2354,30 @@
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+      <c r="Q34" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="R34" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S34" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>0.017</v>
+      </c>
       <c r="U34" s="1" t="n">
-        <v>0.03414019336558526</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.03394112549695429</v>
+        <v>0.028952</v>
       </c>
       <c r="C35" t="n">
         <v>33</v>
@@ -2377,30 +2387,50 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+      <c r="O35" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="P35" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="Q35" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="R35" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="S35" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="T35" s="1" t="n">
+        <v>0.019</v>
+      </c>
       <c r="U35" s="1" t="n">
-        <v>0.03394112549695429</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>0.03374244605404963</v>
+        <v>0.02523870470028509</v>
       </c>
       <c r="C36" t="n">
         <v>34</v>
@@ -2417,27 +2447,29 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" s="1" t="n">
+        <v>0.008390526828552224</v>
+      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" s="1" t="n">
-        <v>0.006193547366749198</v>
+        <v>0.008390526828552224</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.03096773683374599</v>
+        <v>0.0335621073142089</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.03716128420049519</v>
+        <v>0.01678105365710445</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>turkoid</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>0.03354415579774805</v>
+        <v>0.02505907021418326</v>
       </c>
       <c r="C37" t="n">
         <v>35</v>
@@ -2448,39 +2480,51 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="J37" s="1" t="n">
+        <v>0.001009794899024148</v>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>0.002019589798048296</v>
+      </c>
+      <c r="L37" s="1" t="n">
+        <v>0.002019589798048296</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <v>0.002019589798048296</v>
+      </c>
+      <c r="N37" s="1" t="n">
+        <v>0.004039179596096593</v>
+      </c>
+      <c r="O37" s="1" t="n">
+        <v>0.002019589798048296</v>
+      </c>
       <c r="P37" s="1" t="n">
-        <v>0.0036942902860956</v>
+        <v>0.006058769394144889</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>0.0036942902860956</v>
+        <v>0.01110774388926563</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>0.0147771611443824</v>
+        <v>0.006058769394144889</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>0.0036942902860956</v>
+        <v>0.008078359192193185</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>0.0258600320026692</v>
+        <v>0.009088154091217332</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>0.0221657417165736</v>
+        <v>0.01312733368731392</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Иван Царевич</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>0.03334625549341529</v>
+        <v>0.02503200000000001</v>
       </c>
       <c r="C38" t="n">
         <v>36</v>
@@ -2491,35 +2535,51 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="J38" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L38" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="M38" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N38" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O38" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="Q38" s="1" t="n">
+        <v>0.011</v>
+      </c>
       <c r="R38" s="1" t="n">
-        <v>0.01836247549196877</v>
+        <v>0.011</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>0.009181237745984387</v>
+        <v>0.013</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>0.004590618872992194</v>
+        <v>0.008</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>0.04131556985692974</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Staryii</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>0.03314874591095039</v>
+        <v>0.02479042170266385</v>
       </c>
       <c r="C39" t="n">
         <v>37</v>
@@ -2539,20 +2599,24 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" s="1" t="n">
+        <v>0.01351222113153917</v>
+      </c>
       <c r="T39" s="1" t="n">
-        <v>0.08816155827380423</v>
-      </c>
-      <c r="U39" t="inlineStr"/>
+        <v>0.01351222113153917</v>
+      </c>
+      <c r="U39" s="1" t="n">
+        <v>0.009008147421026111</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3y6a</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>0.03295162782483064</v>
+        <v>0.02390192993060988</v>
       </c>
       <c r="C40" t="n">
         <v>38</v>
@@ -2571,21 +2635,25 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+      <c r="R40" s="1" t="n">
+        <v>0.01497614657306383</v>
+      </c>
+      <c r="S40" s="1" t="n">
+        <v>0.01497614657306383</v>
+      </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" s="1" t="n">
-        <v>0.03295162782483064</v>
+        <v>0.01497614657306383</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Leomane</t>
+          <t>swapblet</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>0.03275490201415708</v>
+        <v>0.02372553237018496</v>
       </c>
       <c r="C41" t="n">
         <v>39</v>
@@ -2608,17 +2676,17 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" s="1" t="n">
-        <v>0.03275490201415708</v>
+        <v>0.02372553237018496</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>FISHer</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>0.03255856926270075</v>
+        <v>0.0234617540347327</v>
       </c>
       <c r="C42" t="n">
         <v>40</v>
@@ -2641,17 +2709,17 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" s="1" t="n">
-        <v>0.03255856926270075</v>
+        <v>0.06239828200726781</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nolekri</t>
+          <t>Горыныч</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>0.03236263035894951</v>
+        <v>0.02337404659986632</v>
       </c>
       <c r="C43" t="n">
         <v>41</v>
@@ -2667,32 +2735,34 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" s="1" t="n">
+        <v>0.006057021663608791</v>
+      </c>
       <c r="P43" s="1" t="n">
-        <v>0.004303541271136904</v>
+        <v>0.01211404332721758</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" s="1" t="n">
-        <v>0.01291062381341071</v>
+        <v>0.006057021663608791</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>0.01291062381341071</v>
+        <v>0.006057021663608791</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>0.01721416508454762</v>
+        <v>0.003028510831804396</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>0.03873187144023214</v>
+        <v>0.01817106499082637</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Комар</t>
+          <t>Julia_2499</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>0.0321670860961555</v>
+        <v>0.02319896056500719</v>
       </c>
       <c r="C44" t="n">
         <v>42</v>
@@ -2708,24 +2778,36 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
+      <c r="O44" s="1" t="n">
+        <v>0.002689422741132297</v>
+      </c>
+      <c r="P44" s="1" t="n">
+        <v>0.002689422741132297</v>
+      </c>
+      <c r="Q44" s="1" t="n">
+        <v>0.005378845482264594</v>
+      </c>
+      <c r="R44" s="1" t="n">
+        <v>0.008068268223396891</v>
+      </c>
+      <c r="S44" s="1" t="n">
+        <v>0.002689422741132297</v>
+      </c>
+      <c r="T44" s="1" t="n">
+        <v>0.01075769096452919</v>
+      </c>
       <c r="U44" s="1" t="n">
-        <v>0.0321670860961555</v>
+        <v>0.01882595918792608</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>No1z11</t>
+          <t>KidPoker</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>0.03197193727238341</v>
+        <v>0.02311158223996105</v>
       </c>
       <c r="C45" t="n">
         <v>43</v>
@@ -2748,17 +2830,17 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" s="1" t="n">
-        <v>0.03197193727238341</v>
+        <v>0.02311158223996105</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>0.03177718469055921</v>
+        <v>0.0229371556658979</v>
       </c>
       <c r="C46" t="n">
         <v>44</v>
@@ -2771,31 +2853,39 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" s="1" t="n">
+        <v>0.002088994140792159</v>
+      </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" s="1" t="n">
+        <v>0.002088994140792159</v>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="Q46" s="1" t="n">
+        <v>0.002088994140792159</v>
+      </c>
+      <c r="R46" s="1" t="n">
+        <v>0.006266982422376476</v>
+      </c>
       <c r="S46" s="1" t="n">
-        <v>0.03756168403139386</v>
+        <v>0.004177988281584317</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>0.0281712630235454</v>
+        <v>0.01044497070396079</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.01878084201569693</v>
+        <v>0.01044497070396079</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Maxim</t>
+          <t>Gur4an</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>0.03158282915851982</v>
+        <v>0.02285010769495784</v>
       </c>
       <c r="C47" t="n">
         <v>45</v>
@@ -2815,20 +2905,20 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+      <c r="S47" s="1" t="n">
+        <v>0.06077156301850489</v>
+      </c>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" s="1" t="n">
-        <v>0.03158282915851982</v>
-      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>0.03138887148906335</v>
+        <v>0.0227631701210112</v>
       </c>
       <c r="C48" t="n">
         <v>46</v>
@@ -2847,21 +2937,25 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+      <c r="R48" s="1" t="n">
+        <v>0.01654300154143256</v>
+      </c>
+      <c r="S48" s="1" t="n">
+        <v>0.008271500770716282</v>
+      </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" s="1" t="n">
-        <v>0.03138887148906335</v>
+        <v>0.008271500770716282</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Демон</t>
+          <t>sfv</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>0.03119531250000001</v>
+        <v>0.02267634308442317</v>
       </c>
       <c r="C49" t="n">
         <v>47</v>
@@ -2884,17 +2978,17 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" s="1" t="n">
-        <v>0.03119531250000001</v>
+        <v>0.02267634308442317</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>TryFraiz</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>0.03100215301420393</v>
+        <v>0.0225896267260957</v>
       </c>
       <c r="C50" t="n">
         <v>48</v>
@@ -2917,17 +3011,17 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" s="1" t="n">
-        <v>0.03100215301420393</v>
+        <v>0.0225896267260957</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>Rabie</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>0.0308093938596656</v>
+        <v>0.02250302118747094</v>
       </c>
       <c r="C51" t="n">
         <v>49</v>
@@ -2946,21 +3040,21 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="R51" s="1" t="n">
+        <v>0.04956612596359239</v>
+      </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" s="1" t="n">
-        <v>0.0308093938596656</v>
-      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>z9</t>
+          <t>kuromi</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>0.03061703586954512</v>
+        <v>0.02233014313782</v>
       </c>
       <c r="C52" t="n">
         <v>50</v>
@@ -2983,7 +3077,7 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" s="1" t="n">
-        <v>0.03061703586954512</v>
+        <v>0.02233014313782</v>
       </c>
     </row>
   </sheetData>

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:AA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Top 18 Prob</t>
+          <t>Top 24 Prob</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -538,6 +538,36 @@
       <c r="U1" t="inlineStr">
         <is>
           <t>Rank 18</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Rank 19</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Rank 20</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Rank 21</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Rank 22</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Rank 23</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Rank 24</t>
         </is>
       </c>
     </row>
@@ -549,7 +579,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0.8068640000000001</v>
+        <v>0.86668</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -557,151 +587,197 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>0.024</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" s="1" t="n">
-        <v>0.05</v>
+        <v>0.007</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.082</v>
+        <v>0.007</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>0.128</v>
+        <v>0.026</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0.139</v>
+        <v>0.054</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>0.133</v>
+        <v>0.068</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>0.113</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>0.079</v>
+        <v>0.097</v>
       </c>
       <c r="Q3" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="S3" s="1" t="n">
         <v>0.075</v>
       </c>
-      <c r="R3" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>0.029</v>
-      </c>
       <c r="T3" s="1" t="n">
-        <v>0.025</v>
+        <v>0.065</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>0.023</v>
+        <v>0.058</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="W3" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>0.021</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.7659999999999999</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.602</v>
+        <v>0.186</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.265</v>
+        <v>0.279</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.104</v>
+        <v>0.248</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.015</v>
+        <v>0.137</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.003</v>
+        <v>0.031</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.001</v>
+        <v>0.022</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+        <v>0.012</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Горыныч</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.7659999999999999</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.175</v>
+        <v>0.004</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.417</v>
+        <v>0.025</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.269</v>
+        <v>0.068</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.059</v>
+        <v>0.168</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.04</v>
+        <v>0.192</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.017</v>
+        <v>0.187</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.138</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.008</v>
+        <v>0.092</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.055</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>0.036</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.016</v>
+      </c>
       <c r="O5" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+        <v>0.007</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -710,59 +786,75 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.685248</v>
+        <v>0.765234</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.02</v>
+        <v>0.037</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.148</v>
+        <v>0.12</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.314</v>
+        <v>0.187</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.222</v>
+        <v>0.176</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.12</v>
+        <v>0.146</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.083</v>
+        <v>0.114</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.039</v>
+        <v>0.096</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.018</v>
+        <v>0.052</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.012</v>
+        <v>0.03</v>
       </c>
       <c r="N6" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="P6" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="P6" s="1" t="n">
-        <v>0.001</v>
-      </c>
       <c r="Q6" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+        <v>0.001</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="W6" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -771,332 +863,392 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.6549759999999999</v>
+        <v>0.7093159999999998</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" s="1" t="n">
-        <v>0.019</v>
+        <v>0.001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.037</v>
+        <v>0.002</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.098</v>
+        <v>0.012</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.119</v>
+        <v>0.032</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.149</v>
+        <v>0.041</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.133</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.09</v>
+        <v>0.105</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.076</v>
+        <v>0.105</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.058</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.052</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.035</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.026</v>
+        <v>0.054</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.018</v>
+        <v>0.04</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.02</v>
+        <v>0.045</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.01</v>
+        <v>0.029</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.011</v>
+        <v>0.027</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="W7" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.60939</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.004</v>
+        <v>0.482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.027</v>
+        <v>0.257</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>0.143</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.242</v>
+        <v>0.051</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.189</v>
+        <v>0.024</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.149</v>
+        <v>0.02</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.092</v>
+        <v>0.01</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.049</v>
+        <v>0.005</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.034</v>
+        <v>0.002</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.021</v>
+        <v>0.003</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.019</v>
+        <v>0.002</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="Q8" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>0.003</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Чека-чека</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.60573</v>
+        <v>0.6845600000000001</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.216</v>
+        <v>0.036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>0.256</v>
+        <v>0.117</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.253</v>
+        <v>0.169</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.092</v>
+        <v>0.176</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.031</v>
+        <v>0.083</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.023</v>
+        <v>0.09</v>
       </c>
       <c r="K9" s="1" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="N9" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="L9" s="1" t="n">
+      <c r="O9" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="P9" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="N9" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="O9" s="1" t="n">
+      <c r="Q9" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="P9" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="R9" s="1" t="n">
+      <c r="T9" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="X9" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="S9" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>лучший игрок</t>
+          <t>Чека-чека</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.59414</v>
+        <v>0.6838719999999999</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" s="1" t="n">
+        <v>0.268</v>
+      </c>
       <c r="E10" s="1" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>0.026</v>
-      </c>
       <c r="P10" s="1" t="n">
-        <v>0.026</v>
+        <v>0.006</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>0.011</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.5788899999999999</v>
+        <v>0.676992</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="E11" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.051</v>
+        <v>0.045</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.13</v>
+        <v>0.105</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.129</v>
+        <v>0.127</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.142</v>
+        <v>0.135</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0.106</v>
+        <v>0.127</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.079</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="R11" s="1" t="n">
         <v>0.021</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="U11" s="1" t="n">
         <v>0.011</v>
       </c>
+      <c r="V11" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>gvrdkn</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.55571</v>
+        <v>0.6297260000000001</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1104,60 +1256,68 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I12" s="1" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="T12" s="1" t="n">
         <v>0.051</v>
       </c>
-      <c r="J12" s="1" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="O12" s="1" t="n">
+      <c r="U12" s="1" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="V12" s="1" t="n">
         <v>0.08</v>
       </c>
-      <c r="P12" s="1" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0.017</v>
+      <c r="W12" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gvrdkn</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.4853</v>
+        <v>0.593744</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -1166,358 +1326,482 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0.006</v>
+      </c>
       <c r="J13" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>0.014</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0.019</v>
+      </c>
       <c r="L13" s="1" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.018</v>
+        <v>0.06</v>
       </c>
       <c r="N13" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="X13" s="1" t="n">
         <v>0.034</v>
       </c>
-      <c r="O13" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="U13" s="1" t="n">
-        <v>0.095</v>
+      <c r="Y13" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="Z13" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>0.031</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.47214</v>
+        <v>0.58926</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="E14" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G14" s="1" t="n">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.011</v>
+        <v>0.021</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.035</v>
+        <v>0.066</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.046</v>
+        <v>0.078</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.074</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0.092</v>
+        <v>0.117</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.099</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0.066</v>
+        <v>0.056</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.059</v>
+        <v>0.037</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.048</v>
+        <v>0.041</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.039</v>
+        <v>0.021</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.044</v>
+        <v>0.016</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.024</v>
+        <v>0.029</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>0.014</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.3904000000000001</v>
+        <v>0.57767</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="E15" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0.003</v>
+      </c>
       <c r="H15" s="1" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.002</v>
+        <v>0.037</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.007</v>
+        <v>0.047</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.015</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.018</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.048</v>
+        <v>0.081</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>0.054</v>
+        <v>0.099</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0.073</v>
+        <v>0.09</v>
       </c>
       <c r="P15" s="1" t="n">
         <v>0.078</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.079</v>
+        <v>0.055</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.064</v>
+        <v>0.049</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.065</v>
+        <v>0.046</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.075</v>
+        <v>0.032</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.06</v>
+        <v>0.025</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>0.014</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.3572979999999999</v>
+        <v>0.51322</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" s="1" t="n">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L16" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="F16" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="G16" s="1" t="n">
+      <c r="M16" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="T16" s="1" t="n">
         <v>0.057</v>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="L16" s="1" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="M16" s="1" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>0.021</v>
-      </c>
       <c r="U16" s="1" t="n">
-        <v>0.021</v>
+        <v>0.065</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>0.064</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.3309040000000001</v>
+        <v>0.501144</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="D17" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.017</v>
+      </c>
       <c r="F17" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="W17" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="X17" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="Z17" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K17" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="L17" s="1" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="S17" s="1" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="T17" s="1" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="U17" s="1" t="n">
-        <v>0.027</v>
+      <c r="AA17" s="1" t="n">
+        <v>0.003</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Maxim</t>
+          <t>mvp</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.312816</v>
+        <v>0.4724160000000001</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="D18" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.015</v>
+      </c>
       <c r="H18" s="1" t="n">
-        <v>0.002</v>
+        <v>0.027</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0.002</v>
+        <v>0.049</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.013</v>
+        <v>0.052</v>
       </c>
       <c r="K18" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="W18" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X18" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="Y18" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="Z18" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="L18" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="M18" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N18" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="O18" s="1" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="P18" s="1" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R18" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="T18" s="1" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U18" s="1" t="n">
-        <v>0.074</v>
+      <c r="AA18" s="1" t="n">
+        <v>0.018</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Maxim</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.234396</v>
+        <v>0.46604</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -1527,107 +1811,143 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="J19" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>0.029</v>
+      </c>
       <c r="M19" s="1" t="n">
-        <v>0.004</v>
+        <v>0.029</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>0.011</v>
+        <v>0.047</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>0.018</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>0.024</v>
+        <v>0.058</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.033</v>
+        <v>0.05</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.042</v>
+        <v>0.053</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.052</v>
+        <v>0.044</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.065</v>
+        <v>0.057</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="W19" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="X19" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="Y19" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="Z19" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AA19" s="1" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Руслан</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>0.22509</v>
-      </c>
-      <c r="C20" s="2" t="n">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Yanchik_250</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>0.4496419999999999</v>
+      </c>
+      <c r="C20" t="n">
         <v>18</v>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J20" s="3" t="n">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="P20" s="1" t="n">
         <v>0.022</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="Q20" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="S20" s="1" t="n">
         <v>0.034</v>
       </c>
-      <c r="O20" s="3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>0.043</v>
+      <c r="T20" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="W20" s="1" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="X20" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="Y20" s="1" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="Z20" s="1" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AA20" s="1" t="n">
+        <v>0.051</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>emilian_s</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.2043</v>
+        <v>0.4154099999999999</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
@@ -1636,57 +1956,77 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>0.002</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="I21" s="1" t="n">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="L21" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="T21" s="1" t="n">
         <v>0.037</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="U21" s="1" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="W21" s="1" t="n">
         <v>0.037</v>
       </c>
-      <c r="N21" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="O21" s="1" t="n">
+      <c r="X21" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Y21" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="Z21" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AA21" s="1" t="n">
         <v>0.033</v>
-      </c>
-      <c r="P21" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="R21" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="S21" s="1" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="T21" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="U21" s="1" t="n">
-        <v>0.037</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ромчик</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.200208</v>
+        <v>0.394912</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
@@ -1696,101 +2036,157 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J22" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+        <v>0.002</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>0.004</v>
+      </c>
       <c r="M22" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>0.008</v>
+        <v>0.016</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.014</v>
+        <v>0.026</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="R22" s="1" t="n">
         <v>0.035</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.048</v>
+        <v>0.051</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.059</v>
+        <v>0.051</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="W22" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="X22" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y22" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="Z22" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AA22" s="1" t="n">
+        <v>0.041</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>yungplague</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.185072</v>
+        <v>0.387262</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="D23" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>0.083</v>
+      </c>
       <c r="K23" s="1" t="n">
-        <v>0.001</v>
+        <v>0.057</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>0.004</v>
+        <v>0.047</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.004</v>
+        <v>0.066</v>
       </c>
       <c r="N23" s="1" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="W23" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X23" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Y23" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="Z23" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AA23" s="1" t="n">
         <v>0.008999999999999999</v>
-      </c>
-      <c r="O23" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <v>0.052</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.181146</v>
+        <v>0.37759</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
@@ -1798,60 +2194,70 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>0.007</v>
-      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K24" s="1" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" s="1" t="n">
-        <v>0.022</v>
+        <v>0.005</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.024</v>
+        <v>0.004</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>0.034</v>
+        <v>0.01</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>0.04</v>
+        <v>0.028</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>0.041</v>
+        <v>0.031</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.034</v>
+        <v>0.029</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.042</v>
+        <v>0.045</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.039</v>
+        <v>0.059</v>
       </c>
       <c r="T24" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="W24" s="1" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="X24" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="Y24" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="Z24" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AA24" s="1" t="n">
         <v>0.036</v>
-      </c>
-      <c r="U24" s="1" t="n">
-        <v>0.045</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>gara_077</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.15738</v>
+        <v>0.317072</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
@@ -1865,105 +2271,143 @@
         <v>0.001</v>
       </c>
       <c r="J25" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="Q25" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="V25" s="1" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y25" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Z25" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AA25" s="1" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>emilian_s</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0.254296</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K26" s="3" t="n">
         <v>0.004</v>
       </c>
-      <c r="K25" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="L25" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="M25" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="N25" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="O25" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="P25" s="1" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="Q25" s="1" t="n">
+      <c r="L26" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="N26" s="3" t="n">
         <v>0.022</v>
       </c>
-      <c r="R25" s="1" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="S25" s="1" t="n">
+      <c r="O26" s="3" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="T26" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="T25" s="1" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="U25" s="1" t="n">
-        <v>0.022</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>szrvi</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="C26" t="n">
-        <v>24</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="L26" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="M26" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="N26" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="O26" s="1" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="P26" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q26" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="R26" s="1" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="S26" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="T26" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="U26" s="1" t="n">
-        <v>0.042</v>
+      <c r="U26" s="3" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>0.036</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dima!</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.104152</v>
+        <v>0.2464480000000001</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
@@ -1971,60 +2415,64 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" s="1" t="n">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q27" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="H27" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="I27" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="J27" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="K27" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="L27" s="1" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="M27" s="1" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="N27" s="1" t="n">
+      <c r="R27" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="U27" s="1" t="n">
         <v>0.018</v>
       </c>
-      <c r="O27" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="P27" s="1" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="Q27" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="R27" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="S27" s="1" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="T27" s="1" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>0.024</v>
+      <c r="V27" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="W27" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="Y27" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="Z27" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AA27" s="1" t="n">
+        <v>0.053</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gara_077</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.09624799999999999</v>
+        <v>0.2408</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
@@ -2035,51 +2483,65 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K28" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O28" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="M28" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="N28" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="O28" s="1" t="n">
-        <v>0.023</v>
-      </c>
       <c r="P28" s="1" t="n">
-        <v>0.028</v>
+        <v>0.007</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>0.022</v>
+        <v>0.013</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>0.023</v>
+        <v>0.014</v>
       </c>
       <c r="S28" s="1" t="n">
         <v>0.026</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.028</v>
+        <v>0.024</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="W28" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="X28" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="Y28" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="Z28" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AA28" s="1" t="n">
+        <v>0.033</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>artyomkalina</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.07501200000000001</v>
+        <v>0.180776</v>
       </c>
       <c r="C29" t="n">
         <v>27</v>
@@ -2091,44 +2553,62 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="K29" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="R29" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="O29" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="P29" s="1" t="n">
+      <c r="S29" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="Q29" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="R29" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="S29" s="1" t="n">
-        <v>0.03</v>
-      </c>
       <c r="T29" s="1" t="n">
-        <v>0.023</v>
+        <v>0.016</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.028</v>
+        <v>0.017</v>
+      </c>
+      <c r="V29" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="W29" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="X29" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y29" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="Z29" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AA29" s="1" t="n">
+        <v>0.043</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>artyomkalina</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.06490399999999999</v>
+        <v>0.16592</v>
       </c>
       <c r="C30" t="n">
         <v>28</v>
@@ -2139,51 +2619,63 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" s="1" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="L30" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="M30" s="1" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O30" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P30" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="O30" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="P30" s="1" t="n">
-        <v>0.005</v>
-      </c>
       <c r="Q30" s="1" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="T30" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="V30" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="W30" s="1" t="n">
         <v>0.024</v>
       </c>
-      <c r="U30" s="1" t="n">
-        <v>0.015</v>
+      <c r="X30" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="Y30" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="Z30" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="AA30" s="1" t="n">
+        <v>0.027</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Фил</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.03754800000000001</v>
+        <v>0.162532</v>
       </c>
       <c r="C31" t="n">
         <v>29</v>
@@ -2197,50 +2689,68 @@
         <v>0.001</v>
       </c>
       <c r="J31" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K31" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="K31" s="1" t="n">
-        <v>0.006</v>
-      </c>
       <c r="L31" s="1" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>0.015</v>
+        <v>0.025</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>0.014</v>
+        <v>0.024</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>0.014</v>
+        <v>0.025</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0.008</v>
+        <v>0.028</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>0.013</v>
+        <v>0.024</v>
+      </c>
+      <c r="V31" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W31" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="X31" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="Y31" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="Z31" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="AA31" s="1" t="n">
+        <v>0.037</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>by_twentyseven</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.03721</v>
+        <v>0.159048</v>
       </c>
       <c r="C32" t="n">
         <v>30</v>
@@ -2250,44 +2760,72 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="I32" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>0.012</v>
+      </c>
       <c r="N32" s="1" t="n">
-        <v>0.001</v>
+        <v>0.016</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>0.001</v>
+        <v>0.021</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>0.005</v>
+        <v>0.016</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>0.007</v>
+        <v>0.029</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>0.005</v>
+        <v>0.03</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>0.011</v>
+        <v>0.026</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>0.012</v>
+        <v>0.031</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>0.019</v>
+        <v>0.027</v>
+      </c>
+      <c r="V32" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="W32" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="X32" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y32" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="Z32" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="AA32" s="1" t="n">
+        <v>0.037</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3y6a</t>
+          <t>szrvi</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.03538</v>
+        <v>0.152684</v>
       </c>
       <c r="C33" t="n">
         <v>31</v>
@@ -2298,45 +2836,67 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="M33" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>0.008</v>
+        <v>0.021</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.007</v>
+        <v>0.018</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.017</v>
+        <v>0.029</v>
+      </c>
+      <c r="V33" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="W33" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="X33" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y33" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="Z33" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AA33" s="1" t="n">
+        <v>0.037</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.031648</v>
+        <v>0.121218</v>
       </c>
       <c r="C34" t="n">
         <v>32</v>
@@ -2345,39 +2905,73 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="J34" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="N34" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="O34" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="P34" s="1" t="n">
+        <v>0.018</v>
+      </c>
       <c r="Q34" s="1" t="n">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T34" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="U34" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="V34" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="W34" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="U34" s="1" t="n">
-        <v>0.013</v>
+      <c r="X34" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="Y34" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Z34" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="AA34" s="1" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.028952</v>
+        <v>0.08299200000000001</v>
       </c>
       <c r="C35" t="n">
         <v>33</v>
@@ -2387,12 +2981,8 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J35" s="1" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" s="1" t="n">
         <v>0.001</v>
@@ -2400,37 +2990,57 @@
       <c r="M35" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="O35" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="P35" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q35" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="R35" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="Q35" s="1" t="n">
+      <c r="S35" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T35" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="U35" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="V35" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W35" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="R35" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="S35" s="1" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="T35" s="1" t="n">
+      <c r="X35" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y35" s="1" t="n">
         <v>0.019</v>
       </c>
-      <c r="U35" s="1" t="n">
-        <v>0.013</v>
+      <c r="Z35" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="AA35" s="1" t="n">
+        <v>0.027</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>Фил</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>0.02523870470028509</v>
+        <v>0.05721600000000001</v>
       </c>
       <c r="C36" t="n">
         <v>34</v>
@@ -2440,36 +3050,72 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="I36" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J36" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N36" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O36" s="1" t="n">
+        <v>0.014</v>
+      </c>
       <c r="P36" s="1" t="n">
-        <v>0.008390526828552224</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+        <v>0.014</v>
+      </c>
+      <c r="Q36" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="R36" s="1" t="n">
+        <v>0.015</v>
+      </c>
       <c r="S36" s="1" t="n">
-        <v>0.008390526828552224</v>
+        <v>0.01</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.0335621073142089</v>
+        <v>0.015</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.01678105365710445</v>
+        <v>0.011</v>
+      </c>
+      <c r="V36" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="W36" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="X36" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y36" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="Z36" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="AA36" s="1" t="n">
+        <v>0.014</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>turkoid</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>0.02505907021418326</v>
+        <v>0.056776</v>
       </c>
       <c r="C37" t="n">
         <v>35</v>
@@ -2479,52 +3125,68 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J37" s="1" t="n">
-        <v>0.001009794899024148</v>
-      </c>
-      <c r="K37" s="1" t="n">
-        <v>0.002019589798048296</v>
-      </c>
-      <c r="L37" s="1" t="n">
-        <v>0.002019589798048296</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" s="1" t="n">
-        <v>0.002019589798048296</v>
+        <v>0.002</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>0.004039179596096593</v>
+        <v>0.002</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>0.002019589798048296</v>
+        <v>0.003</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>0.006058769394144889</v>
+        <v>0.002</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>0.01110774388926563</v>
+        <v>0.008</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>0.006058769394144889</v>
+        <v>0.01</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>0.008078359192193185</v>
+        <v>0.01</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>0.009088154091217332</v>
+        <v>0.006</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>0.01312733368731392</v>
+        <v>0.015</v>
+      </c>
+      <c r="V37" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="W37" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="X37" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="Y37" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="Z37" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AA37" s="1" t="n">
+        <v>0.019</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Иван Царевич</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>0.02503200000000001</v>
+        <v>0.036096</v>
       </c>
       <c r="C38" t="n">
         <v>36</v>
@@ -2535,51 +3197,63 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K38" s="1" t="n">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N38" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O38" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="P38" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="L38" s="1" t="n">
+      <c r="Q38" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="R38" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="M38" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="N38" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O38" s="1" t="n">
+      <c r="S38" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="T38" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="U38" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="V38" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="W38" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="P38" s="1" t="n">
+      <c r="X38" s="1" t="n">
         <v>0.011</v>
       </c>
-      <c r="Q38" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="R38" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="S38" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="T38" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="U38" s="1" t="n">
-        <v>0.015</v>
+      <c r="Y38" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z38" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA38" s="1" t="n">
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Staryii</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>0.02479042170266385</v>
+        <v>0.035236</v>
       </c>
       <c r="C39" t="n">
         <v>37</v>
@@ -2597,26 +3271,42 @@
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" s="1" t="n">
+        <v>0.001</v>
+      </c>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" s="1" t="n">
-        <v>0.01351222113153917</v>
-      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" s="1" t="n">
-        <v>0.01351222113153917</v>
+        <v>0.002</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.009008147421026111</v>
+        <v>0.001</v>
+      </c>
+      <c r="V39" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Y39" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Z39" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA39" s="1" t="n">
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>3y6a</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>0.02390192993060988</v>
+        <v>0.033712</v>
       </c>
       <c r="C40" t="n">
         <v>38</v>
@@ -2635,25 +3325,41 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" s="1" t="n">
-        <v>0.01497614657306383</v>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>0.01497614657306383</v>
-      </c>
-      <c r="T40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" s="1" t="n">
+        <v>0.002</v>
+      </c>
       <c r="U40" s="1" t="n">
-        <v>0.01497614657306383</v>
+        <v>0.002</v>
+      </c>
+      <c r="V40" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="W40" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="X40" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Y40" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z40" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AA40" s="1" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>swapblet</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>0.02372553237018496</v>
+        <v>0.02912246549300428</v>
       </c>
       <c r="C41" t="n">
         <v>39</v>
@@ -2672,21 +3378,43 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" s="1" t="n">
+        <v>0.001763715206698418</v>
+      </c>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
+      <c r="T41" s="1" t="n">
+        <v>0.001763715206698418</v>
+      </c>
       <c r="U41" s="1" t="n">
-        <v>0.02372553237018496</v>
+        <v>0.003527430413396837</v>
+      </c>
+      <c r="V41" s="1" t="n">
+        <v>0.01234600644688893</v>
+      </c>
+      <c r="W41" s="1" t="n">
+        <v>0.003527430413396837</v>
+      </c>
+      <c r="X41" s="1" t="n">
+        <v>0.001763715206698418</v>
+      </c>
+      <c r="Y41" s="1" t="n">
+        <v>0.003527430413396837</v>
+      </c>
+      <c r="Z41" s="1" t="n">
+        <v>0.007054860826793674</v>
+      </c>
+      <c r="AA41" s="1" t="n">
+        <v>0.007054860826793674</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FISHer</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>0.0234617540347327</v>
+        <v>0.02847290890182314</v>
       </c>
       <c r="C42" t="n">
         <v>40</v>
@@ -2708,18 +3436,24 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" s="1" t="n">
-        <v>0.06239828200726781</v>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" s="1" t="n">
+        <v>0.02847290890182314</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Горыныч</t>
+          <t>Rabie</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>0.02337404659986632</v>
+        <v>0.02819602607876322</v>
       </c>
       <c r="C43" t="n">
         <v>41</v>
@@ -2736,33 +3470,47 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" s="1" t="n">
-        <v>0.006057021663608791</v>
-      </c>
-      <c r="P43" s="1" t="n">
-        <v>0.01211404332721758</v>
-      </c>
+        <v>0.001019231711927531</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" s="1" t="n">
-        <v>0.006057021663608791</v>
+        <v>0.001019231711927531</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>0.006057021663608791</v>
-      </c>
-      <c r="T43" s="1" t="n">
-        <v>0.003028510831804396</v>
-      </c>
+        <v>0.001019231711927531</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" s="1" t="n">
-        <v>0.01817106499082637</v>
+        <v>0.004076926847710125</v>
+      </c>
+      <c r="V43" s="1" t="n">
+        <v>0.003057695135782594</v>
+      </c>
+      <c r="W43" s="1" t="n">
+        <v>0.006115390271565187</v>
+      </c>
+      <c r="X43" s="1" t="n">
+        <v>0.007134621983492719</v>
+      </c>
+      <c r="Y43" s="1" t="n">
+        <v>0.006115390271565187</v>
+      </c>
+      <c r="Z43" s="1" t="n">
+        <v>0.01019231711927531</v>
+      </c>
+      <c r="AA43" s="1" t="n">
+        <v>0.0132500122550579</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Julia_2499</t>
+          <t>kuromi</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>0.02319896056500719</v>
+        <v>0.02801193922182588</v>
       </c>
       <c r="C44" t="n">
         <v>42</v>
@@ -2778,36 +3526,30 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" s="1" t="n">
-        <v>0.002689422741132297</v>
-      </c>
-      <c r="P44" s="1" t="n">
-        <v>0.002689422741132297</v>
-      </c>
-      <c r="Q44" s="1" t="n">
-        <v>0.005378845482264594</v>
-      </c>
-      <c r="R44" s="1" t="n">
-        <v>0.008068268223396891</v>
-      </c>
-      <c r="S44" s="1" t="n">
-        <v>0.002689422741132297</v>
-      </c>
-      <c r="T44" s="1" t="n">
-        <v>0.01075769096452919</v>
-      </c>
-      <c r="U44" s="1" t="n">
-        <v>0.01882595918792608</v>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" s="1" t="n">
+        <v>0.02801193922182588</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KidPoker</t>
+          <t>sl1dbygad</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>0.02311158223996105</v>
+        <v>0.02773656366808335</v>
       </c>
       <c r="C45" t="n">
         <v>43</v>
@@ -2829,18 +3571,24 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" s="1" t="n">
-        <v>0.02311158223996105</v>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" s="1" t="n">
+        <v>0.02773656366808335</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Gur4an</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>0.0229371556658979</v>
+        <v>0.02755348441041788</v>
       </c>
       <c r="C46" t="n">
         <v>44</v>
@@ -2853,39 +3601,33 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" s="1" t="n">
-        <v>0.002088994140792159</v>
-      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="1" t="n">
-        <v>0.002088994140792159</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" s="1" t="n">
-        <v>0.002088994140792159</v>
-      </c>
-      <c r="R46" s="1" t="n">
-        <v>0.006266982422376476</v>
-      </c>
-      <c r="S46" s="1" t="n">
-        <v>0.004177988281584317</v>
-      </c>
-      <c r="T46" s="1" t="n">
-        <v>0.01044497070396079</v>
-      </c>
-      <c r="U46" s="1" t="n">
-        <v>0.01044497070396079</v>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" s="1" t="n">
+        <v>0.02755348441041788</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Gur4an</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>0.02285010769495784</v>
+        <v>0.02746209644904412</v>
       </c>
       <c r="C47" t="n">
         <v>45</v>
@@ -2905,20 +3647,36 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" s="1" t="n">
-        <v>0.06077156301850489</v>
-      </c>
+      <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
+      <c r="V47" s="1" t="n">
+        <v>0.00360158641954677</v>
+      </c>
+      <c r="W47" s="1" t="n">
+        <v>0.00360158641954677</v>
+      </c>
+      <c r="X47" s="1" t="n">
+        <v>0.009003966048866925</v>
+      </c>
+      <c r="Y47" s="1" t="n">
+        <v>0.005402379629320155</v>
+      </c>
+      <c r="Z47" s="1" t="n">
+        <v>0.0126055524684137</v>
+      </c>
+      <c r="AA47" s="1" t="n">
+        <v>0.01080475925864031</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>ForceUser</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>0.0227631701210112</v>
+        <v>0.02737080974862121</v>
       </c>
       <c r="C48" t="n">
         <v>46</v>
@@ -2937,25 +3695,27 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" s="1" t="n">
-        <v>0.01654300154143256</v>
-      </c>
-      <c r="S48" s="1" t="n">
-        <v>0.008271500770716282</v>
-      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" s="1" t="n">
-        <v>0.008271500770716282</v>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" s="1" t="n">
+        <v>0.02737080974862121</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>0.02267634308442317</v>
+        <v>0.02727962442159903</v>
       </c>
       <c r="C49" t="n">
         <v>47</v>
@@ -2977,18 +3737,30 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" s="1" t="n">
-        <v>0.02267634308442317</v>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" s="1" t="n">
+        <v>0.01281937237857097</v>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" s="1" t="n">
+        <v>0.01281937237857097</v>
+      </c>
+      <c r="Z49" s="1" t="n">
+        <v>0.01281937237857097</v>
+      </c>
+      <c r="AA49" s="1" t="n">
+        <v>0.01281937237857097</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TryFraiz</t>
+          <t>Коленвал</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>0.0225896267260957</v>
+        <v>0.02718854058080291</v>
       </c>
       <c r="C50" t="n">
         <v>48</v>
@@ -3006,22 +3778,44 @@
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" s="1" t="n">
+        <v>0.005164996310942803</v>
+      </c>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
+      <c r="S50" s="1" t="n">
+        <v>0.01032999262188561</v>
+      </c>
+      <c r="T50" s="1" t="n">
+        <v>0.005164996310942803</v>
+      </c>
       <c r="U50" s="1" t="n">
-        <v>0.0225896267260957</v>
+        <v>0.005164996310942803</v>
+      </c>
+      <c r="V50" s="1" t="n">
+        <v>0.005164996310942803</v>
+      </c>
+      <c r="W50" s="1" t="n">
+        <v>0.005164996310942803</v>
+      </c>
+      <c r="X50" s="1" t="n">
+        <v>0.005164996310942803</v>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" s="1" t="n">
+        <v>0.02582498155471401</v>
+      </c>
+      <c r="AA50" s="1" t="n">
+        <v>0.005164996310942803</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rabie</t>
+          <t>turkoid</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>0.02250302118747094</v>
+        <v>0.02700667781108003</v>
       </c>
       <c r="C51" t="n">
         <v>49</v>
@@ -3031,30 +3825,66 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" s="1" t="n">
+        <v>0.001105019550371523</v>
+      </c>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" s="1" t="n">
+        <v>0.001105019550371523</v>
+      </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="M51" s="1" t="n">
+        <v>0.002210039100743047</v>
+      </c>
+      <c r="N51" s="1" t="n">
+        <v>0.002210039100743047</v>
+      </c>
+      <c r="O51" s="1" t="n">
+        <v>0.002210039100743047</v>
+      </c>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
+      <c r="Q51" s="1" t="n">
+        <v>0.006630117302229141</v>
+      </c>
       <c r="R51" s="1" t="n">
-        <v>0.04956612596359239</v>
-      </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
+        <v>0.004420078201486093</v>
+      </c>
+      <c r="S51" s="1" t="n">
+        <v>0.001105019550371523</v>
+      </c>
+      <c r="T51" s="1" t="n">
+        <v>0.001105019550371523</v>
+      </c>
+      <c r="U51" s="1" t="n">
+        <v>0.01105019550371523</v>
+      </c>
+      <c r="V51" s="1" t="n">
+        <v>0.00331505865111457</v>
+      </c>
+      <c r="W51" s="1" t="n">
+        <v>0.001105019550371523</v>
+      </c>
+      <c r="X51" s="1" t="n">
+        <v>0.004420078201486093</v>
+      </c>
+      <c r="Y51" s="1" t="n">
+        <v>0.0143652541548298</v>
+      </c>
+      <c r="Z51" s="1" t="n">
+        <v>0.005525097751857617</v>
+      </c>
+      <c r="AA51" s="1" t="n">
+        <v>0.00994517595334371</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kuromi</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>0.02233014313782</v>
+        <v>0.02691589910970015</v>
       </c>
       <c r="C52" t="n">
         <v>50</v>
@@ -3076,9 +3906,15 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" s="1" t="n">
-        <v>0.02233014313782</v>
-      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" s="1" t="n">
+        <v>0.05928612138700474</v>
+      </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B52">
@@ -3093,7 +3929,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:U52">
+  <conditionalFormatting sqref="D2:AA52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3107,7 +3943,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C52">
     <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="0">
-      <formula>18</formula>
+      <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
